--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G3" t="n">
         <v>2.1</v>
@@ -963,10 +963,10 @@
         <v>5.3</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G4" t="n">
         <v>2.64</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>2.14</v>
       </c>
       <c r="G5" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H5" t="n">
         <v>3.35</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.02</v>
       </c>
       <c r="G7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H7" t="n">
         <v>4.1</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G9" t="n">
         <v>2.52</v>
       </c>
       <c r="H9" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="I9" t="n">
         <v>4.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K9" t="n">
         <v>3.25</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.82</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H11" t="n">
         <v>5.2</v>
@@ -2515,7 +2515,7 @@
         <v>6.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="K11" t="n">
         <v>3.85</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
         <v>3.45</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
         <v>1.09</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
         <v>4.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
@@ -2924,7 +2924,7 @@
         <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="R13" t="n">
         <v>1.39</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH15"/>
+  <dimension ref="A1:BH17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Danish 2nd Division</t>
+          <t>Australian A-League Men</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>05:35:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Skive</t>
+          <t>Macarthur FC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Newcastle Jets</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.2</v>
+        <v>2.58</v>
       </c>
       <c r="G2" t="n">
-        <v>7.4</v>
+        <v>2.68</v>
       </c>
       <c r="H2" t="n">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="I2" t="n">
-        <v>1.76</v>
+        <v>2.58</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>2.16</v>
+        <v>3.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Australian A-League Men</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.04</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6</v>
+        <v>2.32</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3</v>
+        <v>2.42</v>
       </c>
       <c r="J3" t="n">
-        <v>2.98</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>2.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Skive</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.42</v>
+        <v>1.02</v>
       </c>
       <c r="G4" t="n">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>3.55</v>
+        <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.39</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.15</v>
+        <v>1.55</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -1325,37 +1325,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="H5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.35</v>
       </c>
-      <c r="I5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>1.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,50 +1524,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Sarmiento de Junin</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="G6" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3.15</v>
       </c>
-      <c r="H6" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.28</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -1907,36 +1907,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zaragoza</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.06</v>
+        <v>1.05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>3.95</v>
+        <v>2.4</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.28</v>
+        <v>1.28</v>
       </c>
       <c r="G9" t="n">
-        <v>2.52</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
         <v>4.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2.92</v>
+        <v>1.28</v>
       </c>
       <c r="K9" t="n">
-        <v>3.25</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="G10" t="n">
-        <v>2.52</v>
+        <v>2.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="J10" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="G11" t="n">
-        <v>2.04</v>
+        <v>2.52</v>
       </c>
       <c r="H11" t="n">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="I11" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.22</v>
+        <v>2.78</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.96</v>
+        <v>2.38</v>
       </c>
       <c r="G12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.2</v>
       </c>
-      <c r="H12" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.45</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="R12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="G13" t="n">
-        <v>1.61</v>
+        <v>2.22</v>
       </c>
       <c r="H13" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.04</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,378 +3071,766 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.85</v>
+        <v>2.96</v>
       </c>
       <c r="G14" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="H14" t="n">
-        <v>1.96</v>
+        <v>2.54</v>
       </c>
       <c r="I14" t="n">
-        <v>2.16</v>
+        <v>2.76</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X15" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:11:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Jaguares de Cordoba</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:11:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Argentinian Primera Division</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Talleres</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Boca Juniors</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="F17" t="n">
         <v>2.96</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G17" t="n">
         <v>3.2</v>
       </c>
-      <c r="H15" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="H17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I17" t="n">
         <v>3.1</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J17" t="n">
         <v>2.86</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K17" t="n">
         <v>3.05</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>1.46</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q17" t="n">
         <v>2.78</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>2026-03-31 04:04:26</t>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -760,16 +760,16 @@
         <v>2.58</v>
       </c>
       <c r="G2" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="H2" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="I2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K2" t="n">
         <v>4.5</v>
@@ -781,7 +781,7 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.12</v>
@@ -805,10 +805,10 @@
         <v>3.2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X2" t="n">
         <v>40</v>
@@ -823,7 +823,7 @@
         <v>40</v>
       </c>
       <c r="AB2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC2" t="n">
         <v>12</v>
@@ -847,7 +847,7 @@
         <v>25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
         <v>24</v>
@@ -862,10 +862,10 @@
         <v>10.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AP2" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="AQ2" t="n">
         <v>19.5</v>
@@ -880,7 +880,7 @@
         <v>20</v>
       </c>
       <c r="AU2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV2" t="n">
         <v>12</v>
@@ -889,10 +889,10 @@
         <v>19.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>12.5</v>
@@ -916,11 +916,11 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -981,13 +981,13 @@
         <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
         <v>1.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -1002,22 +1002,22 @@
         <v>1.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z3" t="n">
         <v>18.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AB3" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AC3" t="n">
         <v>8.4</v>
@@ -1029,52 +1029,52 @@
         <v>28</v>
       </c>
       <c r="AF3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH3" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
         <v>40</v>
       </c>
       <c r="AJ3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN3" t="n">
         <v>32</v>
       </c>
       <c r="AO3" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
         <v>14</v>
       </c>
       <c r="AS3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU3" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.6</v>
       </c>
       <c r="AV3" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
         <v>21</v>
       </c>
       <c r="AX3" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -1092,29 +1092,29 @@
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG3" t="n">
         <v>14</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02</v>
+        <v>1.49</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>1.76</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -1348,10 +1348,10 @@
         <v>4.5</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
         <v>3.35</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G6" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="H6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J6" t="n">
         <v>2.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1566,7 +1566,7 @@
         <v>1.39</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>2.34</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.05</v>
+        <v>2.9</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.28</v>
+        <v>2.08</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="I9" t="n">
         <v>4.5</v>
       </c>
       <c r="J9" t="n">
-        <v>1.28</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q9" t="n">
         <v>2.72</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G10" t="n">
         <v>2.18</v>
@@ -2318,7 +2318,7 @@
         <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J10" t="n">
         <v>3.3</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>2.28</v>
       </c>
       <c r="G11" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H11" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J11" t="n">
         <v>2.92</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>3.6</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J12" t="n">
         <v>2.98</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.92</v>
+        <v>1.26</v>
       </c>
       <c r="G13" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="I13" t="n">
         <v>5.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H14" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="I14" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="J14" t="n">
         <v>3.35</v>
@@ -3103,7 +3103,7 @@
         <v>3.45</v>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
@@ -3112,7 +3112,7 @@
         <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P14" t="n">
         <v>1.73</v>
@@ -3130,82 +3130,82 @@
         <v>1.87</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="X14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AE14" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AF14" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AG14" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK14" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM14" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN14" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO14" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AP14" t="n">
         <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU14" t="n">
         <v>6.6</v>
@@ -3214,41 +3214,41 @@
         <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
         <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BD14" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I15" t="n">
         <v>7.6</v>
@@ -3312,58 +3312,58 @@
         <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
         <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U15" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V15" t="n">
         <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X15" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y15" t="n">
         <v>27</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA15" t="n">
         <v>190</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE15" t="n">
         <v>120</v>
       </c>
       <c r="AF15" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AG15" t="n">
         <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI15" t="n">
         <v>110</v>
@@ -3372,34 +3372,34 @@
         <v>15.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM15" t="n">
         <v>150</v>
       </c>
       <c r="AN15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
         <v>19.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU15" t="n">
         <v>8.4</v>
@@ -3408,19 +3408,19 @@
         <v>18.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY15" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB15" t="n">
         <v>12.5</v>
@@ -3429,20 +3429,20 @@
         <v>14</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BE15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF15" t="n">
         <v>7.4</v>
       </c>
-      <c r="BF15" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG15" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
         <v>4.3</v>
       </c>
       <c r="G16" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H16" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="I16" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K16" t="n">
         <v>3.75</v>
@@ -3506,7 +3506,7 @@
         <v>1.73</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>2.82</v>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J17" t="n">
         <v>2.86</v>
@@ -3700,7 +3700,7 @@
         <v>1.46</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H2" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J2" t="n">
         <v>4.3</v>
@@ -781,52 +781,52 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="R2" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="S2" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="T2" t="n">
         <v>1.4</v>
       </c>
       <c r="U2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
         <v>40</v>
       </c>
       <c r="Y2" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
         <v>14</v>
@@ -835,7 +835,7 @@
         <v>23</v>
       </c>
       <c r="AF2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
         <v>14</v>
@@ -847,7 +847,7 @@
         <v>25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK2" t="n">
         <v>24</v>
@@ -856,71 +856,71 @@
         <v>25</v>
       </c>
       <c r="AM2" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AN2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU2" t="n">
         <v>10</v>
       </c>
-      <c r="AP2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AV2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY2" t="n">
         <v>12</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>12.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BB2" t="n">
-        <v>34</v>
+        <v>7.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>22</v>
+        <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>34</v>
+        <v>7.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -963,34 +963,34 @@
         <v>2.42</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="T3" t="n">
         <v>1.68</v>
@@ -1005,116 +1005,116 @@
         <v>1.43</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>15.5</v>
+        <v>1.16</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>1.16</v>
       </c>
       <c r="AR3" t="n">
-        <v>14</v>
+        <v>1.16</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.8</v>
+        <v>1.16</v>
       </c>
       <c r="AT3" t="n">
-        <v>12.5</v>
+        <v>1.16</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.4</v>
+        <v>1.06</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>1.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>21</v>
+        <v>1.16</v>
       </c>
       <c r="AX3" t="n">
-        <v>19.5</v>
+        <v>1.16</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>1.16</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>1.16</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.9</v>
+        <v>1.16</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.2</v>
+        <v>1.16</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.8</v>
+        <v>1.16</v>
       </c>
       <c r="BD3" t="n">
-        <v>6</v>
+        <v>1.16</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.2</v>
+        <v>1.16</v>
       </c>
       <c r="BF3" t="n">
-        <v>21</v>
+        <v>1.16</v>
       </c>
       <c r="BG3" t="n">
-        <v>14</v>
+        <v>1.16</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.2</v>
+        <v>1.02</v>
       </c>
       <c r="G4" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.49</v>
+        <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>1.76</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G5" t="n">
         <v>2.1</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
         <v>3.2</v>
@@ -1372,7 +1372,7 @@
         <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>3.25</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.39</v>
+        <v>1.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G7" t="n">
         <v>2.12</v>
       </c>
-      <c r="G7" t="n">
-        <v>2.34</v>
-      </c>
       <c r="H7" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
         <v>3.9</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
         <v>4.1</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="G9" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="I9" t="n">
         <v>4.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="G10" t="n">
         <v>2.18</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
         <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.28</v>
+        <v>1.43</v>
       </c>
       <c r="G11" t="n">
-        <v>2.54</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>3.75</v>
+        <v>1.43</v>
       </c>
       <c r="I11" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>2.92</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="G12" t="n">
         <v>2.52</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="I12" t="n">
         <v>3.95</v>
       </c>
       <c r="J12" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>1.26</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
         <v>5.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3.05</v>
+        <v>1.25</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -2924,7 +2924,7 @@
         <v>1.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4</v>
+        <v>970</v>
       </c>
       <c r="H14" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="I14" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
         <v>3.45</v>
       </c>
       <c r="L14" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.18</v>
+        <v>1.37</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1</v>
+        <v>1.37</v>
       </c>
       <c r="T14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W14" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="X14" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="G15" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
         <v>4.2</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>1.98</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>1.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.77</v>
+        <v>1.27</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>1.89</v>
       </c>
       <c r="T15" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
         <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="X15" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="I16" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="K16" t="n">
-        <v>3.75</v>
+        <v>5.7</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.96</v>
+        <v>1.48</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H17" t="n">
         <v>2.82</v>
       </c>
       <c r="I17" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>2.86</v>
+        <v>1.47</v>
       </c>
       <c r="K17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G2" t="n">
         <v>2.64</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I2" t="n">
         <v>2.56</v>
@@ -781,25 +781,25 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="O2" t="n">
         <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="R2" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="S2" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="U2" t="n">
         <v>3.25</v>
@@ -814,19 +814,19 @@
         <v>40</v>
       </c>
       <c r="Y2" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD2" t="n">
         <v>14</v>
@@ -835,7 +835,7 @@
         <v>23</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG2" t="n">
         <v>14</v>
@@ -847,7 +847,7 @@
         <v>25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AK2" t="n">
         <v>24</v>
@@ -856,71 +856,71 @@
         <v>25</v>
       </c>
       <c r="AM2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AN2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.5</v>
+        <v>29</v>
       </c>
       <c r="AQ2" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="AT2" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AU2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BC2" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG2" t="n">
         <v>8.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -969,34 +969,34 @@
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
         <v>1.68</v>
       </c>
       <c r="U3" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V3" t="n">
         <v>1.7</v>
@@ -1005,37 +1005,37 @@
         <v>1.43</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1044,77 +1044,77 @@
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.16</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.16</v>
+        <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.16</v>
+        <v>9</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.16</v>
+        <v>12.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.06</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.1</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.16</v>
+        <v>21</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.16</v>
+        <v>19.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.16</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.16</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.16</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.16</v>
+        <v>9.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.16</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.16</v>
+        <v>10.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.16</v>
+        <v>21</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.16</v>
+        <v>14</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.02</v>
+        <v>5.1</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02</v>
+        <v>1.57</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>1.81</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1178,88 +1178,88 @@
         <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>1.24</v>
+        <v>2.76</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP4" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AS4" t="n">
         <v>1.03</v>
@@ -1268,10 +1268,10 @@
         <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AW4" t="n">
         <v>1.03</v>
@@ -1301,14 +1301,14 @@
         <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H5" t="n">
         <v>4.6</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J5" t="n">
         <v>3.2</v>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q5" t="n">
         <v>2.26</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="G6" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>2.92</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3.25</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G7" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I7" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="K7" t="n">
         <v>4.1</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="H9" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="I9" t="n">
         <v>4.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G10" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
         <v>4.7</v>
@@ -2324,7 +2324,7 @@
         <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.43</v>
+        <v>2.26</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="H11" t="n">
-        <v>1.43</v>
+        <v>3.65</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>2.96</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="G12" t="n">
         <v>2.52</v>
       </c>
       <c r="H12" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="I12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.26</v>
+        <v>1.92</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
         <v>5.1</v>
       </c>
       <c r="J13" t="n">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="Q13" t="n">
         <v>2.46</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>970</v>
+        <v>3.3</v>
       </c>
       <c r="H14" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="I14" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
         <v>3.45</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.37</v>
+        <v>2.16</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>1.37</v>
+        <v>4.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL14" t="n">
         <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN14" t="n">
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>1.58</v>
       </c>
       <c r="G15" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
         <v>4.2</v>
@@ -3297,152 +3297,152 @@
         <v>4.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>1.98</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.27</v>
+        <v>1.81</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>1.89</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V15" t="n">
         <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z15" t="n">
         <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL15" t="n">
         <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="G16" t="n">
-        <v>9.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="H16" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="I16" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="J16" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K16" t="n">
-        <v>5.7</v>
+        <v>3.75</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.48</v>
+        <v>2.96</v>
       </c>
       <c r="G17" t="n">
         <v>3.15</v>
@@ -3676,10 +3676,10 @@
         <v>2.82</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J17" t="n">
-        <v>1.47</v>
+        <v>2.86</v>
       </c>
       <c r="K17" t="n">
         <v>3.1</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH17"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Slovakian 2 Liga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Zlate Moravce</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Lokomotiva Zvolen</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="G5" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>1.68</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.26</v>
+        <v>1.61</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="G6" t="n">
-        <v>2.72</v>
+        <v>2.06</v>
       </c>
       <c r="H6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.4</v>
       </c>
-      <c r="I6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.25</v>
-      </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>2.26</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,184 +1713,184 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>CSA Steaua Bucuresti</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>1.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -1912,31 +1912,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="G8" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.68</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.28</v>
+        <v>1.6</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.08</v>
+        <v>2.9</v>
       </c>
       <c r="G9" t="n">
-        <v>2.18</v>
+        <v>3.15</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.68</v>
+        <v>2.28</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zaragoza</t>
+          <t>Sarmiento de Junin</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.02</v>
+        <v>2.46</v>
       </c>
       <c r="G10" t="n">
-        <v>2.16</v>
+        <v>2.72</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.22</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="G11" t="n">
-        <v>2.52</v>
+        <v>2.18</v>
       </c>
       <c r="H11" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>2.52</v>
+        <v>2.16</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.52</v>
+        <v>2.22</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="H13" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J14" t="n">
         <v>3</v>
       </c>
-      <c r="G14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.35</v>
-      </c>
       <c r="K14" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="G15" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="L15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>1.61</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.81</v>
+        <v>2.46</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,378 +3459,766 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="H16" t="n">
-        <v>1.89</v>
+        <v>2.48</v>
       </c>
       <c r="I16" t="n">
-        <v>2.08</v>
+        <v>2.66</v>
       </c>
       <c r="J16" t="n">
         <v>3.35</v>
       </c>
       <c r="K16" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-03-31 14:53:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Jaguares de Cordoba</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-03-31 14:53:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Argentinian Primera Division</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Talleres</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Boca Juniors</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F19" t="n">
         <v>2.96</v>
       </c>
-      <c r="G17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="H17" t="n">
+      <c r="G19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H19" t="n">
         <v>2.82</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I19" t="n">
         <v>3.05</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J19" t="n">
         <v>2.86</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K19" t="n">
         <v>3.1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>1.45</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q19" t="n">
         <v>2.86</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>2026-03-31 12:43:31</t>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -766,7 +766,7 @@
         <v>2.52</v>
       </c>
       <c r="I2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J2" t="n">
         <v>4.3</v>
@@ -775,7 +775,7 @@
         <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
@@ -805,7 +805,7 @@
         <v>3.25</v>
       </c>
       <c r="V2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W2" t="n">
         <v>1.6</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -978,7 +978,7 @@
         <v>4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
         <v>2.12</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
         <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="R4" t="n">
         <v>1.42</v>
@@ -1193,7 +1193,7 @@
         <v>1.98</v>
       </c>
       <c r="V4" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="W4" t="n">
         <v>1.15</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="G5" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="H5" t="n">
         <v>4.5</v>
@@ -1351,100 +1351,100 @@
         <v>6.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="T5" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="X5" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="Y5" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Z5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA5" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AD5" t="n">
         <v>25</v>
       </c>
       <c r="AE5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF5" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
         <v>19.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM5" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN5" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AO5" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
         <v>1.03</v>
@@ -1495,14 +1495,14 @@
         <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BG5" t="n">
         <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.98</v>
       </c>
       <c r="G6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H6" t="n">
         <v>4.7</v>
@@ -1551,13 +1551,13 @@
         <v>3.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.4</v>
@@ -1569,134 +1569,134 @@
         <v>2.26</v>
       </c>
       <c r="R6" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="U6" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="V6" t="n">
         <v>1.23</v>
       </c>
       <c r="W6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="X6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y6" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z6" t="n">
         <v>38</v>
       </c>
       <c r="AA6" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL6" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM6" t="n">
         <v>170</v>
       </c>
       <c r="AN6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AO6" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP6" t="n">
         <v>9.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.5</v>
+        <v>25</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
         <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="AX6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY6" t="n">
         <v>9.6</v>
       </c>
-      <c r="AY6" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>4.2</v>
+        <v>17</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="BC6" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="BE6" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
@@ -1739,7 +1739,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>1.48</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -1748,16 +1748,16 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="O7" t="n">
         <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q7" t="n">
         <v>1.3</v>
@@ -1766,7 +1766,7 @@
         <v>1.15</v>
       </c>
       <c r="S7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -1924,167 +1924,167 @@
         <v>2.12</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I8" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="J8" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
         <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P8" t="n">
         <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -2133,152 +2133,152 @@
         <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P9" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q9" t="n">
         <v>2.28</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G10" t="n">
         <v>2.72</v>
@@ -2327,16 +2327,16 @@
         <v>3.25</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P10" t="n">
         <v>1.4</v>
@@ -2345,134 +2345,134 @@
         <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -2515,158 +2515,158 @@
         <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P11" t="n">
         <v>1.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -2703,10 +2703,10 @@
         <v>2.16</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
         <v>3.3</v>
@@ -2715,16 +2715,16 @@
         <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P12" t="n">
         <v>1.67</v>
@@ -2733,134 +2733,134 @@
         <v>2.22</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
         <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="AT16" t="n">
         <v>9.4</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -3709,10 +3709,10 @@
         <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U17" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V17" t="n">
         <v>1.15</v>
@@ -3823,14 +3823,14 @@
         <v>8.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG17" t="n">
         <v>8.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q18" t="n">
         <v>2.06</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
         <v>3.2</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G2" t="n">
         <v>2.62</v>
       </c>
-      <c r="G2" t="n">
-        <v>2.64</v>
-      </c>
       <c r="H2" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I2" t="n">
         <v>2.58</v>
@@ -775,43 +775,43 @@
         <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R2" t="n">
         <v>1.96</v>
       </c>
       <c r="S2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="T2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="U2" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="V2" t="n">
         <v>1.63</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y2" t="n">
         <v>24</v>
@@ -826,10 +826,10 @@
         <v>24</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
         <v>23</v>
@@ -850,7 +850,7 @@
         <v>42</v>
       </c>
       <c r="AK2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP2" t="n">
         <v>29</v>
@@ -874,7 +874,7 @@
         <v>22</v>
       </c>
       <c r="AS2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT2" t="n">
         <v>20</v>
@@ -889,7 +889,7 @@
         <v>19.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY2" t="n">
         <v>12.5</v>
@@ -916,11 +916,11 @@
         <v>9</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="n">
         <v>36</v>
@@ -1068,7 +1068,7 @@
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
         <v>12.5</v>
@@ -1092,13 +1092,13 @@
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB3" t="n">
         <v>10</v>
       </c>
       <c r="BC3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BD3" t="n">
         <v>9.800000000000001</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>1.57</v>
       </c>
       <c r="I4" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="J4" t="n">
         <v>3.65</v>
@@ -1178,7 +1178,7 @@
         <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="R4" t="n">
         <v>1.42</v>
@@ -1205,10 +1205,10 @@
         <v>10.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AB4" t="n">
         <v>25</v>
@@ -1217,10 +1217,10 @@
         <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AF4" t="n">
         <v>60</v>
@@ -1253,7 +1253,7 @@
         <v>10.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>7</v>
@@ -1262,10 +1262,10 @@
         <v>8</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AU4" t="n">
         <v>7.6</v>
@@ -1274,41 +1274,41 @@
         <v>7.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>70</v>
+        <v>4.8</v>
       </c>
       <c r="BG4" t="n">
         <v>6.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="H5" t="n">
         <v>4.5</v>
@@ -1354,7 +1354,7 @@
         <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L5" t="n">
         <v>1.25</v>
@@ -1363,52 +1363,52 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="R5" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="S5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="U5" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
         <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Y5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA5" t="n">
         <v>140</v>
       </c>
       <c r="AB5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD5" t="n">
         <v>25</v>
@@ -1417,16 +1417,16 @@
         <v>70</v>
       </c>
       <c r="AF5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
         <v>21</v>
       </c>
       <c r="AI5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
         <v>19.5</v>
@@ -1435,74 +1435,74 @@
         <v>18</v>
       </c>
       <c r="AL5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM5" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G6" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
         <v>3.3</v>
@@ -1563,10 +1563,10 @@
         <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R6" t="n">
         <v>1.26</v>
@@ -1581,16 +1581,16 @@
         <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z6" t="n">
         <v>38</v>
@@ -1620,7 +1620,7 @@
         <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ6" t="n">
         <v>24</v>
@@ -1644,59 +1644,59 @@
         <v>9.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
         <v>25</v>
       </c>
       <c r="AS6" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX6" t="n">
         <v>10</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AY6" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BB6" t="n">
         <v>20</v>
       </c>
       <c r="BC6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BF6" t="n">
         <v>16</v>
       </c>
       <c r="BG6" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H7" t="n">
         <v>1.09</v>
       </c>
-      <c r="G7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.04</v>
-      </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.48</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -1751,13 +1751,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
         <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
         <v>1.3</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="G8" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H8" t="n">
         <v>3.45</v>
       </c>
       <c r="I8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
         <v>4.1</v>
@@ -1951,13 +1951,13 @@
         <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S8" t="n">
         <v>2.48</v>
@@ -1969,10 +1969,10 @@
         <v>2.48</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2032,7 +2032,7 @@
         <v>3.75</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>3.2</v>
       </c>
       <c r="AR8" t="n">
         <v>21</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
@@ -2193,7 +2193,7 @@
         <v>36</v>
       </c>
       <c r="AF9" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
         <v>13.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G10" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="H10" t="n">
         <v>3.4</v>
@@ -2324,13 +2324,13 @@
         <v>2.92</v>
       </c>
       <c r="K10" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N10" t="n">
         <v>2.24</v>
@@ -2345,22 +2345,22 @@
         <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S10" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="X10" t="n">
         <v>7.4</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
         <v>2.18</v>
@@ -2515,22 +2515,22 @@
         <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
         <v>3.65</v>
       </c>
       <c r="L11" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="O11" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="P11" t="n">
         <v>1.51</v>
@@ -2539,7 +2539,7 @@
         <v>2.66</v>
       </c>
       <c r="R11" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S11" t="n">
         <v>4.7</v>
@@ -2560,7 +2560,7 @@
         <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z11" t="n">
         <v>44</v>
@@ -2611,49 +2611,49 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AQ11" t="n">
         <v>2.52</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="AS11" t="n">
         <v>3.05</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AU11" t="n">
         <v>2.36</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="AW11" t="n">
         <v>3.05</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AY11" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BA11" t="n">
         <v>3.05</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.84</v>
+        <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BE11" t="n">
         <v>3.05</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
         <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
         <v>1.09</v>
@@ -2727,10 +2727,10 @@
         <v>1.41</v>
       </c>
       <c r="P12" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R12" t="n">
         <v>1.2</v>
@@ -2739,7 +2739,7 @@
         <v>3.7</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U12" t="n">
         <v>1.73</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -3103,16 +3103,16 @@
         <v>3.2</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P14" t="n">
         <v>1.52</v>
@@ -3121,134 +3121,134 @@
         <v>2.52</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -3297,152 +3297,152 @@
         <v>3.75</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P15" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="Q15" t="n">
         <v>2.46</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
         <v>4.1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U16" t="n">
         <v>1.98</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G17" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="H17" t="n">
         <v>6.6</v>
@@ -3682,10 +3682,10 @@
         <v>4.2</v>
       </c>
       <c r="K17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
@@ -3709,16 +3709,16 @@
         <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="U17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V17" t="n">
         <v>1.15</v>
       </c>
       <c r="W17" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="X17" t="n">
         <v>17.5</v>
@@ -3766,7 +3766,7 @@
         <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN17" t="n">
         <v>9</v>
@@ -3781,7 +3781,7 @@
         <v>19</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS17" t="n">
         <v>8.6</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q18" t="n">
         <v>2.06</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -760,10 +760,10 @@
         <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H2" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="I2" t="n">
         <v>2.58</v>
@@ -775,7 +775,7 @@
         <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
@@ -793,7 +793,7 @@
         <v>1.38</v>
       </c>
       <c r="R2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S2" t="n">
         <v>1.93</v>
@@ -808,10 +808,10 @@
         <v>1.63</v>
       </c>
       <c r="W2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y2" t="n">
         <v>24</v>
@@ -838,10 +838,10 @@
         <v>26</v>
       </c>
       <c r="AG2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI2" t="n">
         <v>25</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -978,13 +978,13 @@
         <v>4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
         <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="R3" t="n">
         <v>1.44</v>
@@ -1092,13 +1092,13 @@
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB3" t="n">
         <v>10</v>
       </c>
       <c r="BC3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BD3" t="n">
         <v>9.800000000000001</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="G4" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.31</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="U4" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="V4" t="n">
-        <v>2.22</v>
+        <v>2.7</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AA4" t="n">
         <v>970</v>
       </c>
       <c r="AB4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AE4" t="n">
         <v>970</v>
       </c>
       <c r="AF4" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AG4" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AH4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AI4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AL4" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AM4" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AO4" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AP4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY4" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.3</v>
       </c>
       <c r="AZ4" t="n">
         <v>4.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC4" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC4" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE4" t="n">
         <v>4.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="G5" t="n">
         <v>1.72</v>
@@ -1351,7 +1351,7 @@
         <v>6.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
         <v>5.1</v>
@@ -1363,7 +1363,7 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
@@ -1372,13 +1372,13 @@
         <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="R5" t="n">
         <v>1.61</v>
       </c>
       <c r="S5" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
         <v>1.64</v>
@@ -1459,10 +1459,10 @@
         <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AV5" t="n">
         <v>4.3</v>
@@ -1471,7 +1471,7 @@
         <v>4.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AY5" t="n">
         <v>3.7</v>
@@ -1495,14 +1495,14 @@
         <v>4.9</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BG5" t="n">
         <v>4.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         <v>5.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
         <v>3.4</v>
@@ -1572,7 +1572,7 @@
         <v>1.26</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T6" t="n">
         <v>1.91</v>
@@ -1584,7 +1584,7 @@
         <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="X6" t="n">
         <v>11</v>
@@ -1656,7 +1656,7 @@
         <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
         <v>17</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -1733,13 +1733,13 @@
         <v>1000</v>
       </c>
       <c r="H7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
         <v>1.09</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.03</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -1751,13 +1751,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="O7" t="n">
         <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="Q7" t="n">
         <v>1.3</v>
@@ -1766,13 +1766,13 @@
         <v>1.15</v>
       </c>
       <c r="S7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.06</v>
       </c>
       <c r="G8" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H8" t="n">
         <v>3.45</v>
@@ -1972,119 +1972,119 @@
         <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y8" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Z8" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB8" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AF8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AG8" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AJ8" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AK8" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL8" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AM8" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AN8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV8" t="n">
         <v>13</v>
       </c>
-      <c r="AO8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AR8" t="n">
+      <c r="AW8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB8" t="n">
         <v>21</v>
       </c>
-      <c r="AS8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>19</v>
-      </c>
       <c r="BC8" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>38</v>
+        <v>7.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG8" t="n">
-        <v>18</v>
+        <v>6.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
         <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
         <v>1.89</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G10" t="n">
         <v>2.64</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -2527,10 +2527,10 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="P11" t="n">
         <v>1.51</v>
@@ -2539,13 +2539,13 @@
         <v>2.66</v>
       </c>
       <c r="R11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S11" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
         <v>1.54</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H12" t="n">
         <v>4.1</v>
@@ -2718,149 +2718,149 @@
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q12" t="n">
         <v>2.26</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="U12" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="V12" t="n">
         <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X12" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN12" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AO12" t="n">
         <v>100</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.2</v>
+        <v>9.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.3</v>
+        <v>10.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>19.5</v>
+        <v>6.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.9</v>
+        <v>6.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="AW12" t="n">
-        <v>40</v>
+        <v>7.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.55</v>
+        <v>18.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="BB12" t="n">
-        <v>17</v>
+        <v>6.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BG12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -3106,13 +3106,13 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N14" t="n">
-        <v>2.26</v>
+        <v>2.62</v>
       </c>
       <c r="O14" t="n">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="P14" t="n">
         <v>1.52</v>
@@ -3121,16 +3121,16 @@
         <v>2.52</v>
       </c>
       <c r="R14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="V14" t="n">
         <v>1.34</v>
@@ -3139,116 +3139,116 @@
         <v>1.66</v>
       </c>
       <c r="X14" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY14" t="n">
         <v>10</v>
       </c>
-      <c r="Y14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AZ14" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD14" t="n">
         <v>8</v>
       </c>
-      <c r="AC14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AQ14" t="n">
+      <c r="BE14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF14" t="n">
         <v>7.4</v>
       </c>
-      <c r="AR14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>26</v>
-      </c>
       <c r="BG14" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
         <v>3.25</v>
       </c>
       <c r="K15" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3303,10 +3303,10 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="P15" t="n">
         <v>1.56</v>
@@ -3321,10 +3321,10 @@
         <v>4.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="V15" t="n">
         <v>1.25</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
         <v>1.4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
         <v>2.16</v>
@@ -3515,7 +3515,7 @@
         <v>4.1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U16" t="n">
         <v>1.98</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
         <v>4.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -3873,158 +3873,158 @@
         <v>2.04</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
         <v>3.75</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q18" t="n">
         <v>2.06</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
         <v>2.86</v>
       </c>
       <c r="K19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>1.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -772,10 +772,10 @@
         <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -978,7 +978,7 @@
         <v>4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
         <v>2.12</v>
@@ -993,10 +993,10 @@
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U3" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V3" t="n">
         <v>1.7</v>
@@ -1038,7 +1038,7 @@
         <v>16.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="n">
         <v>55</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -1154,13 +1154,13 @@
         <v>1.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="J4" t="n">
         <v>4.6</v>
       </c>
       <c r="K4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.31</v>
@@ -1193,13 +1193,13 @@
         <v>1.89</v>
       </c>
       <c r="V4" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="W4" t="n">
         <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="Y4" t="n">
         <v>11</v>
@@ -1211,7 +1211,7 @@
         <v>970</v>
       </c>
       <c r="AB4" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AC4" t="n">
         <v>970</v>
@@ -1226,10 +1226,10 @@
         <v>75</v>
       </c>
       <c r="AG4" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="AH4" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AI4" t="n">
         <v>42</v>
@@ -1259,10 +1259,10 @@
         <v>3.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.55</v>
+        <v>6.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.8</v>
+        <v>9.6</v>
       </c>
       <c r="AT4" t="n">
         <v>4.4</v>
@@ -1274,7 +1274,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.95</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
         <v>4.8</v>
@@ -1283,7 +1283,7 @@
         <v>4.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA4" t="n">
         <v>4.6</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
@@ -1378,7 +1378,7 @@
         <v>1.61</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T5" t="n">
         <v>1.64</v>
@@ -1390,7 +1390,7 @@
         <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="X5" t="n">
         <v>30</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -1539,10 +1539,10 @@
         <v>2.08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
         <v>3.35</v>
@@ -1569,7 +1569,7 @@
         <v>2.22</v>
       </c>
       <c r="R6" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
         <v>4.3</v>
@@ -1584,7 +1584,7 @@
         <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="X6" t="n">
         <v>11</v>
@@ -1593,7 +1593,7 @@
         <v>15</v>
       </c>
       <c r="Z6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA6" t="n">
         <v>120</v>
@@ -1605,7 +1605,7 @@
         <v>7.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE6" t="n">
         <v>75</v>
@@ -1647,22 +1647,22 @@
         <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
         <v>17</v>
       </c>
       <c r="AW6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX6" t="n">
         <v>10</v>
@@ -1674,29 +1674,29 @@
         <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB6" t="n">
         <v>20</v>
       </c>
       <c r="BC6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BE6" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BF6" t="n">
         <v>16</v>
       </c>
       <c r="BG6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -1742,7 +1742,7 @@
         <v>1.09</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1835,52 +1835,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.06</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H8" t="n">
         <v>3.45</v>
@@ -1933,10 +1933,10 @@
         <v>3.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1969,43 +1969,43 @@
         <v>2.48</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X8" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
         <v>20</v>
       </c>
       <c r="Z8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA8" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB8" t="n">
         <v>14.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF8" t="n">
         <v>16.5</v>
       </c>
-      <c r="AE8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>17</v>
-      </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
         <v>40</v>
@@ -2014,10 +2014,10 @@
         <v>27</v>
       </c>
       <c r="AK8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM8" t="n">
         <v>60</v>
@@ -2026,65 +2026,65 @@
         <v>11</v>
       </c>
       <c r="AO8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP8" t="n">
         <v>19.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AT8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>13</v>
       </c>
-      <c r="AW8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BA8" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BB8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC8" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF8" t="n">
         <v>9</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
         <v>2.28</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
         <v>4.4</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>1.71</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Q10" t="n">
         <v>3.1</v>
@@ -2354,7 +2354,7 @@
         <v>2.34</v>
       </c>
       <c r="U10" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
         <v>1.34</v>
@@ -2405,10 +2405,10 @@
         <v>46</v>
       </c>
       <c r="AL10" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM10" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AN10" t="n">
         <v>60</v>
@@ -2447,7 +2447,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA10" t="n">
         <v>8.6</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
         <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
         <v>3.65</v>
@@ -2524,10 +2524,10 @@
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O11" t="n">
         <v>1.56</v>
@@ -2539,7 +2539,7 @@
         <v>2.66</v>
       </c>
       <c r="R11" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
         <v>5.6</v>
@@ -2548,125 +2548,125 @@
         <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="V11" t="n">
         <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AG11" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ11" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AK11" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AL11" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN11" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.52</v>
+        <v>4.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.86</v>
+        <v>6.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.05</v>
+        <v>7.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.26</v>
+        <v>5.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.36</v>
+        <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.74</v>
+        <v>5.9</v>
       </c>
       <c r="AW11" t="n">
-        <v>3.05</v>
+        <v>7.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.56</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY11" t="n">
-        <v>2.58</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.84</v>
+        <v>6.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>3.05</v>
+        <v>7.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.82</v>
+        <v>6.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.96</v>
+        <v>7.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.05</v>
+        <v>8</v>
       </c>
       <c r="BF11" t="n">
-        <v>17.5</v>
+        <v>6.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.05</v>
+        <v>8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H12" t="n">
         <v>4.1</v>
@@ -2733,22 +2733,22 @@
         <v>2.26</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
         <v>4.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U12" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V12" t="n">
         <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X12" t="n">
         <v>11.5</v>
@@ -2838,7 +2838,7 @@
         <v>18.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="BB12" t="n">
         <v>6.6</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="Q13" t="n">
         <v>2.74</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T14" t="n">
         <v>2.08</v>
@@ -3193,7 +3193,7 @@
         <v>100</v>
       </c>
       <c r="AP14" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ14" t="n">
         <v>8.6</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I15" t="n">
         <v>5.1</v>
@@ -3294,7 +3294,7 @@
         <v>3.25</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3303,7 +3303,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="n">
         <v>1.05</v>
@@ -3327,10 +3327,10 @@
         <v>1.56</v>
       </c>
       <c r="V15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W15" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X15" t="n">
         <v>13</v>
@@ -3381,7 +3381,7 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
@@ -3393,10 +3393,10 @@
         <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="AT15" t="n">
         <v>2.2</v>
@@ -3405,10 +3405,10 @@
         <v>5.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="AX15" t="n">
         <v>2.46</v>
@@ -3420,29 +3420,29 @@
         <v>2.72</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BB15" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BF15" t="n">
         <v>15</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -3497,13 +3497,13 @@
         <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q16" t="n">
         <v>2.16</v>
@@ -3515,7 +3515,7 @@
         <v>4.1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U16" t="n">
         <v>1.98</v>
@@ -3560,7 +3560,7 @@
         <v>19.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ16" t="n">
         <v>60</v>
@@ -3602,7 +3602,7 @@
         <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX16" t="n">
         <v>18</v>
@@ -3617,26 +3617,26 @@
         <v>8.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BD16" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE16" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BG16" t="n">
         <v>21</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G17" t="n">
         <v>1.59</v>
       </c>
-      <c r="G17" t="n">
-        <v>1.6</v>
-      </c>
       <c r="H17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I17" t="n">
         <v>7.4</v>
@@ -3709,46 +3709,46 @@
         <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="U17" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V17" t="n">
         <v>1.15</v>
       </c>
       <c r="W17" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X17" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y17" t="n">
         <v>24</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA17" t="n">
         <v>190</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG17" t="n">
         <v>10</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>10.5</v>
       </c>
       <c r="AH17" t="n">
         <v>24</v>
@@ -3757,13 +3757,13 @@
         <v>110</v>
       </c>
       <c r="AJ17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK17" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM17" t="n">
         <v>140</v>
@@ -3772,65 +3772,65 @@
         <v>9</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP17" t="n">
         <v>14</v>
       </c>
       <c r="AQ17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX17" t="n">
         <v>8.4</v>
       </c>
-      <c r="AV17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>8</v>
-      </c>
       <c r="AY17" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="BB17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
         <v>1.89</v>
       </c>
       <c r="I18" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J18" t="n">
         <v>3.4</v>
@@ -3891,7 +3891,7 @@
         <v>1.35</v>
       </c>
       <c r="P18" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q18" t="n">
         <v>2.06</v>
@@ -3903,13 +3903,13 @@
         <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V18" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W18" t="n">
         <v>1.23</v>
@@ -3969,7 +3969,7 @@
         <v>22</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AQ18" t="n">
         <v>2.06</v>
@@ -3978,7 +3978,7 @@
         <v>7.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AT18" t="n">
         <v>9.6</v>
@@ -3987,44 +3987,44 @@
         <v>2.06</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AX18" t="n">
         <v>22</v>
       </c>
       <c r="AY18" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BA18" t="n">
         <v>25</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BG18" t="n">
         <v>10</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BH22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,7 +793,7 @@
         <v>1.38</v>
       </c>
       <c r="R2" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S2" t="n">
         <v>1.93</v>
@@ -859,7 +859,7 @@
         <v>40</v>
       </c>
       <c r="AN2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO2" t="n">
         <v>9.800000000000001</v>
@@ -913,14 +913,14 @@
         <v>32</v>
       </c>
       <c r="BF2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G3" t="n">
         <v>3.3</v>
@@ -960,16 +960,16 @@
         <v>2.32</v>
       </c>
       <c r="I3" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -978,19 +978,19 @@
         <v>4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T3" t="n">
         <v>1.69</v>
@@ -999,7 +999,7 @@
         <v>2.34</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W3" t="n">
         <v>1.43</v>
@@ -1008,7 +1008,7 @@
         <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
         <v>16</v>
@@ -1044,7 +1044,7 @@
         <v>55</v>
       </c>
       <c r="AK3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL3" t="n">
         <v>42</v>
@@ -1068,7 +1068,7 @@
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT3" t="n">
         <v>12.5</v>
@@ -1092,19 +1092,19 @@
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC3" t="n">
         <v>10</v>
       </c>
       <c r="BD3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF3" t="n">
         <v>21</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -1160,10 +1160,10 @@
         <v>4.6</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
@@ -1172,10 +1172,10 @@
         <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
         <v>1.69</v>
@@ -1190,10 +1190,10 @@
         <v>1.87</v>
       </c>
       <c r="U4" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="V4" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="W4" t="n">
         <v>1.13</v>
@@ -1247,16 +1247,16 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AO4" t="n">
         <v>8</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AR4" t="n">
         <v>6.8</v>
@@ -1265,7 +1265,7 @@
         <v>9.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU4" t="n">
         <v>3.75</v>
@@ -1283,32 +1283,32 @@
         <v>4.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BA4" t="n">
         <v>4.6</v>
       </c>
       <c r="BB4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.9</v>
       </c>
       <c r="BD4" t="n">
         <v>4.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG4" t="n">
         <v>5.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.54</v>
       </c>
       <c r="G5" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="H5" t="n">
         <v>4.5</v>
@@ -1351,7 +1351,7 @@
         <v>6.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
         <v>5.1</v>
@@ -1363,7 +1363,7 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
@@ -1378,7 +1378,7 @@
         <v>1.61</v>
       </c>
       <c r="S5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
         <v>1.64</v>
@@ -1390,7 +1390,7 @@
         <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X5" t="n">
         <v>30</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -1536,16 +1536,16 @@
         <v>1.99</v>
       </c>
       <c r="G6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
         <v>3.4</v>
@@ -1563,7 +1563,7 @@
         <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q6" t="n">
         <v>2.22</v>
@@ -1620,7 +1620,7 @@
         <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ6" t="n">
         <v>24</v>
@@ -1629,7 +1629,7 @@
         <v>24</v>
       </c>
       <c r="AL6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM6" t="n">
         <v>170</v>
@@ -1647,7 +1647,7 @@
         <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS6" t="n">
         <v>14</v>
@@ -1668,7 +1668,7 @@
         <v>10</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
         <v>17.5</v>
@@ -1686,7 +1686,7 @@
         <v>12</v>
       </c>
       <c r="BE6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BF6" t="n">
         <v>16</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,179 +1912,179 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Sarmiento de Junin</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="G8" t="n">
-        <v>2.16</v>
+        <v>2.64</v>
       </c>
       <c r="H8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="J8" t="n">
-        <v>3.95</v>
+        <v>2.92</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="N8" t="n">
-        <v>5.2</v>
+        <v>2.24</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.56</v>
+        <v>1.13</v>
       </c>
       <c r="S8" t="n">
-        <v>2.48</v>
+        <v>7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.55</v>
+        <v>2.34</v>
       </c>
       <c r="U8" t="n">
-        <v>2.48</v>
+        <v>1.59</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>7.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AA8" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AB8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG8" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG8" t="n">
+      <c r="AH8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY8" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU8" t="n">
+      <c r="AZ8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD8" t="n">
         <v>8.4</v>
       </c>
-      <c r="AV8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>24</v>
-      </c>
       <c r="BE8" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BG8" t="n">
         <v>8.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.9</v>
+        <v>2.06</v>
       </c>
       <c r="G9" t="n">
-        <v>3.15</v>
+        <v>2.16</v>
       </c>
       <c r="H9" t="n">
-        <v>2.68</v>
+        <v>3.45</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>5.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.28</v>
+        <v>1.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>4.4</v>
+        <v>2.48</v>
       </c>
       <c r="T9" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="U9" t="n">
-        <v>1.97</v>
+        <v>2.48</v>
       </c>
       <c r="V9" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="W9" t="n">
-        <v>1.46</v>
+        <v>1.88</v>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="Z9" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AA9" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE9" t="n">
         <v>36</v>
       </c>
       <c r="AF9" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AG9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV9" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>11</v>
-      </c>
       <c r="AW9" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="AX9" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AY9" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BA9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF9" t="n">
         <v>9</v>
       </c>
-      <c r="BB9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BG9" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="I10" t="n">
-        <v>3.95</v>
+        <v>2.86</v>
       </c>
       <c r="J10" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M10" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>2.24</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="P10" t="n">
-        <v>1.43</v>
+        <v>1.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.34</v>
+        <v>1.9</v>
       </c>
       <c r="U10" t="n">
-        <v>1.59</v>
+        <v>1.97</v>
       </c>
       <c r="V10" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="W10" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="X10" t="n">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA10" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
         <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AF10" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>32</v>
+        <v>19.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AK10" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AL10" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="AN10" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AO10" t="n">
-        <v>140</v>
+        <v>36</v>
       </c>
       <c r="AP10" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AY10" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BD10" t="n">
         <v>8.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -2506,10 +2506,10 @@
         <v>2.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
         <v>4.5</v>
@@ -2527,7 +2527,7 @@
         <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="O11" t="n">
         <v>1.56</v>
@@ -2536,7 +2536,7 @@
         <v>1.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R11" t="n">
         <v>1.2</v>
@@ -2548,13 +2548,13 @@
         <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="V11" t="n">
         <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="X11" t="n">
         <v>9.199999999999999</v>
@@ -2602,13 +2602,13 @@
         <v>70</v>
       </c>
       <c r="AM11" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AN11" t="n">
         <v>32</v>
       </c>
       <c r="AO11" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP11" t="n">
         <v>7.6</v>
@@ -2620,7 +2620,7 @@
         <v>6.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT11" t="n">
         <v>5.8</v>
@@ -2632,10 +2632,10 @@
         <v>5.9</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
         <v>7.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11" t="n">
         <v>6.6</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H12" t="n">
         <v>4.1</v>
@@ -2727,7 +2727,7 @@
         <v>1.42</v>
       </c>
       <c r="P12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q12" t="n">
         <v>2.26</v>
@@ -2736,7 +2736,7 @@
         <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T12" t="n">
         <v>1.96</v>
@@ -2748,7 +2748,7 @@
         <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X12" t="n">
         <v>11.5</v>
@@ -2778,7 +2778,7 @@
         <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH12" t="n">
         <v>23</v>
@@ -2811,28 +2811,28 @@
         <v>10.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT12" t="n">
         <v>6.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX12" t="n">
         <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
         <v>18.5</v>
@@ -2841,26 +2841,26 @@
         <v>60</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
         <v>21</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF12" t="n">
         <v>16</v>
       </c>
       <c r="BG12" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="G14" t="n">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="P14" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="S14" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="V14" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="W14" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="X14" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,184 +3265,184 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.89</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.08</v>
+        <v>3.3</v>
       </c>
       <c r="H15" t="n">
-        <v>4.4</v>
+        <v>2.48</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>2.64</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.46</v>
+        <v>2.16</v>
       </c>
       <c r="R15" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="U15" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="V15" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="W15" t="n">
-        <v>1.92</v>
+        <v>1.43</v>
       </c>
       <c r="X15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y15" t="n">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>48</v>
+        <v>16.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AC15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV15" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD15" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.68</v>
-      </c>
       <c r="AW15" t="n">
-        <v>2.96</v>
+        <v>7.4</v>
       </c>
       <c r="AX15" t="n">
-        <v>2.46</v>
+        <v>18</v>
       </c>
       <c r="AY15" t="n">
-        <v>2.46</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.72</v>
+        <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.96</v>
+        <v>8.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>2.72</v>
+        <v>8.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.74</v>
+        <v>8</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.84</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.96</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.96</v>
+        <v>21</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3</v>
+        <v>1.59</v>
       </c>
       <c r="H16" t="n">
-        <v>2.48</v>
+        <v>7</v>
       </c>
       <c r="I16" t="n">
-        <v>2.66</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="K16" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S16" t="n">
         <v>3.1</v>
       </c>
-      <c r="O16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.1</v>
-      </c>
       <c r="T16" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U16" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="V16" t="n">
-        <v>1.6</v>
+        <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>1.43</v>
+        <v>2.68</v>
       </c>
       <c r="X16" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP16" t="n">
         <v>14</v>
       </c>
-      <c r="Y16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC16" t="n">
+      <c r="AQ16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF16" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>8</v>
-      </c>
       <c r="BG16" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,179 +3658,179 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="G17" t="n">
-        <v>1.59</v>
+        <v>2.52</v>
       </c>
       <c r="H17" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="I17" t="n">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="N17" t="n">
-        <v>3.95</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>2.04</v>
+        <v>1.52</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.81</v>
+        <v>2.56</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="V17" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>2.68</v>
+        <v>1.66</v>
       </c>
       <c r="X17" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Y17" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AA17" t="n">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AF17" t="n">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="AG17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AH17" t="n">
         <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AK17" t="n">
-        <v>16.5</v>
+        <v>36</v>
       </c>
       <c r="AL17" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AM17" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="AN17" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="AO17" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AP17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV17" t="n">
         <v>14</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR17" t="n">
+      <c r="AW17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX17" t="n">
         <v>12</v>
       </c>
-      <c r="AS17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT17" t="n">
+      <c r="AY17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC17" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX17" t="n">
+      <c r="BD17" t="n">
         <v>8.4</v>
       </c>
-      <c r="AY17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>32</v>
-      </c>
       <c r="BE17" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF17" t="n">
         <v>7.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -3864,16 +3864,16 @@
         <v>4.3</v>
       </c>
       <c r="G18" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="I18" t="n">
         <v>2.02</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K18" t="n">
         <v>3.75</v>
@@ -3903,7 +3903,7 @@
         <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
         <v>1.78</v>
@@ -3912,7 +3912,7 @@
         <v>1.98</v>
       </c>
       <c r="W18" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -3927,7 +3927,7 @@
         <v>30</v>
       </c>
       <c r="AB18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC18" t="n">
         <v>11</v>
@@ -3978,10 +3978,10 @@
         <v>7.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.34</v>
+        <v>16.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.6</v>
+        <v>2.26</v>
       </c>
       <c r="AU18" t="n">
         <v>2.06</v>
@@ -3990,7 +3990,7 @@
         <v>2.16</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AX18" t="n">
         <v>22</v>
@@ -4005,7 +4005,7 @@
         <v>25</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BC18" t="n">
         <v>2.48</v>
@@ -4014,17 +4014,17 @@
         <v>2.48</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BF18" t="n">
         <v>2.54</v>
       </c>
       <c r="BG18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,589 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SE Palmeiras</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Gremio</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-01 01:28:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X21" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-01 01:28:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X22" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH22"/>
+  <dimension ref="A1:BH23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G2" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I2" t="n">
         <v>2.58</v>
@@ -808,7 +808,7 @@
         <v>1.63</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X2" t="n">
         <v>36</v>
@@ -817,7 +817,7 @@
         <v>24</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA2" t="n">
         <v>40</v>
@@ -865,7 +865,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ2" t="n">
         <v>20</v>
@@ -886,10 +886,10 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY2" t="n">
         <v>12.5</v>
@@ -907,7 +907,7 @@
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE2" t="n">
         <v>32</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G3" t="n">
         <v>3.3</v>
@@ -960,22 +960,22 @@
         <v>2.32</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.26</v>
@@ -993,13 +993,13 @@
         <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U3" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W3" t="n">
         <v>1.43</v>
@@ -1023,7 +1023,7 @@
         <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE3" t="n">
         <v>24</v>
@@ -1041,7 +1041,7 @@
         <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
         <v>34</v>
@@ -1068,7 +1068,7 @@
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
         <v>12.5</v>
@@ -1095,26 +1095,26 @@
         <v>10</v>
       </c>
       <c r="BB3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
         <v>10</v>
       </c>
       <c r="BD3" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>21</v>
+        <v>9.6</v>
       </c>
       <c r="BG3" t="n">
         <v>14</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -1145,67 +1145,67 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6.4</v>
+        <v>1.09</v>
       </c>
       <c r="G4" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
         <v>1.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="O4" t="n">
         <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
         <v>1.69</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="T4" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U4" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="V4" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
         <v>950</v>
       </c>
       <c r="Y4" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA4" t="n">
         <v>970</v>
@@ -1217,13 +1217,13 @@
         <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
         <v>970</v>
       </c>
       <c r="AF4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AG4" t="n">
         <v>950</v>
@@ -1244,78 +1244,78 @@
         <v>110</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN4" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AO4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AQ4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG4" t="n">
         <v>3.65</v>
       </c>
-      <c r="AR4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Slovakian 2 Liga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Zlate Moravce</t>
+          <t>Tampere Utd</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lokomotiva Zvolen</t>
+          <t>FC Jazz</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I5" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="K5" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="R5" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="T5" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W5" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="X5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Slovakian 2 Liga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Zlate Moravce</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Lokomotiva Zvolen</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.99</v>
+        <v>1.59</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K6" t="n">
         <v>5.1</v>
       </c>
-      <c r="J6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>1.71</v>
+        <v>2.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.22</v>
+        <v>1.48</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="S6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X6" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV6" t="n">
         <v>4.3</v>
       </c>
-      <c r="T6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="X6" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>17</v>
-      </c>
       <c r="AW6" t="n">
-        <v>13</v>
+        <v>4.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>17.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>20</v>
+        <v>4.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>12</v>
+        <v>4.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>14</v>
+        <v>4.9</v>
       </c>
       <c r="BF6" t="n">
-        <v>16</v>
+        <v>3.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>13.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CSA Steaua Bucuresti</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>1.09</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>1.36</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.3</v>
+        <v>2.28</v>
       </c>
       <c r="R7" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>1.05</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.97</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>CSA Steaua Bucuresti</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>2.92</v>
+        <v>1.09</v>
       </c>
       <c r="K8" t="n">
-        <v>3.15</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.24</v>
+        <v>1.36</v>
       </c>
       <c r="O8" t="n">
-        <v>1.71</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>1.05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.34</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.59</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Sarmiento de Junin</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="G9" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="H9" t="n">
         <v>3.45</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>2.86</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="N9" t="n">
-        <v>5.2</v>
+        <v>2.18</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.56</v>
+        <v>1.13</v>
       </c>
       <c r="S9" t="n">
-        <v>2.48</v>
+        <v>7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.55</v>
+        <v>2.42</v>
       </c>
       <c r="U9" t="n">
-        <v>2.48</v>
+        <v>1.61</v>
       </c>
       <c r="V9" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W9" t="n">
-        <v>1.88</v>
+        <v>1.61</v>
       </c>
       <c r="X9" t="n">
-        <v>23</v>
+        <v>7.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="Z9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AA9" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AB9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG9" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11</v>
-      </c>
       <c r="AH9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV9" t="n">
         <v>15</v>
       </c>
-      <c r="AI9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT9" t="n">
+      <c r="AW9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX9" t="n">
         <v>12</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD9" t="n">
         <v>8.4</v>
       </c>
-      <c r="AV9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>24</v>
-      </c>
       <c r="BE9" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BF9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="G10" t="n">
-        <v>3.05</v>
+        <v>2.14</v>
       </c>
       <c r="H10" t="n">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="I10" t="n">
-        <v>2.86</v>
+        <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>1.72</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="S10" t="n">
-        <v>4.4</v>
+        <v>2.48</v>
       </c>
       <c r="T10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.9</v>
       </c>
-      <c r="U10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.49</v>
-      </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="Z10" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AA10" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AB10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN10" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG10" t="n">
+      <c r="AO10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV10" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV10" t="n">
+      <c r="AW10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE10" t="n">
         <v>11</v>
       </c>
-      <c r="AW10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BF10" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,156 +2489,156 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.04</v>
+        <v>2.76</v>
       </c>
       <c r="G11" t="n">
-        <v>2.26</v>
+        <v>3.05</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>2.84</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="P11" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="U11" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="X11" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="AA11" t="n">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="AB11" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="AF11" t="n">
         <v>970</v>
       </c>
       <c r="AG11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH11" t="n">
         <v>970</v>
       </c>
-      <c r="AH11" t="n">
-        <v>950</v>
-      </c>
       <c r="AI11" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AK11" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AL11" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>280</v>
+        <v>150</v>
       </c>
       <c r="AN11" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AO11" t="n">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="AP11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS11" t="n">
         <v>7.6</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>8</v>
-      </c>
       <c r="AT11" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.9</v>
+        <v>15.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
         <v>6.4</v>
@@ -2647,33 +2647,33 @@
         <v>7.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF11" t="n">
         <v>7.4</v>
       </c>
-      <c r="BE11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG11" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zaragoza</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="P12" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.26</v>
+        <v>2.68</v>
       </c>
       <c r="R12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.28</v>
       </c>
-      <c r="S12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.27</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="X12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y12" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y12" t="n">
-        <v>13.5</v>
-      </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA12" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AB12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>18.5</v>
+        <v>950</v>
       </c>
       <c r="AE12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL12" t="n">
         <v>70</v>
       </c>
-      <c r="AF12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>50</v>
-      </c>
       <c r="AM12" t="n">
-        <v>170</v>
+        <v>280</v>
       </c>
       <c r="AN12" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AO12" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="AR12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD12" t="n">
         <v>7.4</v>
       </c>
-      <c r="AS12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT12" t="n">
+      <c r="BE12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF12" t="n">
         <v>6.6</v>
       </c>
-      <c r="AU12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD12" t="n">
+      <c r="BG12" t="n">
         <v>8</v>
       </c>
-      <c r="BE12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2.26</v>
       </c>
-      <c r="G13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="R13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S13" t="n">
         <v>4.3</v>
       </c>
-      <c r="J13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.78</v>
+        <v>2.26</v>
       </c>
       <c r="G14" t="n">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="H14" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="J14" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.26</v>
+        <v>2.74</v>
       </c>
       <c r="R14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,184 +3265,184 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>1.82</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3</v>
+        <v>1.98</v>
       </c>
       <c r="H15" t="n">
-        <v>2.48</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>2.64</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
         <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="P15" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="T15" t="n">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="U15" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="V15" t="n">
-        <v>1.61</v>
+        <v>1.24</v>
       </c>
       <c r="W15" t="n">
-        <v>1.43</v>
+        <v>2.02</v>
       </c>
       <c r="X15" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.5</v>
+        <v>42</v>
       </c>
       <c r="AA15" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="AE15" t="n">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="AF15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC15" t="n">
         <v>21</v>
       </c>
-      <c r="AG15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ15" t="n">
+      <c r="BD15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG15" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AR15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>21</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>1.59</v>
+        <v>3.3</v>
       </c>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>2.44</v>
       </c>
       <c r="I16" t="n">
-        <v>7.4</v>
+        <v>2.64</v>
       </c>
       <c r="J16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S16" t="n">
         <v>4.2</v>
       </c>
-      <c r="K16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.1</v>
-      </c>
       <c r="T16" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U16" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="V16" t="n">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
       <c r="W16" t="n">
-        <v>2.68</v>
+        <v>1.43</v>
       </c>
       <c r="X16" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z16" t="n">
         <v>16</v>
       </c>
-      <c r="Y16" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>60</v>
-      </c>
       <c r="AA16" t="n">
-        <v>190</v>
+        <v>40</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>27</v>
+        <v>12.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="AF16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT16" t="n">
         <v>9.4</v>
       </c>
-      <c r="AG16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK16" t="n">
+      <c r="AU16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>16.5</v>
       </c>
-      <c r="AL16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>20</v>
-      </c>
       <c r="BA16" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="BB16" t="n">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD16" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BE16" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG16" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.38</v>
+        <v>1.56</v>
       </c>
       <c r="G17" t="n">
-        <v>2.52</v>
+        <v>1.58</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M17" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>3.95</v>
       </c>
       <c r="O17" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="P17" t="n">
-        <v>1.52</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.56</v>
+        <v>1.81</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="V17" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="W17" t="n">
-        <v>1.66</v>
+        <v>2.72</v>
       </c>
       <c r="X17" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="Z17" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="AA17" t="n">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="AB17" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>17.5</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AF17" t="n">
-        <v>15</v>
+        <v>9.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AH17" t="n">
         <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ17" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="AK17" t="n">
-        <v>36</v>
+        <v>16.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AM17" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="AN17" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="AO17" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AP17" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU17" t="n">
         <v>8.6</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AV17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>20</v>
       </c>
-      <c r="AS17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>19</v>
-      </c>
       <c r="BA17" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BC17" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BE17" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BF17" t="n">
         <v>7.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.3</v>
+        <v>2.36</v>
       </c>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>2.52</v>
       </c>
       <c r="H18" t="n">
-        <v>1.91</v>
+        <v>3.6</v>
       </c>
       <c r="I18" t="n">
-        <v>2.02</v>
+        <v>3.95</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="N18" t="n">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="O18" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="P18" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.06</v>
+        <v>2.56</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V18" t="n">
-        <v>1.98</v>
+        <v>1.34</v>
       </c>
       <c r="W18" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y18" t="n">
         <v>11</v>
       </c>
       <c r="Z18" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AA18" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="AB18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR18" t="n">
         <v>20</v>
       </c>
-      <c r="AC18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>95</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AS18" t="n">
-        <v>16.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.26</v>
+        <v>6.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.06</v>
+        <v>6</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.16</v>
+        <v>14</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.36</v>
+        <v>8.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
-        <v>2.32</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.34</v>
+        <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.56</v>
+        <v>7.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.48</v>
+        <v>7.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.48</v>
+        <v>8.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.56</v>
+        <v>9.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.54</v>
+        <v>7.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Talleres</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="G19" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="H19" t="n">
-        <v>2.82</v>
+        <v>1.87</v>
       </c>
       <c r="I19" t="n">
-        <v>3.05</v>
+        <v>2.02</v>
       </c>
       <c r="J19" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P19" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>2.04</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,36 +4235,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Talleres</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.54</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>1.58</v>
+        <v>3.2</v>
       </c>
       <c r="H20" t="n">
-        <v>6.8</v>
+        <v>2.84</v>
       </c>
       <c r="I20" t="n">
-        <v>7.8</v>
+        <v>3.15</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2</v>
+        <v>2.82</v>
       </c>
       <c r="K20" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4.2</v>
+        <v>1.54</v>
       </c>
       <c r="G21" t="n">
-        <v>4.8</v>
+        <v>1.58</v>
       </c>
       <c r="H21" t="n">
-        <v>1.94</v>
+        <v>6.8</v>
       </c>
       <c r="I21" t="n">
-        <v>2.06</v>
+        <v>7.8</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="K21" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.22</v>
+        <v>1.87</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,184 +4623,378 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="H22" t="n">
-        <v>3.7</v>
+        <v>1.98</v>
       </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>2.12</v>
       </c>
       <c r="J22" t="n">
         <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M22" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="P22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T22" t="n">
         <v>1.99</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="U22" t="n">
         <v>1.89</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.2</v>
-      </c>
       <c r="V22" t="n">
-        <v>1.32</v>
+        <v>1.89</v>
       </c>
       <c r="W22" t="n">
-        <v>1.76</v>
+        <v>1.27</v>
       </c>
       <c r="X22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y22" t="n">
-        <v>16</v>
+        <v>7.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="AA22" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AC22" t="n">
         <v>8</v>
       </c>
       <c r="AD22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-01 03:35:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH23" t="n">
         <v>16.5</v>
       </c>
-      <c r="AE22" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH22" t="n">
+      <c r="AI23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
         <v>970</v>
       </c>
-      <c r="AI22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO22" t="n">
+      <c r="AO23" t="n">
         <v>42</v>
       </c>
-      <c r="AP22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ22" t="n">
+      <c r="AP23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF23" t="n">
         <v>13.5</v>
       </c>
-      <c r="AR22" t="n">
+      <c r="BG23" t="n">
         <v>8.4</v>
       </c>
-      <c r="AS22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>2026-04-01 01:28:12</t>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH23"/>
+  <dimension ref="A1:BH31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="H2" t="n">
         <v>2.54</v>
@@ -787,43 +787,43 @@
         <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R2" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="S2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="U2" t="n">
         <v>3.35</v>
       </c>
       <c r="V2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB2" t="n">
         <v>27</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>24</v>
       </c>
       <c r="AC2" t="n">
         <v>12</v>
@@ -835,7 +835,7 @@
         <v>23</v>
       </c>
       <c r="AF2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
         <v>14.5</v>
@@ -847,80 +847,80 @@
         <v>25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
         <v>25</v>
       </c>
       <c r="AM2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AN2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
         <v>30</v>
       </c>
       <c r="AQ2" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV2" t="n">
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>22</v>
+        <v>7.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BE2" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>3.2</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H3" t="n">
         <v>2.32</v>
@@ -969,7 +969,7 @@
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -978,25 +978,25 @@
         <v>4.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="R3" t="n">
         <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="U3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V3" t="n">
         <v>1.72</v>
@@ -1005,116 +1005,116 @@
         <v>1.43</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>15.5</v>
+        <v>1.63</v>
       </c>
       <c r="AQ3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AT3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS3" t="n">
+      <c r="AU3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY3" t="n">
         <v>10</v>
       </c>
-      <c r="AT3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>1.78</v>
       </c>
       <c r="BA3" t="n">
-        <v>10</v>
+        <v>1.54</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>1.54</v>
       </c>
       <c r="BC3" t="n">
-        <v>10</v>
+        <v>1.54</v>
       </c>
       <c r="BD3" t="n">
-        <v>34</v>
+        <v>1.54</v>
       </c>
       <c r="BE3" t="n">
-        <v>11.5</v>
+        <v>1.54</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.6</v>
+        <v>1.34</v>
       </c>
       <c r="BG3" t="n">
-        <v>14</v>
+        <v>1.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -1145,58 +1145,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5</v>
+        <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9</v>
+        <v>1.24</v>
       </c>
       <c r="O4" t="n">
         <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.69</v>
+        <v>1.24</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>2.58</v>
+        <v>1.23</v>
       </c>
       <c r="T4" t="n">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
         <v>950</v>
@@ -1205,10 +1205,10 @@
         <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
         <v>950</v>
@@ -1223,7 +1223,7 @@
         <v>970</v>
       </c>
       <c r="AF4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
         <v>950</v>
@@ -1232,90 +1232,90 @@
         <v>950</v>
       </c>
       <c r="AI4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.9</v>
+        <v>1.14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4</v>
+        <v>1.21</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.1</v>
+        <v>1.21</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.6</v>
+        <v>1.21</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.3</v>
+        <v>1.17</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.2</v>
+        <v>1.21</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.1</v>
+        <v>1.21</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.8</v>
+        <v>1.21</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>1.15</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.2</v>
+        <v>1.17</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.2</v>
+        <v>1.16</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.1</v>
+        <v>1.11</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.9</v>
+        <v>1.21</v>
       </c>
       <c r="BC4" t="n">
-        <v>6</v>
+        <v>1.15</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>1.15</v>
       </c>
       <c r="BE4" t="n">
-        <v>6</v>
+        <v>1.15</v>
       </c>
       <c r="BF4" t="n">
-        <v>6</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.65</v>
+        <v>1.21</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1330,67 +1330,67 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tampere Utd</t>
+          <t>KAC 1909</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Jazz</t>
+          <t>VST Volkermarkt</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
-        <v>1.76</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
-        <v>5.7</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="R5" t="n">
-        <v>1.69</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>2.06</v>
+        <v>1.14</v>
       </c>
       <c r="T5" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1441,7 +1441,7 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1495,21 +1495,21 @@
         <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Slovakian 2 Liga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Zlate Moravce</t>
+          <t>Tampere Utd</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lokomotiva Zvolen</t>
+          <t>FC Jazz</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.59</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>2.24</v>
       </c>
       <c r="I6" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>2.24</v>
       </c>
       <c r="K6" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="P6" t="n">
-        <v>2.34</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="R6" t="n">
-        <v>1.61</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2</v>
+        <v>1.14</v>
       </c>
       <c r="T6" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="X6" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Slovakian 2 Liga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Zlate Moravce</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Lokomotiva Zvolen</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1.02</v>
       </c>
       <c r="G7" t="n">
-        <v>2.08</v>
+        <v>600</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6</v>
+        <v>1.02</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>1.22</v>
       </c>
       <c r="O7" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="P7" t="n">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.28</v>
+        <v>1.16</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="S7" t="n">
-        <v>4.3</v>
+        <v>1.17</v>
       </c>
       <c r="T7" t="n">
-        <v>1.97</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AS7" t="n">
         <v>1.25</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="X7" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AT7" t="n">
-        <v>6.8</v>
+        <v>1.25</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>1.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>17</v>
+        <v>1.19</v>
       </c>
       <c r="AW7" t="n">
-        <v>11.5</v>
+        <v>1.23</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>1.25</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.800000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="AZ7" t="n">
-        <v>18</v>
+        <v>1.25</v>
       </c>
       <c r="BA7" t="n">
-        <v>11</v>
+        <v>1.25</v>
       </c>
       <c r="BB7" t="n">
-        <v>21</v>
+        <v>1.25</v>
       </c>
       <c r="BC7" t="n">
-        <v>21</v>
+        <v>1.25</v>
       </c>
       <c r="BD7" t="n">
-        <v>11.5</v>
+        <v>1.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>11.5</v>
+        <v>1.25</v>
       </c>
       <c r="BF7" t="n">
-        <v>16</v>
+        <v>1.25</v>
       </c>
       <c r="BG7" t="n">
-        <v>11</v>
+        <v>1.22</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,33 +1907,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CSA Steaua Bucuresti</t>
+          <t>SAK Klagenfurt</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>Kottmannsdorf</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -1945,28 +1945,28 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="R8" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
@@ -2029,52 +2029,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,184 +2101,184 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Asco Atsv Wolfsberg</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Atus Ferlach</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="G9" t="n">
-        <v>2.62</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="I9" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>2.86</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
-        <v>3.15</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>2.18</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.71</v>
+        <v>1.09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>1.09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>1.09</v>
       </c>
       <c r="T9" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="X10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BD10" t="n">
         <v>3.7</v>
       </c>
-      <c r="J10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="X10" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>24</v>
-      </c>
       <c r="BE10" t="n">
-        <v>11</v>
+        <v>3.9</v>
       </c>
       <c r="BF10" t="n">
-        <v>9</v>
+        <v>5.9</v>
       </c>
       <c r="BG10" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>CSA Steaua Bucuresti</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>2.84</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>1.09</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>1.36</v>
       </c>
       <c r="O11" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="S11" t="n">
-        <v>4.4</v>
+        <v>1.05</v>
       </c>
       <c r="T11" t="n">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.96</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,184 +2683,184 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Sarmiento de Junin</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.04</v>
+        <v>1.06</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3</v>
+        <v>990</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>4.5</v>
+        <v>990</v>
       </c>
       <c r="J12" t="n">
-        <v>3.15</v>
+        <v>1.07</v>
       </c>
       <c r="K12" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R12" t="n">
         <v>1.12</v>
       </c>
-      <c r="N12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.2</v>
-      </c>
       <c r="S12" t="n">
-        <v>5.6</v>
+        <v>1.05</v>
       </c>
       <c r="T12" t="n">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.66</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zaragoza</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="G13" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="n">
         <v>4.1</v>
       </c>
-      <c r="I13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.35</v>
-      </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="P13" t="n">
-        <v>1.67</v>
+        <v>2.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.26</v>
+        <v>1.54</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.51</v>
       </c>
       <c r="S13" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="U13" t="n">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="V13" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X13" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC13" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AD13" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AF13" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AG13" t="n">
         <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AJ13" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AL13" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AM13" t="n">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="AN13" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AO13" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="AP13" t="n">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AU13" t="n">
-        <v>7</v>
+        <v>3.65</v>
       </c>
       <c r="AV13" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY13" t="n">
         <v>10</v>
       </c>
-      <c r="AY13" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>60</v>
+        <v>4.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BD13" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="BF13" t="n">
-        <v>16</v>
+        <v>3.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.6</v>
+        <v>16.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,184 +3071,184 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="G14" t="n">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="H14" t="n">
-        <v>3.65</v>
+        <v>2.48</v>
       </c>
       <c r="I14" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="J14" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.74</v>
+        <v>2.16</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.82</v>
+        <v>1.29</v>
       </c>
       <c r="G15" t="n">
-        <v>1.98</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>1.09</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>2.68</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="P15" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.38</v>
+        <v>1.51</v>
       </c>
       <c r="R15" t="n">
         <v>1.2</v>
       </c>
       <c r="S15" t="n">
-        <v>4.8</v>
+        <v>1.52</v>
       </c>
       <c r="T15" t="n">
-        <v>2.14</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
         <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,108 +3459,108 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="G16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
         <v>3.3</v>
       </c>
-      <c r="H16" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.35</v>
-      </c>
       <c r="K16" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P16" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R16" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>1.05</v>
       </c>
       <c r="T16" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U16" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="V16" t="n">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="W16" t="n">
-        <v>1.43</v>
+        <v>1.78</v>
       </c>
       <c r="X16" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
         <v>11</v>
       </c>
-      <c r="AC16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>14</v>
-      </c>
       <c r="AH16" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
         <v>1000</v>
@@ -3572,78 +3572,78 @@
         <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
         <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>10</v>
+        <v>1.11</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>1.11</v>
       </c>
       <c r="AR16" t="n">
-        <v>14</v>
+        <v>1.11</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>1.11</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.4</v>
+        <v>1.11</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV16" t="n">
-        <v>10.5</v>
+        <v>1.11</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.6</v>
+        <v>1.11</v>
       </c>
       <c r="AX16" t="n">
-        <v>18</v>
+        <v>1.11</v>
       </c>
       <c r="AY16" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16.5</v>
+        <v>1.11</v>
       </c>
       <c r="BA16" t="n">
-        <v>40</v>
+        <v>1.11</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.6</v>
+        <v>1.11</v>
       </c>
       <c r="BC16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="BD16" t="n">
-        <v>46</v>
+        <v>1.11</v>
       </c>
       <c r="BE16" t="n">
-        <v>9.4</v>
+        <v>1.11</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="BG16" t="n">
-        <v>21</v>
+        <v>1.11</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="G17" t="n">
-        <v>1.58</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>1.44</v>
       </c>
       <c r="I17" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="K17" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="L17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.04</v>
+        <v>1.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>2.52</v>
+        <v>110</v>
       </c>
       <c r="H18" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>3.95</v>
+        <v>110</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>1.03</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>2.62</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="P18" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.56</v>
+        <v>1.33</v>
       </c>
       <c r="R18" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>5.3</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Juticalpa</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>2.02</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="K19" t="n">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.04</v>
+        <v>1.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
         <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AS19" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV19" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW19" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY19" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,184 +4235,184 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Talleres</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>1.26</v>
       </c>
       <c r="G20" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>3.15</v>
+        <v>5.1</v>
       </c>
       <c r="J20" t="n">
-        <v>2.82</v>
+        <v>1.26</v>
       </c>
       <c r="K20" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P20" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>1.47</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -4429,184 +4429,184 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.54</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
-        <v>1.58</v>
+        <v>3.7</v>
       </c>
       <c r="H21" t="n">
-        <v>6.8</v>
+        <v>2.26</v>
       </c>
       <c r="I21" t="n">
-        <v>7.8</v>
+        <v>2.62</v>
       </c>
       <c r="J21" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.87</v>
+        <v>1.37</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -4623,378 +4623,1930 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>1.55</v>
       </c>
       <c r="G22" t="n">
-        <v>4.6</v>
+        <v>1.58</v>
       </c>
       <c r="H22" t="n">
-        <v>1.98</v>
+        <v>6.8</v>
       </c>
       <c r="I22" t="n">
-        <v>2.12</v>
+        <v>7.8</v>
       </c>
       <c r="J22" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>2.06</v>
       </c>
       <c r="O22" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="P22" t="n">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2</v>
+        <v>1.27</v>
       </c>
       <c r="T22" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="U22" t="n">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.89</v>
+        <v>1.15</v>
       </c>
       <c r="W22" t="n">
-        <v>1.27</v>
+        <v>2.72</v>
       </c>
       <c r="X22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="Z22" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="AA22" t="n">
-        <v>26</v>
+        <v>280</v>
       </c>
       <c r="AB22" t="n">
-        <v>13</v>
+        <v>950</v>
       </c>
       <c r="AC22" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="AE22" t="n">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="AF22" t="n">
-        <v>34</v>
+        <v>9.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="AH22" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AI22" t="n">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="AJ22" t="n">
-        <v>130</v>
+        <v>15</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM22" t="n">
         <v>180</v>
       </c>
       <c r="AN22" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="AO22" t="n">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.6</v>
+        <v>16.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AT22" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV22" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AW22" t="n">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="AX22" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>15.5</v>
+        <v>8.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA22" t="n">
-        <v>38</v>
+        <v>7.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BF22" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>17.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sao Bernardo</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Operario PR</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-01 05:42:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Deportivo La Guaira</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Carabobo FC</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G24" t="n">
+        <v>110</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K24" t="n">
+        <v>950</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-04-01 05:42:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>20:15:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CD Olimpia</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Lobos UPNFM</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K25" t="n">
+        <v>950</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-04-01 05:42:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Jaguares de Cordoba</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-04-01 05:42:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Talleres</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-01 05:42:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SE Palmeiras</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Gremio</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-01 05:42:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G29" t="n">
+        <v>600</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-01 05:42:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>22:30:00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Once Caldas</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Ind Medellin</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="H23" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="F30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
         <v>1.06</v>
       </c>
-      <c r="N23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="N30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-01 05:42:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Real Espana</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>CD Marathon</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K31" t="n">
+        <v>950</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O31" t="n">
         <v>1.39</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="X23" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>2026-04-01 03:35:09</t>
+      <c r="P31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH31"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,13 +760,13 @@
         <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H2" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="I2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J2" t="n">
         <v>4.3</v>
@@ -781,7 +781,7 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="O2" t="n">
         <v>1.12</v>
@@ -790,137 +790,137 @@
         <v>3.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R2" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="S2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="T2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="U2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X2" t="n">
         <v>34</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AC2" t="n">
         <v>12</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG2" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
         <v>13.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL2" t="n">
         <v>25</v>
       </c>
       <c r="AM2" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AN2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU2" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>10</v>
       </c>
       <c r="AV2" t="n">
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BC2" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BE2" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="BF2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG2" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BG2" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -954,22 +954,22 @@
         <v>3.2</v>
       </c>
       <c r="G3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H3" t="n">
         <v>2.32</v>
       </c>
       <c r="I3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J3" t="n">
         <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -978,143 +978,143 @@
         <v>4.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="U3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W3" t="n">
         <v>1.43</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.63</v>
+        <v>15.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.78</v>
+        <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.54</v>
+        <v>10.5</v>
       </c>
       <c r="AT3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AU3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.54</v>
-      </c>
       <c r="BB3" t="n">
-        <v>1.54</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.54</v>
+        <v>10.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.54</v>
+        <v>10.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.54</v>
+        <v>12.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.34</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.6</v>
+        <v>14</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1131,60 +1131,60 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Skive</t>
+          <t>VSK Aarhus FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Vendsyssel FF</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.02</v>
+        <v>2.92</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02</v>
+        <v>1.96</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>2.96</v>
       </c>
       <c r="O4" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>1.23</v>
+        <v>2.48</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1193,46 +1193,46 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="X4" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
         <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
@@ -1250,72 +1250,72 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KAC 1909</t>
+          <t>Skive</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VST Volkermarkt</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>1.55</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="K5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X5" t="n">
         <v>950</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1000</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ5" t="n">
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN5" t="n">
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tampere Utd</t>
+          <t>Roskilde</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Jazz</t>
+          <t>Naestved</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="G6" t="n">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="H6" t="n">
-        <v>2.24</v>
+        <v>3.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
-        <v>2.24</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.14</v>
+        <v>1.98</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>1.14</v>
+        <v>2.86</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>2.22</v>
+        <v>1.69</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1641,52 +1641,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Slovakian 2 Liga</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,60 +1713,60 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Zlate Moravce</t>
+          <t>Brabrand</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lokomotiva Zvolen</t>
+          <t>FC Helsingor</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>600</v>
+        <v>5.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>1.87</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>2.84</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.22</v>
+        <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.22</v>
+        <v>1.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="R7" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.17</v>
+        <v>3.05</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -1775,122 +1775,122 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1907,17 +1907,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAK Klagenfurt</t>
+          <t>KAC 1909</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kottmannsdorf</t>
+          <t>VST Volkermarkt</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1942,31 +1942,31 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O8" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="R8" t="n">
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
@@ -2029,52 +2029,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,72 +2101,72 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Asco Atsv Wolfsberg</t>
+          <t>Tampere Utd</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atus Ferlach</t>
+          <t>FC Jazz</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.67</v>
       </c>
       <c r="H9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.25</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2217,75 +2217,75 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Slovakian 2 Liga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Zlate Moravce</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Lokomotiva Zvolen</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="G10" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>1.64</v>
+        <v>2.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>4.3</v>
+        <v>2.16</v>
       </c>
       <c r="T10" t="n">
-        <v>1.88</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.82</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>950</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Z10" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AA10" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
         <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>19.5</v>
+        <v>950</v>
       </c>
       <c r="AE10" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF10" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AK10" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AL10" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AM10" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
         <v>970</v>
       </c>
       <c r="AO10" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.4</v>
+        <v>1.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.55</v>
+        <v>1.22</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.85</v>
+        <v>1.25</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.1</v>
+        <v>1.25</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>1.25</v>
       </c>
       <c r="AV10" t="n">
-        <v>16.5</v>
+        <v>1.19</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.8</v>
+        <v>1.23</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.9</v>
+        <v>1.25</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.800000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6.2</v>
+        <v>1.25</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.8</v>
+        <v>1.25</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.6</v>
+        <v>1.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.4</v>
+        <v>1.25</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>3.9</v>
+        <v>1.25</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.9</v>
+        <v>1.25</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.8</v>
+        <v>1.22</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,33 +2489,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CSA Steaua Bucuresti</t>
+          <t>SAK Klagenfurt</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>Kottmannsdorf</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
         <v>950</v>
@@ -2527,22 +2527,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="P11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="R11" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,33 +2683,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Asco Atsv Wolfsberg</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Atus Ferlach</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="G12" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="I12" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
         <v>950</v>
@@ -2724,19 +2724,19 @@
         <v>1.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="P12" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="R12" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="K13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S13" t="n">
         <v>4.3</v>
       </c>
-      <c r="L13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.3</v>
-      </c>
       <c r="T13" t="n">
-        <v>1.51</v>
+        <v>1.98</v>
       </c>
       <c r="U13" t="n">
-        <v>2.36</v>
+        <v>1.89</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="W13" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="X13" t="n">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA13" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AB13" t="n">
-        <v>17.5</v>
+        <v>7.8</v>
       </c>
       <c r="AC13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF13" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>20</v>
       </c>
       <c r="AG13" t="n">
         <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AL13" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AM13" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AN13" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AO13" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.3</v>
+        <v>9.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.6</v>
+        <v>28</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.65</v>
+        <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AY13" t="n">
         <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.6</v>
+        <v>21</v>
       </c>
       <c r="BC13" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.9</v>
+        <v>12.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.8</v>
+        <v>16.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,78 +3071,78 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>CSA Steaua Bucuresti</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>1.09</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>2.84</v>
+        <v>1.36</v>
       </c>
       <c r="O14" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.16</v>
+        <v>1.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4</v>
+        <v>1.05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.86</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3151,10 +3151,10 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3193,69 +3193,69 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,184 +3265,184 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Sarmiento de Junin</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.29</v>
+        <v>2.46</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="J15" t="n">
-        <v>1.09</v>
+        <v>2.86</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>2.18</v>
       </c>
       <c r="O15" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.51</v>
+        <v>3.15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="S15" t="n">
-        <v>1.52</v>
+        <v>7.2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="V15" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zaragoza</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="G16" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="I16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O16" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>1.62</v>
+        <v>2.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.14</v>
+        <v>1.61</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="S16" t="n">
-        <v>1.05</v>
+        <v>2.44</v>
       </c>
       <c r="T16" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="U16" t="n">
-        <v>1.8</v>
+        <v>2.52</v>
       </c>
       <c r="V16" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="W16" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.11</v>
+        <v>19.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.11</v>
+        <v>17</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.11</v>
+        <v>25</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.11</v>
+        <v>50</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.11</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.11</v>
+        <v>13.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.11</v>
+        <v>30</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.11</v>
+        <v>14</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.11</v>
+        <v>13.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.11</v>
+        <v>32</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.11</v>
+        <v>22</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.11</v>
+        <v>16.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.11</v>
+        <v>24</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.11</v>
+        <v>10.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.11</v>
+        <v>19</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O17" t="n">
         <v>1.44</v>
       </c>
-      <c r="G17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
       <c r="P17" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="G18" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE18" t="n">
         <v>110</v>
       </c>
-      <c r="H18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I18" t="n">
-        <v>110</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="AF18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH18" t="n">
         <v>950</v>
       </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>50</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Genesis Huracan</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Juticalpa</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N19" t="n">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.2</v>
+        <v>2.32</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.26</v>
+        <v>2.36</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="J20" t="n">
-        <v>1.26</v>
+        <v>2.94</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.47</v>
+        <v>2.74</v>
       </c>
       <c r="R20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,72 +4429,72 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
+        <v>1.76</v>
       </c>
       <c r="G21" t="n">
-        <v>3.7</v>
+        <v>2.08</v>
       </c>
       <c r="H21" t="n">
-        <v>2.26</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>2.62</v>
+        <v>5.7</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K21" t="n">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="O21" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.37</v>
+        <v>1.9</v>
       </c>
       <c r="R21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>1.36</v>
+        <v>2.58</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>1.84</v>
       </c>
       <c r="U21" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="V21" t="n">
-        <v>1.61</v>
+        <v>1.21</v>
       </c>
       <c r="W21" t="n">
-        <v>1.37</v>
+        <v>1.93</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Juticalpa</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
-        <v>1.58</v>
+        <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="I22" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="K22" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>2.06</v>
+        <v>1.28</v>
       </c>
       <c r="O22" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>1.28</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="R22" t="n">
         <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
         <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
         <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,72 +4817,72 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.36</v>
+        <v>1.91</v>
       </c>
       <c r="G23" t="n">
-        <v>2.52</v>
+        <v>1.97</v>
       </c>
       <c r="H23" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="I23" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N23" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.25</v>
       </c>
-      <c r="O23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.34</v>
-      </c>
       <c r="W23" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="G24" t="n">
-        <v>110</v>
+        <v>3.35</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="J24" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="K24" t="n">
-        <v>950</v>
+        <v>3.4</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="P24" t="n">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.02</v>
+        <v>2.18</v>
       </c>
       <c r="R24" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S24" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.03</v>
+        <v>48</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CD Olimpia</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lobos UPNFM</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>1.58</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="J25" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>1.25</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.14</v>
+        <v>1.86</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>1.14</v>
+        <v>3.15</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>46</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>55</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.02</v>
+        <v>2.36</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="I26" t="n">
-        <v>2.02</v>
+        <v>3.85</v>
       </c>
       <c r="J26" t="n">
-        <v>1.09</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="N26" t="n">
-        <v>1.24</v>
+        <v>2.68</v>
       </c>
       <c r="O26" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V26" t="n">
         <v>1.35</v>
       </c>
-      <c r="P26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.98</v>
-      </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Talleres</t>
+          <t>Deportivo La Guaira</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="G27" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X27" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT27" t="n">
         <v>3.2</v>
       </c>
-      <c r="H27" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:15:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>CD Olimpia</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Lobos UPNFM</t>
         </is>
       </c>
       <c r="F28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K28" t="n">
+        <v>950</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T28" t="n">
         <v>1.11</v>
       </c>
-      <c r="G28" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.83</v>
+        <v>4.3</v>
       </c>
       <c r="G29" t="n">
-        <v>600</v>
+        <v>5.1</v>
       </c>
       <c r="H29" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="I29" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="J29" t="n">
-        <v>1.64</v>
+        <v>3.5</v>
       </c>
       <c r="K29" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
         <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="O29" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="P29" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.4</v>
+        <v>2.08</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="T29" t="n">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="U29" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="V29" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,378 +6175,960 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Talleres</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="J30" t="n">
-        <v>1.09</v>
+        <v>2.86</v>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.26</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SE Palmeiras</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Gremio</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-01 07:50:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-01 07:50:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-04-01 07:50:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Honduras Liga Nacional</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>22:30:00</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Real Espana</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>CD Marathon</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="F34" t="n">
         <v>1.04</v>
       </c>
-      <c r="G31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H31" t="n">
+      <c r="G34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H34" t="n">
         <v>1.04</v>
       </c>
-      <c r="I31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J31" t="n">
+      <c r="I34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J34" t="n">
         <v>1.03</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K34" t="n">
         <v>950</v>
       </c>
-      <c r="L31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O31" t="n">
+      <c r="L34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O34" t="n">
         <v>1.39</v>
       </c>
-      <c r="P31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R31" t="n">
+      <c r="P34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R34" t="n">
         <v>1.18</v>
       </c>
-      <c r="S31" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
+      <c r="S34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AQ34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AR31" t="n">
+      <c r="AR34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AS31" t="n">
+      <c r="AS34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AT31" t="n">
+      <c r="AT34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AU34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AV31" t="n">
+      <c r="AV34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AW31" t="n">
+      <c r="AW34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AX31" t="n">
+      <c r="AX34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AY31" t="n">
+      <c r="AY34" t="n">
         <v>1.03</v>
       </c>
-      <c r="AZ31" t="n">
+      <c r="AZ34" t="n">
         <v>1.03</v>
       </c>
-      <c r="BA31" t="n">
+      <c r="BA34" t="n">
         <v>1.03</v>
       </c>
-      <c r="BB31" t="n">
+      <c r="BB34" t="n">
         <v>1.03</v>
       </c>
-      <c r="BC31" t="n">
+      <c r="BC34" t="n">
         <v>1.03</v>
       </c>
-      <c r="BD31" t="n">
+      <c r="BD34" t="n">
         <v>1.03</v>
       </c>
-      <c r="BE31" t="n">
+      <c r="BE34" t="n">
         <v>1.03</v>
       </c>
-      <c r="BF31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH31" t="inlineStr">
-        <is>
-          <t>2026-04-01 05:42:54</t>
+      <c r="BF34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH34"/>
+  <dimension ref="A1:BH36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G2" t="n">
         <v>2.6</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2.64</v>
       </c>
       <c r="H2" t="n">
         <v>2.58</v>
@@ -772,7 +772,7 @@
         <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.2</v>
@@ -781,22 +781,22 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="S2" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="T2" t="n">
         <v>1.4</v>
@@ -808,25 +808,25 @@
         <v>1.62</v>
       </c>
       <c r="W2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X2" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="Y2" t="n">
         <v>24</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AA2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB2" t="n">
         <v>24</v>
       </c>
       <c r="AC2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD2" t="n">
         <v>13.5</v>
@@ -844,7 +844,7 @@
         <v>13.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ2" t="n">
         <v>40</v>
@@ -856,13 +856,13 @@
         <v>25</v>
       </c>
       <c r="AM2" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AN2" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AP2" t="n">
         <v>32</v>
@@ -871,16 +871,16 @@
         <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT2" t="n">
         <v>21</v>
       </c>
       <c r="AU2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="n">
         <v>12</v>
@@ -889,38 +889,38 @@
         <v>20</v>
       </c>
       <c r="AX2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD2" t="n">
         <v>22</v>
       </c>
       <c r="BE2" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BF2" t="n">
         <v>9</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="H3" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
         <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -999,10 +999,10 @@
         <v>2.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="W3" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="X3" t="n">
         <v>21</v>
@@ -1011,13 +1011,13 @@
         <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB3" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AC3" t="n">
         <v>8.4</v>
@@ -1026,13 +1026,13 @@
         <v>11.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH3" t="n">
         <v>16.5</v>
@@ -1041,10 +1041,10 @@
         <v>34</v>
       </c>
       <c r="AJ3" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AK3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AL3" t="n">
         <v>42</v>
@@ -1053,10 +1053,10 @@
         <v>85</v>
       </c>
       <c r="AN3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO3" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AP3" t="n">
         <v>15.5</v>
@@ -1065,56 +1065,56 @@
         <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="AT3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV3" t="n">
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AX3" t="n">
         <v>20</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BB3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE3" t="n">
         <v>11</v>
       </c>
-      <c r="BC3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BF3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="I4" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="J4" t="n">
         <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,22 +1169,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="Q4" t="n">
         <v>1.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1193,10 +1193,10 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -1339,61 +1339,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="I5" t="n">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="J5" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U5" t="n">
         <v>2.24</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.89</v>
-      </c>
       <c r="V5" t="n">
-        <v>2.84</v>
+        <v>2.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="X5" t="n">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
@@ -1408,7 +1408,7 @@
         <v>950</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
         <v>970</v>
@@ -1417,92 +1417,92 @@
         <v>970</v>
       </c>
       <c r="AF5" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="AG5" t="n">
         <v>950</v>
       </c>
       <c r="AH5" t="n">
-        <v>950</v>
+        <v>18</v>
       </c>
       <c r="AI5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ5" t="n">
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AL5" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO5" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.7</v>
+        <v>9.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AS5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX5" t="n">
         <v>4.4</v>
       </c>
-      <c r="AT5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA5" t="n">
         <v>4.3</v>
       </c>
-      <c r="AV5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5</v>
-      </c>
       <c r="BB5" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.1</v>
+        <v>9.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="G6" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="H6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" t="n">
         <v>3.2</v>
       </c>
-      <c r="I6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.1</v>
-      </c>
       <c r="K6" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1557,22 +1557,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1581,10 +1581,10 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="G7" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="H7" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="I7" t="n">
-        <v>2.54</v>
+        <v>2.96</v>
       </c>
       <c r="J7" t="n">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="K7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,22 +1751,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.82</v>
+        <v>1.78</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
-        <v>3.05</v>
+        <v>2.18</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -1775,10 +1775,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,72 +1907,72 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>10:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KAC 1909</t>
+          <t>Al-Jndal</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VST Volkermarkt</t>
+          <t>Jeddah Club</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="H8" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>2.74</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>5.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.28</v>
+        <v>2.36</v>
       </c>
       <c r="O8" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.14</v>
+        <v>2.84</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,31 +2106,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tampere Utd</t>
+          <t>KAC 1909</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Jazz</t>
+          <t>VST Volkermarkt</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="G9" t="n">
-        <v>1.67</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,34 +2139,34 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>5.1</v>
+        <v>1.28</v>
       </c>
       <c r="O9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P9" t="n">
-        <v>2.58</v>
+        <v>1.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.45</v>
+        <v>1.14</v>
       </c>
       <c r="R9" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>2.04</v>
+        <v>1.14</v>
       </c>
       <c r="T9" t="n">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2217,75 +2217,75 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Slovakian 2 Liga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Zlate Moravce</t>
+          <t>Tampere Utd</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lokomotiva Zvolen</t>
+          <t>FC Jazz</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="G10" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="H10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT10" t="n">
         <v>4.3</v>
       </c>
-      <c r="I10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="AU10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV10" t="n">
         <v>4.9</v>
       </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="X10" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AW10" t="n">
-        <v>1.23</v>
+        <v>5.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.25</v>
+        <v>4.7</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.25</v>
+        <v>5.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.25</v>
+        <v>4.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.25</v>
+        <v>4.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.25</v>
+        <v>5.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.25</v>
+        <v>2.86</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.22</v>
+        <v>5.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>12:55:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAK Klagenfurt</t>
+          <t>Al Faisaly ( KSA )</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kottmannsdorf</t>
+          <t>Al Jubail</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>1.65</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2527,34 +2527,34 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.16</v>
+        <v>1.52</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>1.16</v>
+        <v>2.32</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Slovakian 2 Liga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Asco Atsv Wolfsberg</t>
+          <t>Zlate Moravce</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atus Ferlach</t>
+          <t>Lokomotiva Zvolen</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>1.8</v>
       </c>
       <c r="H12" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X12" t="n">
         <v>950</v>
       </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1000</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>SAK Klagenfurt</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Kottmannsdorf</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="G13" t="n">
-        <v>2.04</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="n">
-        <v>3.4</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N13" t="n">
         <v>1.1</v>
       </c>
-      <c r="N13" t="n">
-        <v>3.15</v>
-      </c>
       <c r="O13" t="n">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.3</v>
+        <v>1.16</v>
       </c>
       <c r="R13" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>4.3</v>
+        <v>1.16</v>
       </c>
       <c r="T13" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,33 +3071,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CSA Steaua Bucuresti</t>
+          <t>Asco Atsv Wolfsberg</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>Atus Ferlach</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
@@ -3109,22 +3109,22 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="P14" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="R14" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.64</v>
+        <v>2.06</v>
       </c>
       <c r="H15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K15" t="n">
         <v>3.4</v>
       </c>
-      <c r="I15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.05</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.18</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P15" t="n">
         <v>1.71</v>
       </c>
-      <c r="P15" t="n">
-        <v>1.39</v>
-      </c>
       <c r="Q15" t="n">
-        <v>3.15</v>
+        <v>2.28</v>
       </c>
       <c r="R15" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU15" t="n">
         <v>7.2</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>380</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW15" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AX15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD15" t="n">
         <v>12</v>
       </c>
-      <c r="AY15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE15" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.4</v>
+        <v>75</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,184 +3459,184 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>CSA Steaua Bucuresti</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.06</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>2.14</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>1.09</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L16" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>1.36</v>
       </c>
       <c r="O16" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.36</v>
+        <v>1.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="S16" t="n">
-        <v>2.44</v>
+        <v>1.05</v>
       </c>
       <c r="T16" t="n">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>2.52</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.88</v>
+        <v>2.08</v>
       </c>
       <c r="G17" t="n">
-        <v>3.05</v>
+        <v>2.12</v>
       </c>
       <c r="H17" t="n">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="J17" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M17" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="P17" t="n">
-        <v>1.72</v>
+        <v>2.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.26</v>
+        <v>1.62</v>
       </c>
       <c r="R17" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="S17" t="n">
-        <v>4.4</v>
+        <v>2.44</v>
       </c>
       <c r="T17" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="U17" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="X17" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="Y17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF17" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Z17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>42</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG17" t="n">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.04</v>
+        <v>2.9</v>
       </c>
       <c r="G18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q18" t="n">
         <v>2.24</v>
       </c>
-      <c r="H18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.68</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S18" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.24</v>
+        <v>1.94</v>
       </c>
       <c r="U18" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="X18" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z18" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="n">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AB18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="AF18" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AI18" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AJ18" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AK18" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AL18" t="n">
         <v>70</v>
       </c>
       <c r="AM18" t="n">
-        <v>280</v>
+        <v>160</v>
       </c>
       <c r="AN18" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AO18" t="n">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="AP18" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.7</v>
+        <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.2</v>
+        <v>24</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>19.5</v>
+        <v>42</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.5</v>
+        <v>27</v>
       </c>
       <c r="BD18" t="n">
-        <v>50</v>
+        <v>7.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zaragoza</t>
+          <t>Sarmiento de Junin</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="G19" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="I19" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="K19" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="N19" t="n">
-        <v>3.05</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="P19" t="n">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.32</v>
+        <v>3.15</v>
       </c>
       <c r="R19" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="S19" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="V19" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W19" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="X19" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z19" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AA19" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AC19" t="n">
         <v>7.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AF19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG19" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AI19" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AJ19" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AM19" t="n">
-        <v>170</v>
+        <v>380</v>
       </c>
       <c r="AN19" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="AO19" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AP19" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="AS19" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AV19" t="n">
         <v>15</v>
       </c>
       <c r="AW19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX19" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="BA19" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE19" t="n">
         <v>8.6</v>
       </c>
-      <c r="BC19" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BF19" t="n">
-        <v>18</v>
+        <v>7.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="G20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N20" t="n">
         <v>2.56</v>
       </c>
-      <c r="H20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P20" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I21" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="K21" t="n">
-        <v>5.8</v>
+        <v>3.55</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="O21" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="P21" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>2.58</v>
+        <v>4.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="U21" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="V21" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Genesis Huracan</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juticalpa</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
-        <v>1.03</v>
+        <v>2.94</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>3.25</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.28</v>
+        <v>1.51</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.19</v>
+        <v>2.74</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="G23" t="n">
-        <v>1.97</v>
+        <v>2.54</v>
       </c>
       <c r="H23" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N23" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="O23" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="R23" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S23" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="U23" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="V23" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="W23" t="n">
-        <v>2.02</v>
+        <v>1.64</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.1</v>
+        <v>1.76</v>
       </c>
       <c r="G24" t="n">
-        <v>3.35</v>
+        <v>2.04</v>
       </c>
       <c r="H24" t="n">
-        <v>2.46</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>2.62</v>
+        <v>5.6</v>
       </c>
       <c r="J24" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="P24" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="S24" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="T24" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="U24" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="V24" t="n">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>1.42</v>
+        <v>1.97</v>
       </c>
       <c r="X24" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Juticalpa</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.56</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>1.58</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="K25" t="n">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>1.29</v>
       </c>
       <c r="O25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P25" t="n">
         <v>1.29</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.06</v>
-      </c>
       <c r="Q25" t="n">
-        <v>1.86</v>
+        <v>1.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>3.15</v>
+        <v>1.05</v>
       </c>
       <c r="T25" t="n">
-        <v>1.95</v>
+        <v>1.11</v>
       </c>
       <c r="U25" t="n">
-        <v>1.95</v>
+        <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.36</v>
+        <v>1.91</v>
       </c>
       <c r="G26" t="n">
-        <v>2.52</v>
+        <v>1.99</v>
       </c>
       <c r="H26" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="I26" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O26" t="n">
         <v>1.51</v>
       </c>
       <c r="P26" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="R26" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="U26" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="V26" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="W26" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="X26" t="n">
         <v>10.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AA26" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AE26" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AF26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF26" t="n">
         <v>16.5</v>
       </c>
-      <c r="AG26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BG26" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="F27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q27" t="n">
         <v>2.2</v>
       </c>
-      <c r="G27" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="H27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.54</v>
-      </c>
       <c r="R27" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="T27" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U27" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V27" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="W27" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="X27" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC27" t="n">
         <v>9</v>
       </c>
-      <c r="Y27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ27" t="n">
         <v>8</v>
       </c>
-      <c r="AC27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AR27" t="n">
-        <v>4.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.2</v>
+        <v>9.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AW27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE27" t="n">
         <v>4.9</v>
       </c>
-      <c r="AX27" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB27" t="n">
+      <c r="BF27" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC27" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BG27" t="n">
-        <v>5.1</v>
+        <v>21</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CD Olimpia</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lobos UPNFM</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="G28" t="n">
-        <v>1000</v>
+        <v>1.58</v>
       </c>
       <c r="H28" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="I28" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="J28" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="K28" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>1.28</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="P28" t="n">
-        <v>1.28</v>
+        <v>2.06</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.14</v>
+        <v>1.86</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>1.14</v>
+        <v>3.15</v>
       </c>
       <c r="T28" t="n">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="U28" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Deportivo La Guaira</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4.3</v>
+        <v>2.22</v>
       </c>
       <c r="G29" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S29" t="n">
         <v>5.1</v>
       </c>
-      <c r="H29" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.7</v>
-      </c>
       <c r="T29" t="n">
-        <v>1.88</v>
+        <v>1.11</v>
       </c>
       <c r="U29" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="V29" t="n">
-        <v>1.98</v>
+        <v>1.28</v>
       </c>
       <c r="W29" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="X29" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>15.5</v>
+        <v>8</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD29" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR29" t="n">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AS29" t="n">
-        <v>19</v>
+        <v>5.4</v>
       </c>
       <c r="AT29" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU29" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>18.5</v>
+        <v>5.3</v>
       </c>
       <c r="AX29" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="AY29" t="n">
-        <v>15.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>17</v>
+        <v>4.7</v>
       </c>
       <c r="BA29" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="BC29" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="BD29" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="BE29" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BG29" t="n">
-        <v>13.5</v>
+        <v>5.4</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:15:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Talleres</t>
+          <t>CD Olimpia</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Lobos UPNFM</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="G30" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="I30" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="K30" t="n">
-        <v>3.05</v>
+        <v>950</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P30" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>1.14</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.53</v>
+        <v>4.3</v>
       </c>
       <c r="G31" t="n">
-        <v>1.58</v>
+        <v>4.9</v>
       </c>
       <c r="H31" t="n">
-        <v>6.8</v>
+        <v>1.92</v>
       </c>
       <c r="I31" t="n">
-        <v>8.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="K31" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V31" t="n">
         <v>2</v>
       </c>
-      <c r="Q31" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,191 +6563,191 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Talleres</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="G32" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="H32" t="n">
-        <v>1.96</v>
+        <v>2.88</v>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>2.96</v>
       </c>
       <c r="J32" t="n">
-        <v>3.45</v>
+        <v>2.92</v>
       </c>
       <c r="K32" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.22</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,378 +6757,766 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.14</v>
+        <v>1.53</v>
       </c>
       <c r="G33" t="n">
-        <v>2.26</v>
+        <v>1.58</v>
       </c>
       <c r="H33" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="I33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J33" t="n">
         <v>4.2</v>
       </c>
-      <c r="J33" t="n">
-        <v>3.35</v>
-      </c>
       <c r="K33" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R33" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:01:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X35" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:01:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Honduras Liga Nacional</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>22:30:00</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Real Espana</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>CD Marathon</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="F36" t="n">
         <v>1.04</v>
       </c>
-      <c r="G34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H34" t="n">
+      <c r="G36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H36" t="n">
         <v>1.04</v>
       </c>
-      <c r="I34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K34" t="n">
+      <c r="I36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K36" t="n">
         <v>950</v>
       </c>
-      <c r="L34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O34" t="n">
+      <c r="L36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O36" t="n">
         <v>1.39</v>
       </c>
-      <c r="P34" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="P36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Q36" t="n">
         <v>1.38</v>
       </c>
-      <c r="R34" t="n">
+      <c r="R36" t="n">
         <v>1.18</v>
       </c>
-      <c r="S34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T34" t="n">
+      <c r="S36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T36" t="n">
         <v>1.11</v>
       </c>
-      <c r="U34" t="n">
+      <c r="U36" t="n">
         <v>1.11</v>
       </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>2026-04-01 07:50:57</t>
+      <c r="V36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -760,16 +760,16 @@
         <v>2.56</v>
       </c>
       <c r="G2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H2" t="n">
         <v>2.6</v>
       </c>
-      <c r="H2" t="n">
-        <v>2.58</v>
-      </c>
       <c r="I2" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
         <v>4.5</v>
@@ -796,7 +796,7 @@
         <v>1.99</v>
       </c>
       <c r="S2" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="T2" t="n">
         <v>1.4</v>
@@ -805,19 +805,19 @@
         <v>3.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X2" t="n">
         <v>40</v>
       </c>
       <c r="Y2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA2" t="n">
         <v>42</v>
@@ -826,7 +826,7 @@
         <v>24</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD2" t="n">
         <v>13.5</v>
@@ -853,10 +853,10 @@
         <v>22</v>
       </c>
       <c r="AL2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AN2" t="n">
         <v>9.4</v>
@@ -865,7 +865,7 @@
         <v>10.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AQ2" t="n">
         <v>20</v>
@@ -874,13 +874,13 @@
         <v>23</v>
       </c>
       <c r="AS2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT2" t="n">
         <v>21</v>
       </c>
       <c r="AU2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV2" t="n">
         <v>12</v>
@@ -889,7 +889,7 @@
         <v>20</v>
       </c>
       <c r="AX2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY2" t="n">
         <v>12</v>
@@ -898,19 +898,19 @@
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB2" t="n">
         <v>34</v>
       </c>
       <c r="BC2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
         <v>22</v>
       </c>
       <c r="BE2" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BF2" t="n">
         <v>9</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
         <v>2.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
         <v>3.8</v>
@@ -1029,7 +1029,7 @@
         <v>23</v>
       </c>
       <c r="AF3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG3" t="n">
         <v>14.5</v>
@@ -1044,16 +1044,16 @@
         <v>70</v>
       </c>
       <c r="AK3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AM3" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO3" t="n">
         <v>15</v>
@@ -1068,7 +1068,7 @@
         <v>13.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AT3" t="n">
         <v>13.5</v>
@@ -1095,16 +1095,16 @@
         <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BD3" t="n">
         <v>9.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BF3" t="n">
         <v>8.6</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>4.5</v>
@@ -1160,13 +1160,13 @@
         <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -1184,7 +1184,7 @@
         <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="G5" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="H5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I5" t="n">
         <v>1.76</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.92</v>
       </c>
       <c r="J5" t="n">
         <v>3.6</v>
@@ -1363,43 +1363,43 @@
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="T5" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="U5" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="V5" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X5" t="n">
-        <v>17.5</v>
+        <v>950</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AA5" t="n">
         <v>970</v>
@@ -1408,7 +1408,7 @@
         <v>950</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
         <v>970</v>
@@ -1417,7 +1417,7 @@
         <v>970</v>
       </c>
       <c r="AF5" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AG5" t="n">
         <v>950</v>
@@ -1426,83 +1426,83 @@
         <v>18</v>
       </c>
       <c r="AI5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ5" t="n">
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN5" t="n">
         <v>85</v>
       </c>
-      <c r="AN5" t="n">
-        <v>65</v>
-      </c>
       <c r="AO5" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.6</v>
+        <v>4</v>
       </c>
       <c r="AQ5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.55</v>
+        <v>6.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AT5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>8</v>
+        <v>3.95</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -1533,58 +1533,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="G6" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -1727,58 +1727,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="G7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K7" t="n">
         <v>4.1</v>
       </c>
-      <c r="H7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="K7" t="n">
-        <v>6.4</v>
-      </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.78</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>1.78</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U7" t="n">
         <v>2.18</v>
       </c>
-      <c r="T7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.11</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="W7" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -1921,58 +1921,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="G8" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="J8" t="n">
         <v>2.74</v>
       </c>
       <c r="K8" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="O8" t="n">
         <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
@@ -2139,13 +2139,13 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O9" t="n">
         <v>1.14</v>
       </c>
       <c r="P9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q9" t="n">
         <v>1.14</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="G10" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="H10" t="n">
-        <v>1.09</v>
+        <v>5.8</v>
       </c>
       <c r="I10" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="K10" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,34 +2333,34 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="O10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.15</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.16</v>
-      </c>
       <c r="W10" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2399,7 +2399,7 @@
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
         <v>1000</v>
@@ -2423,40 +2423,40 @@
         <v>5.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT10" t="n">
         <v>4.3</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AV10" t="n">
         <v>4.9</v>
       </c>
       <c r="AW10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA10" t="n">
         <v>5.5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.4</v>
       </c>
       <c r="BB10" t="n">
         <v>4.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BD10" t="n">
         <v>4.9</v>
@@ -2465,14 +2465,14 @@
         <v>5.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.86</v>
+        <v>4</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -2506,19 +2506,19 @@
         <v>1.37</v>
       </c>
       <c r="G11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="H11" t="n">
         <v>5.5</v>
       </c>
       <c r="I11" t="n">
-        <v>140</v>
+        <v>990</v>
       </c>
       <c r="J11" t="n">
         <v>4.1</v>
       </c>
       <c r="K11" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2533,28 +2533,28 @@
         <v>1.19</v>
       </c>
       <c r="P11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
         <v>1.52</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
         <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
         <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
         <v>4.8</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
@@ -2930,7 +2930,7 @@
         <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -3282,10 +3282,10 @@
         <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
         <v>5</v>
@@ -3306,7 +3306,7 @@
         <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P15" t="n">
         <v>1.71</v>
@@ -3321,7 +3321,7 @@
         <v>4.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U15" t="n">
         <v>1.92</v>
@@ -3330,10 +3330,10 @@
         <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="X15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y15" t="n">
         <v>14.5</v>
@@ -3393,22 +3393,22 @@
         <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU15" t="n">
         <v>7.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
         <v>17.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB15" t="n">
         <v>21</v>
@@ -3432,7 +3432,7 @@
         <v>12</v>
       </c>
       <c r="BE15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF15" t="n">
         <v>16.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="G16" t="n">
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.09</v>
+        <v>1.46</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3512,7 +3512,7 @@
         <v>1.15</v>
       </c>
       <c r="S16" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G17" t="n">
         <v>2.12</v>
@@ -3697,7 +3697,7 @@
         <v>1.21</v>
       </c>
       <c r="P17" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
         <v>1.62</v>
@@ -3715,7 +3715,7 @@
         <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
         <v>1.89</v>
@@ -3727,19 +3727,19 @@
         <v>19.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA17" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE17" t="n">
         <v>36</v>
@@ -3751,7 +3751,7 @@
         <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI17" t="n">
         <v>40</v>
@@ -3766,7 +3766,7 @@
         <v>29</v>
       </c>
       <c r="AM17" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN17" t="n">
         <v>11</v>
@@ -3775,7 +3775,7 @@
         <v>26</v>
       </c>
       <c r="AP17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ17" t="n">
         <v>17</v>
@@ -3784,13 +3784,13 @@
         <v>25</v>
       </c>
       <c r="AS17" t="n">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="AT17" t="n">
         <v>12</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV17" t="n">
         <v>13.5</v>
@@ -3820,7 +3820,7 @@
         <v>24</v>
       </c>
       <c r="BE17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF17" t="n">
         <v>9.199999999999999</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
         <v>3.05</v>
       </c>
       <c r="H18" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I18" t="n">
         <v>2.8</v>
@@ -3876,10 +3876,10 @@
         <v>3.25</v>
       </c>
       <c r="K18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
@@ -3894,10 +3894,10 @@
         <v>1.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R18" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
         <v>4.4</v>
@@ -3921,7 +3921,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA18" t="n">
         <v>55</v>
@@ -3945,7 +3945,7 @@
         <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI18" t="n">
         <v>65</v>
@@ -3966,7 +3966,7 @@
         <v>50</v>
       </c>
       <c r="AO18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP18" t="n">
         <v>10</v>
@@ -3978,7 +3978,7 @@
         <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT18" t="n">
         <v>9</v>
@@ -3990,7 +3990,7 @@
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AX18" t="n">
         <v>16.5</v>
@@ -4002,7 +4002,7 @@
         <v>17.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.2</v>
+        <v>44</v>
       </c>
       <c r="BB18" t="n">
         <v>42</v>
@@ -4011,20 +4011,20 @@
         <v>27</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF18" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -4097,10 +4097,10 @@
         <v>7.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U19" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="V19" t="n">
         <v>1.35</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>2.04</v>
       </c>
       <c r="G20" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H20" t="n">
         <v>4.1</v>
@@ -4261,7 +4261,7 @@
         <v>4.5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K20" t="n">
         <v>3.5</v>
@@ -4270,37 +4270,37 @@
         <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q20" t="n">
         <v>2.56</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.68</v>
       </c>
       <c r="R20" t="n">
         <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U20" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="V20" t="n">
         <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="X20" t="n">
         <v>10.5</v>
@@ -4312,7 +4312,7 @@
         <v>34</v>
       </c>
       <c r="AA20" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB20" t="n">
         <v>7</v>
@@ -4324,7 +4324,7 @@
         <v>20</v>
       </c>
       <c r="AE20" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF20" t="n">
         <v>12</v>
@@ -4336,7 +4336,7 @@
         <v>950</v>
       </c>
       <c r="AI20" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ20" t="n">
         <v>29</v>
@@ -4348,13 +4348,13 @@
         <v>65</v>
       </c>
       <c r="AM20" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AN20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO20" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AP20" t="n">
         <v>7.6</v>
@@ -4363,25 +4363,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV20" t="n">
         <v>16</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY20" t="n">
         <v>10</v>
@@ -4390,29 +4390,29 @@
         <v>19.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB20" t="n">
         <v>19.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF20" t="n">
         <v>20</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -4449,13 +4449,13 @@
         <v>2.12</v>
       </c>
       <c r="H21" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I21" t="n">
         <v>4.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
         <v>3.55</v>
@@ -4476,7 +4476,7 @@
         <v>1.71</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R21" t="n">
         <v>1.26</v>
@@ -4515,7 +4515,7 @@
         <v>7.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AE21" t="n">
         <v>70</v>
@@ -4572,7 +4572,7 @@
         <v>15</v>
       </c>
       <c r="AW21" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="AX21" t="n">
         <v>10.5</v>
@@ -4584,10 +4584,10 @@
         <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>60</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="BC21" t="n">
         <v>21</v>
@@ -4599,14 +4599,14 @@
         <v>10.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BG21" t="n">
-        <v>10.5</v>
+        <v>60</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -4646,10 +4646,10 @@
         <v>3.5</v>
       </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J22" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="K22" t="n">
         <v>3.25</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -4873,13 +4873,13 @@
         <v>5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U23" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="V23" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W23" t="n">
         <v>1.64</v>
@@ -4888,13 +4888,13 @@
         <v>10.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z23" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA23" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB23" t="n">
         <v>8</v>
@@ -4903,13 +4903,13 @@
         <v>7.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE23" t="n">
         <v>60</v>
       </c>
       <c r="AF23" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG23" t="n">
         <v>13</v>
@@ -4927,13 +4927,13 @@
         <v>36</v>
       </c>
       <c r="AL23" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM23" t="n">
         <v>200</v>
       </c>
       <c r="AN23" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO23" t="n">
         <v>85</v>
@@ -4948,7 +4948,7 @@
         <v>20</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT23" t="n">
         <v>6.6</v>
@@ -4960,7 +4960,7 @@
         <v>13.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX23" t="n">
         <v>12</v>
@@ -4972,29 +4972,29 @@
         <v>19</v>
       </c>
       <c r="BA23" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB23" t="n">
-        <v>5.8</v>
+        <v>30</v>
       </c>
       <c r="BC23" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BD23" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE23" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.8</v>
+        <v>29</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -5025,170 +5025,170 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="G24" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I24" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
         <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P24" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="T24" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="U24" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W24" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -5252,13 +5252,13 @@
         <v>1.29</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="R25" t="n">
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="T25" t="n">
         <v>1.11</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="G26" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H26" t="n">
         <v>4.6</v>
@@ -5425,10 +5425,10 @@
         <v>5.1</v>
       </c>
       <c r="J26" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K26" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5458,13 +5458,13 @@
         <v>2.22</v>
       </c>
       <c r="U26" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V26" t="n">
         <v>1.25</v>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X26" t="n">
         <v>10.5</v>
@@ -5527,7 +5527,7 @@
         <v>11</v>
       </c>
       <c r="AR26" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="AS26" t="n">
         <v>8.4</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -5610,13 +5610,13 @@
         <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H27" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I27" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
         <v>3.35</v>
@@ -5625,7 +5625,7 @@
         <v>3.4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M27" t="n">
         <v>1.09</v>
@@ -5634,40 +5634,40 @@
         <v>3.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P27" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q27" t="n">
         <v>2.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="T27" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U27" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W27" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X27" t="n">
         <v>14</v>
       </c>
       <c r="Y27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z27" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA27" t="n">
         <v>46</v>
@@ -5676,22 +5676,22 @@
         <v>13</v>
       </c>
       <c r="AC27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF27" t="n">
         <v>26</v>
       </c>
       <c r="AG27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="n">
         <v>65</v>
@@ -5724,7 +5724,7 @@
         <v>13.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.6</v>
+        <v>32</v>
       </c>
       <c r="AT27" t="n">
         <v>9.4</v>
@@ -5733,13 +5733,13 @@
         <v>6.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>21</v>
+        <v>4.1</v>
       </c>
       <c r="AX27" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY27" t="n">
         <v>12</v>
@@ -5748,29 +5748,29 @@
         <v>17</v>
       </c>
       <c r="BA27" t="n">
-        <v>42</v>
+        <v>4.3</v>
       </c>
       <c r="BB27" t="n">
-        <v>48</v>
+        <v>4.3</v>
       </c>
       <c r="BC27" t="n">
-        <v>34</v>
+        <v>4.2</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BG27" t="n">
         <v>21</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -5804,10 +5804,10 @@
         <v>1.57</v>
       </c>
       <c r="G28" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H28" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I28" t="n">
         <v>7.4</v>
@@ -5828,31 +5828,31 @@
         <v>4.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P28" t="n">
         <v>2.06</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R28" t="n">
         <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T28" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="U28" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V28" t="n">
         <v>1.15</v>
       </c>
       <c r="W28" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="X28" t="n">
         <v>16</v>
@@ -5891,7 +5891,7 @@
         <v>110</v>
       </c>
       <c r="AJ28" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK28" t="n">
         <v>16.5</v>
@@ -5921,7 +5921,7 @@
         <v>46</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU28" t="n">
         <v>8.800000000000001</v>
@@ -5936,7 +5936,7 @@
         <v>8.4</v>
       </c>
       <c r="AY28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ28" t="n">
         <v>20</v>
@@ -5954,7 +5954,7 @@
         <v>30</v>
       </c>
       <c r="BE28" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="BF28" t="n">
         <v>7.8</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -6007,22 +6007,22 @@
         <v>4.5</v>
       </c>
       <c r="J29" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K29" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L29" t="n">
         <v>1.55</v>
       </c>
       <c r="M29" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N29" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="O29" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="P29" t="n">
         <v>1.5</v>
@@ -6034,13 +6034,13 @@
         <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="T29" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U29" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V29" t="n">
         <v>1.28</v>
@@ -6049,7 +6049,7 @@
         <v>1.65</v>
       </c>
       <c r="X29" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y29" t="n">
         <v>1000</v>
@@ -6061,10 +6061,10 @@
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
         <v>1000</v>
@@ -6109,10 +6109,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT29" t="n">
         <v>5.7</v>
@@ -6121,44 +6121,44 @@
         <v>5.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AY29" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BC29" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BD29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF29" t="n">
         <v>5.3</v>
       </c>
-      <c r="BE29" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>5</v>
-      </c>
       <c r="BG29" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -6213,13 +6213,13 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O30" t="n">
         <v>1.14</v>
       </c>
       <c r="P30" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q30" t="n">
         <v>1.14</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -6401,13 +6401,13 @@
         <v>3.75</v>
       </c>
       <c r="L31" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M31" t="n">
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O31" t="n">
         <v>1.37</v>
@@ -6428,7 +6428,7 @@
         <v>1.93</v>
       </c>
       <c r="U31" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="V31" t="n">
         <v>2</v>
@@ -6437,116 +6437,116 @@
         <v>1.26</v>
       </c>
       <c r="X31" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z31" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AA31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH31" t="n">
         <v>24</v>
       </c>
-      <c r="AB31" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>21</v>
-      </c>
       <c r="AI31" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AJ31" t="n">
         <v>130</v>
       </c>
       <c r="AK31" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AL31" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AM31" t="n">
         <v>150</v>
       </c>
       <c r="AN31" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AO31" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ31" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS31" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU31" t="n">
         <v>7</v>
       </c>
       <c r="AV31" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AW31" t="n">
         <v>18.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AZ31" t="n">
         <v>17</v>
       </c>
       <c r="BA31" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="BB31" t="n">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="BC31" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD31" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="BE31" t="n">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="BF31" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="BG31" t="n">
         <v>13.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G32" t="n">
         <v>3.2</v>
@@ -6586,7 +6586,7 @@
         <v>2.88</v>
       </c>
       <c r="I32" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J32" t="n">
         <v>2.92</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G33" t="n">
         <v>1.58</v>
@@ -6783,7 +6783,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K33" t="n">
         <v>4.7</v>
@@ -6804,7 +6804,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G34" t="n">
         <v>4.7</v>
       </c>
       <c r="H34" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="I34" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J34" t="n">
         <v>3.45</v>
       </c>
       <c r="K34" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L34" t="n">
         <v>1.4</v>
@@ -6992,28 +6992,28 @@
         <v>3.1</v>
       </c>
       <c r="O34" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P34" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q34" t="n">
         <v>2.22</v>
       </c>
       <c r="R34" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T34" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V34" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="W34" t="n">
         <v>1.27</v>
@@ -7049,7 +7049,7 @@
         <v>22</v>
       </c>
       <c r="AH34" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI34" t="n">
         <v>60</v>
@@ -7097,7 +7097,7 @@
         <v>21</v>
       </c>
       <c r="AX34" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AY34" t="n">
         <v>15.5</v>
@@ -7106,7 +7106,7 @@
         <v>19</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BB34" t="n">
         <v>4.2</v>
@@ -7115,20 +7115,20 @@
         <v>4.1</v>
       </c>
       <c r="BD34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE34" t="n">
         <v>4.2</v>
       </c>
-      <c r="BE34" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BF34" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG34" t="n">
         <v>14</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -7162,19 +7162,19 @@
         <v>2.14</v>
       </c>
       <c r="G35" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H35" t="n">
         <v>3.7</v>
       </c>
       <c r="I35" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>3.35</v>
       </c>
       <c r="K35" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7198,7 +7198,7 @@
         <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T35" t="n">
         <v>1.71</v>
@@ -7210,7 +7210,7 @@
         <v>1.32</v>
       </c>
       <c r="W35" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X35" t="n">
         <v>17.5</v>
@@ -7228,7 +7228,7 @@
         <v>12</v>
       </c>
       <c r="AC35" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD35" t="n">
         <v>18.5</v>
@@ -7261,10 +7261,10 @@
         <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO35" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP35" t="n">
         <v>13</v>
@@ -7282,22 +7282,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU35" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AV35" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.8</v>
+        <v>32</v>
       </c>
       <c r="AX35" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ35" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BA35" t="n">
         <v>4.9</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
         <v>1000</v>
       </c>
       <c r="J36" t="n">
-        <v>1.09</v>
+        <v>1.53</v>
       </c>
       <c r="K36" t="n">
         <v>950</v>
@@ -7374,16 +7374,16 @@
         <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N36" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="O36" t="n">
         <v>1.39</v>
       </c>
       <c r="P36" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Q36" t="n">
         <v>1.38</v>
@@ -7392,7 +7392,7 @@
         <v>1.18</v>
       </c>
       <c r="S36" t="n">
-        <v>1.38</v>
+        <v>1.05</v>
       </c>
       <c r="T36" t="n">
         <v>1.11</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH36"/>
+  <dimension ref="A1:BH37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,7 +760,7 @@
         <v>2.56</v>
       </c>
       <c r="G2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H2" t="n">
         <v>2.6</v>
@@ -769,37 +769,37 @@
         <v>2.62</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K2" t="n">
         <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="R2" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="S2" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="U2" t="n">
         <v>3.4</v>
@@ -808,25 +808,25 @@
         <v>1.61</v>
       </c>
       <c r="W2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Y2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Z2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA2" t="n">
         <v>42</v>
       </c>
       <c r="AB2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD2" t="n">
         <v>13.5</v>
@@ -844,7 +844,7 @@
         <v>13.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ2" t="n">
         <v>40</v>
@@ -856,31 +856,31 @@
         <v>24</v>
       </c>
       <c r="AM2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AQ2" t="n">
         <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS2" t="n">
         <v>36</v>
       </c>
       <c r="AT2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="n">
         <v>12</v>
@@ -889,38 +889,38 @@
         <v>20</v>
       </c>
       <c r="AX2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BF2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H3" t="n">
         <v>2.24</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="J3" t="n">
         <v>3.75</v>
@@ -975,7 +975,7 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.26</v>
@@ -993,13 +993,13 @@
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U3" t="n">
         <v>2.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="W3" t="n">
         <v>1.4</v>
@@ -1011,7 +1011,7 @@
         <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
         <v>29</v>
@@ -1023,7 +1023,7 @@
         <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
         <v>23</v>
@@ -1044,10 +1044,10 @@
         <v>70</v>
       </c>
       <c r="AK3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1077,13 +1077,13 @@
         <v>7.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3" t="n">
         <v>19.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -1092,29 +1092,29 @@
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
-        <v>9.4</v>
+        <v>30</v>
       </c>
       <c r="BD3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.6</v>
+        <v>24</v>
       </c>
       <c r="BG3" t="n">
         <v>13</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>1.97</v>
       </c>
       <c r="I4" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J4" t="n">
         <v>3.2</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="G5" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I5" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
         <v>4.2</v>
@@ -1360,7 +1360,7 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
         <v>4.6</v>
@@ -1372,7 +1372,7 @@
         <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="R5" t="n">
         <v>1.45</v>
@@ -1387,10 +1387,10 @@
         <v>2.1</v>
       </c>
       <c r="V5" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="W5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X5" t="n">
         <v>950</v>
@@ -1408,7 +1408,7 @@
         <v>950</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
         <v>970</v>
@@ -1417,7 +1417,7 @@
         <v>970</v>
       </c>
       <c r="AF5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG5" t="n">
         <v>950</v>
@@ -1432,77 +1432,77 @@
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AL5" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AO5" t="n">
         <v>970</v>
       </c>
       <c r="AP5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU5" t="n">
         <v>4</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS5" t="n">
+      <c r="AV5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG5" t="n">
         <v>3.95</v>
       </c>
-      <c r="AT5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
@@ -1533,28 +1533,28 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="G6" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
         <v>2.96</v>
@@ -1563,7 +1563,7 @@
         <v>1.43</v>
       </c>
       <c r="P6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q6" t="n">
         <v>2.1</v>
@@ -1581,10 +1581,10 @@
         <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W6" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1602,7 +1602,7 @@
         <v>8.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1647,22 +1647,22 @@
         <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX6" t="n">
         <v>8.6</v>
@@ -1671,32 +1671,32 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BA6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE6" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>5</v>
-      </c>
       <c r="BF6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         <v>2.74</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.39</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,31 +2106,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KAC 1909</t>
+          <t>Tampere Utd</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VST Volkermarkt</t>
+          <t>FC Jazz</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.49</v>
       </c>
       <c r="H9" t="n">
-        <v>1.02</v>
+        <v>6.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,34 +2139,34 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3</v>
+        <v>2.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="S9" t="n">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2217,75 +2217,75 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,31 +2300,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tampere Utd</t>
+          <t>KAC 1909</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Jazz</t>
+          <t>VST Volkermarkt</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.41</v>
+        <v>1.02</v>
       </c>
       <c r="G10" t="n">
-        <v>1.51</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>5.8</v>
+        <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>4.9</v>
+        <v>1.09</v>
       </c>
       <c r="K10" t="n">
-        <v>7.4</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,34 +2333,34 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.14</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>1.92</v>
+        <v>1.14</v>
       </c>
       <c r="T10" t="n">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>2.28</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2411,68 +2411,68 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I11" t="n">
-        <v>990</v>
+        <v>24</v>
       </c>
       <c r="J11" t="n">
         <v>4.1</v>
@@ -2527,7 +2527,7 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
         <v>1.19</v>
@@ -2536,13 +2536,13 @@
         <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -2551,10 +2551,10 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H15" t="n">
         <v>4.8</v>
@@ -3303,10 +3303,10 @@
         <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P15" t="n">
         <v>1.71</v>
@@ -3330,7 +3330,7 @@
         <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X15" t="n">
         <v>10.5</v>
@@ -3360,7 +3360,7 @@
         <v>11.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
         <v>21</v>
@@ -3381,10 +3381,10 @@
         <v>150</v>
       </c>
       <c r="AN15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO15" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AP15" t="n">
         <v>9.4</v>
@@ -3393,16 +3393,16 @@
         <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>29</v>
+        <v>11.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
         <v>17.5</v>
@@ -3417,32 +3417,32 @@
         <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB15" t="n">
         <v>21</v>
       </c>
       <c r="BC15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD15" t="n">
         <v>12</v>
       </c>
       <c r="BE15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF15" t="n">
         <v>16.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.46</v>
+        <v>1.1</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,184 +3653,184 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:35:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>Al-Zulfi SC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Al-Anwar Club</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="G17" t="n">
-        <v>2.12</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="I17" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L17" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>5.1</v>
+        <v>1.25</v>
       </c>
       <c r="O17" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="T17" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G18" t="n">
         <v>3.05</v>
       </c>
       <c r="H18" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="J18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K18" t="n">
         <v>3.4</v>
@@ -3882,13 +3882,13 @@
         <v>1.5</v>
       </c>
       <c r="M18" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N18" t="n">
         <v>3.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P18" t="n">
         <v>1.71</v>
@@ -3909,16 +3909,16 @@
         <v>1.98</v>
       </c>
       <c r="V18" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W18" t="n">
         <v>1.48</v>
       </c>
       <c r="X18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z18" t="n">
         <v>20</v>
@@ -3930,7 +3930,7 @@
         <v>10</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD18" t="n">
         <v>14.5</v>
@@ -3942,7 +3942,7 @@
         <v>22</v>
       </c>
       <c r="AG18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH18" t="n">
         <v>22</v>
@@ -3972,13 +3972,13 @@
         <v>10</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR18" t="n">
         <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT18" t="n">
         <v>9</v>
@@ -3990,7 +3990,7 @@
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>29</v>
+        <v>6.6</v>
       </c>
       <c r="AX18" t="n">
         <v>16.5</v>
@@ -4002,36 +4002,36 @@
         <v>17.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="BB18" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="BC18" t="n">
         <v>27</v>
       </c>
       <c r="BD18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>34</v>
+        <v>6.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.46</v>
+        <v>2.04</v>
       </c>
       <c r="G19" t="n">
-        <v>2.62</v>
+        <v>2.12</v>
       </c>
       <c r="H19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I19" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J19" t="n">
-        <v>2.86</v>
+        <v>3.95</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.71</v>
+        <v>1.21</v>
       </c>
       <c r="P19" t="n">
-        <v>1.39</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.15</v>
+        <v>1.62</v>
       </c>
       <c r="R19" t="n">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="S19" t="n">
-        <v>7.2</v>
+        <v>2.44</v>
       </c>
       <c r="T19" t="n">
-        <v>2.42</v>
+        <v>1.58</v>
       </c>
       <c r="U19" t="n">
-        <v>1.59</v>
+        <v>2.48</v>
       </c>
       <c r="V19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W19" t="n">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="X19" t="n">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="Y19" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Z19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR19" t="n">
         <v>25</v>
       </c>
-      <c r="AA19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>380</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>20</v>
-      </c>
       <c r="AS19" t="n">
-        <v>8.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="AX19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY19" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BC19" t="n">
-        <v>36</v>
+        <v>16.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.4</v>
+        <v>22</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Sarmiento de Junin</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.04</v>
+        <v>2.44</v>
       </c>
       <c r="G20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N20" t="n">
         <v>2.2</v>
       </c>
-      <c r="H20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.62</v>
-      </c>
       <c r="O20" t="n">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="P20" t="n">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="U20" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="X20" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="Z20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH20" t="n">
         <v>34</v>
       </c>
-      <c r="AA20" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>950</v>
-      </c>
       <c r="AI20" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL20" t="n">
         <v>110</v>
       </c>
-      <c r="AJ20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL20" t="n">
+      <c r="AM20" t="n">
+        <v>380</v>
+      </c>
+      <c r="AN20" t="n">
         <v>65</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>28</v>
       </c>
       <c r="AO20" t="n">
         <v>150</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="AS20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF20" t="n">
         <v>7.8</v>
       </c>
-      <c r="AT20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>20</v>
-      </c>
       <c r="BG20" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zaragoza</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G21" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="H21" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K21" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>2.58</v>
       </c>
       <c r="O21" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="P21" t="n">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="S21" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="V21" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W21" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK21" t="n">
         <v>32</v>
       </c>
-      <c r="AA21" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="AL21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS21" t="n">
         <v>7.8</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AT21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG21" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>60</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="G22" t="n">
-        <v>2.56</v>
+        <v>2.12</v>
       </c>
       <c r="H22" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="I22" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="J22" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P22" t="n">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>2.4</v>
       </c>
       <c r="G23" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="H23" t="n">
         <v>3.5</v>
       </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.56</v>
+        <v>2.92</v>
       </c>
       <c r="R23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,141 +5011,141 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.85</v>
+        <v>2.42</v>
       </c>
       <c r="G24" t="n">
-        <v>1.98</v>
+        <v>2.54</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="O24" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.35</v>
       </c>
-      <c r="P24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.24</v>
-      </c>
       <c r="W24" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="X24" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Z24" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC24" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AE24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI24" t="n">
         <v>80</v>
       </c>
-      <c r="AF24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>90</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AK24" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AL24" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN24" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="AO24" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AP24" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR24" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU24" t="n">
         <v>6.2</v>
@@ -5154,48 +5154,48 @@
         <v>13.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="AX24" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="AY24" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>15.5</v>
+        <v>30</v>
       </c>
       <c r="BC24" t="n">
-        <v>15.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD24" t="n">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF24" t="n">
-        <v>10.5</v>
+        <v>29</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.2</v>
+        <v>60</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Genesis Huracan</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juticalpa</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>1.97</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>1.29</v>
+        <v>3.35</v>
       </c>
       <c r="O25" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="P25" t="n">
-        <v>1.29</v>
+        <v>1.82</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.19</v>
+        <v>2.04</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>1.2</v>
+        <v>3.75</v>
       </c>
       <c r="T25" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="U25" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Juticalpa</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>1.98</v>
+        <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>550</v>
       </c>
       <c r="J26" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="K26" t="n">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T26" t="n">
         <v>1.11</v>
       </c>
-      <c r="N26" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S26" t="n">
-        <v>5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.22</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,184 +5593,184 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.1</v>
+        <v>1.89</v>
       </c>
       <c r="G27" t="n">
-        <v>3.25</v>
+        <v>1.98</v>
       </c>
       <c r="H27" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K27" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="L27" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="O27" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="P27" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="Q27" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="n">
         <v>2.2</v>
       </c>
-      <c r="R27" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.91</v>
-      </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="V27" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="W27" t="n">
-        <v>1.44</v>
+        <v>2.02</v>
       </c>
       <c r="X27" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="Y27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF27" t="n">
         <v>11</v>
       </c>
-      <c r="Z27" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>26</v>
-      </c>
       <c r="AG27" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AI27" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AJ27" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="AK27" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="AL27" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM27" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="AO27" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AR27" t="n">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="AS27" t="n">
-        <v>32</v>
+        <v>8.4</v>
       </c>
       <c r="AT27" t="n">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
       <c r="AU27" t="n">
         <v>6.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX27" t="n">
-        <v>18.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY27" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
-        <v>17</v>
+        <v>6.8</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.3</v>
+        <v>19.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>4.2</v>
+        <v>21</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.3</v>
+        <v>16.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G28" t="n">
         <v>1.59</v>
@@ -5810,7 +5810,7 @@
         <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J28" t="n">
         <v>4.3</v>
@@ -5849,7 +5849,7 @@
         <v>1.96</v>
       </c>
       <c r="V28" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W28" t="n">
         <v>2.68</v>
@@ -5888,7 +5888,7 @@
         <v>24</v>
       </c>
       <c r="AI28" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ28" t="n">
         <v>14.5</v>
@@ -5906,7 +5906,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AO28" t="n">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AP28" t="n">
         <v>14</v>
@@ -5964,14 +5964,14 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.22</v>
+        <v>3.15</v>
       </c>
       <c r="G29" t="n">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="H29" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="I29" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J29" t="n">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="K29" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="M29" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N29" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="P29" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="T29" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="U29" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="W29" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="X29" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP29" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AQ29" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.1</v>
+        <v>13.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.8</v>
+        <v>32</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.7</v>
+        <v>9.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB29" t="n">
         <v>4.6</v>
       </c>
-      <c r="AW29" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BC29" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>5.8</v>
+        <v>21</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,75 +6175,75 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20:15:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CD Olimpia</t>
+          <t>Deportivo La Guaira</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lobos UPNFM</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J30" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="K30" t="n">
-        <v>950</v>
+        <v>3.3</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.14</v>
+        <v>1.52</v>
       </c>
       <c r="P30" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.14</v>
+        <v>2.56</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>1.14</v>
+        <v>4.9</v>
       </c>
       <c r="T30" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U30" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y30" t="n">
         <v>1000</v>
@@ -6297,69 +6297,69 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:15:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>CD Olimpia</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Lobos UPNFM</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="G31" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="H31" t="n">
-        <v>1.92</v>
+        <v>1.04</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="K31" t="n">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L31" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="O31" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="P31" t="n">
-        <v>1.82</v>
+        <v>1.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.08</v>
+        <v>1.14</v>
       </c>
       <c r="R31" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>3.85</v>
+        <v>1.14</v>
       </c>
       <c r="T31" t="n">
-        <v>1.93</v>
+        <v>1.11</v>
       </c>
       <c r="U31" t="n">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="V31" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,191 +6563,191 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Talleres</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="G32" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="H32" t="n">
-        <v>2.88</v>
+        <v>1.92</v>
       </c>
       <c r="I32" t="n">
-        <v>2.98</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P32" t="n">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,36 +6757,36 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Talleres</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.54</v>
+        <v>2.9</v>
       </c>
       <c r="G33" t="n">
-        <v>1.58</v>
+        <v>3.1</v>
       </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>2.9</v>
       </c>
       <c r="I33" t="n">
-        <v>8.199999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
-        <v>4.3</v>
+        <v>2.96</v>
       </c>
       <c r="K33" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -6801,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.84</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
@@ -6956,186 +6956,186 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="F34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H34" t="n">
+        <v>7</v>
+      </c>
+      <c r="I34" t="n">
+        <v>8</v>
+      </c>
+      <c r="J34" t="n">
         <v>4.3</v>
       </c>
-      <c r="G34" t="n">
+      <c r="K34" t="n">
         <v>4.7</v>
       </c>
-      <c r="H34" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="J34" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K34" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.22</v>
+        <v>1.84</v>
       </c>
       <c r="R34" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,378 +7145,572 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.14</v>
+        <v>4.3</v>
       </c>
       <c r="G35" t="n">
-        <v>2.24</v>
+        <v>4.6</v>
       </c>
       <c r="H35" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>4.1</v>
+        <v>2.06</v>
       </c>
       <c r="J35" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K35" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M35" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N35" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="O35" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="P35" t="n">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.87</v>
+        <v>2.22</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="S35" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="T35" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>2.24</v>
+        <v>1.9</v>
       </c>
       <c r="V35" t="n">
-        <v>1.32</v>
+        <v>1.94</v>
       </c>
       <c r="W35" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="X35" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z35" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AA35" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="AB35" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD35" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AE35" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AF35" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="AG35" t="n">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="AH35" t="n">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="AI35" t="n">
         <v>60</v>
       </c>
       <c r="AJ35" t="n">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="AK35" t="n">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="AL35" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN35" t="n">
-        <v>18.5</v>
+        <v>110</v>
       </c>
       <c r="AO35" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="AP35" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AQ35" t="n">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="AR35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS35" t="n">
         <v>21</v>
       </c>
-      <c r="AS35" t="n">
-        <v>5</v>
-      </c>
       <c r="AT35" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AU35" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV35" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AW35" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AX35" t="n">
-        <v>11.5</v>
+        <v>4.1</v>
       </c>
       <c r="AY35" t="n">
-        <v>8.4</v>
+        <v>15.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BB35" t="n">
-        <v>21</v>
+        <v>4.3</v>
       </c>
       <c r="BC35" t="n">
-        <v>17.5</v>
+        <v>4.3</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BE35" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BF35" t="n">
-        <v>12.5</v>
+        <v>4.1</v>
       </c>
       <c r="BG35" t="n">
-        <v>4.8</v>
+        <v>17</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-01 12:12:56</t>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X36" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:28:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Honduras Liga Nacional</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>22:30:00</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Real Espana</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>CD Marathon</t>
         </is>
       </c>
-      <c r="F36" t="n">
+      <c r="F37" t="n">
         <v>1.04</v>
       </c>
-      <c r="G36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H36" t="n">
+      <c r="G37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H37" t="n">
         <v>1.04</v>
       </c>
-      <c r="I36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="K36" t="n">
+      <c r="I37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K37" t="n">
         <v>950</v>
       </c>
-      <c r="L36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N36" t="n">
+      <c r="L37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N37" t="n">
         <v>1.25</v>
       </c>
-      <c r="O36" t="n">
+      <c r="O37" t="n">
         <v>1.39</v>
       </c>
-      <c r="P36" t="n">
+      <c r="P37" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="Q37" t="n">
         <v>1.38</v>
       </c>
-      <c r="R36" t="n">
+      <c r="R37" t="n">
         <v>1.18</v>
       </c>
-      <c r="S36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T36" t="n">
+      <c r="S37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T37" t="n">
         <v>1.11</v>
       </c>
-      <c r="U36" t="n">
+      <c r="U37" t="n">
         <v>1.11</v>
       </c>
-      <c r="V36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH36" t="inlineStr">
-        <is>
-          <t>2026-04-01 12:12:56</t>
+      <c r="V37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:28:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I2" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="J2" t="n">
         <v>4.3</v>
@@ -775,40 +775,40 @@
         <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="T2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="U2" t="n">
         <v>3.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X2" t="n">
         <v>42</v>
@@ -817,22 +817,22 @@
         <v>25</v>
       </c>
       <c r="Z2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA2" t="n">
         <v>42</v>
       </c>
       <c r="AB2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC2" t="n">
         <v>12.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF2" t="n">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>13.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ2" t="n">
         <v>40</v>
@@ -859,25 +859,25 @@
         <v>38</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AP2" t="n">
         <v>34</v>
       </c>
       <c r="AQ2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS2" t="n">
         <v>36</v>
       </c>
       <c r="AT2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU2" t="n">
         <v>11</v>
@@ -889,38 +889,38 @@
         <v>20</v>
       </c>
       <c r="AX2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD2" t="n">
         <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BF2" t="n">
         <v>8.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G3" t="n">
         <v>3.4</v>
       </c>
-      <c r="G3" t="n">
-        <v>3.5</v>
-      </c>
       <c r="H3" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="I3" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
         <v>3.75</v>
@@ -984,7 +984,7 @@
         <v>2.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R3" t="n">
         <v>1.46</v>
@@ -996,28 +996,28 @@
         <v>1.67</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V3" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Y3" t="n">
         <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA3" t="n">
         <v>29</v>
       </c>
       <c r="AB3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC3" t="n">
         <v>8.4</v>
@@ -1026,34 +1026,34 @@
         <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF3" t="n">
         <v>27</v>
       </c>
       <c r="AG3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL3" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AO3" t="n">
         <v>15</v>
@@ -1062,49 +1062,49 @@
         <v>15.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AT3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU3" t="n">
         <v>7.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX3" t="n">
         <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD3" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BE3" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BF3" t="n">
         <v>24</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -1154,19 +1154,19 @@
         <v>1.97</v>
       </c>
       <c r="I4" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J4" t="n">
         <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -1175,7 +1175,7 @@
         <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
         <v>1.6</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>1.79</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
         <v>4.2</v>
@@ -1363,22 +1363,22 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R5" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
         <v>1.73</v>
@@ -1447,7 +1447,7 @@
         <v>970</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AQ5" t="n">
         <v>4.2</v>
@@ -1465,10 +1465,10 @@
         <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX5" t="n">
         <v>5.6</v>
@@ -1480,7 +1480,7 @@
         <v>5.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB5" t="n">
         <v>6</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="G6" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="H6" t="n">
         <v>4.1</v>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1566,7 +1566,7 @@
         <v>1.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -1733,16 +1733,16 @@
         <v>3.6</v>
       </c>
       <c r="H7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I7" t="n">
         <v>2.62</v>
       </c>
       <c r="J7" t="n">
-        <v>2.92</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1841,19 +1841,19 @@
         <v>3.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AS7" t="n">
         <v>3.85</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AU7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AW7" t="n">
         <v>3.75</v>
@@ -1868,29 +1868,29 @@
         <v>3.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BB7" t="n">
         <v>4</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BE7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF7" t="n">
         <v>3.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -1933,22 +1933,22 @@
         <v>3.7</v>
       </c>
       <c r="J8" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="K8" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
         <v>1.39</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
         <v>2.46</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="P8" t="n">
         <v>1.54</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G9" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="H9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,10 +2139,10 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
         <v>2.98</v>
@@ -2160,16 +2160,16 @@
         <v>1.65</v>
       </c>
       <c r="U9" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V9" t="n">
         <v>1.15</v>
       </c>
       <c r="W9" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -2184,101 +2184,101 @@
         <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="n">
         <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="n">
         <v>4.7</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC9" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AS9" t="n">
+      <c r="BD9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF9" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4</v>
-      </c>
       <c r="BG9" t="n">
-        <v>4.1</v>
+        <v>2.26</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.02</v>
+        <v>2.24</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -2524,10 +2524,10 @@
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
         <v>1.19</v>
@@ -2554,7 +2554,7 @@
         <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
         <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
         <v>4.8</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K13" t="n">
         <v>950</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H15" t="n">
         <v>4.8</v>
@@ -3291,28 +3291,28 @@
         <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
         <v>3.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M15" t="n">
         <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P15" t="n">
         <v>1.71</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R15" t="n">
         <v>1.27</v>
@@ -3321,7 +3321,7 @@
         <v>4.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U15" t="n">
         <v>1.92</v>
@@ -3330,7 +3330,7 @@
         <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="X15" t="n">
         <v>10.5</v>
@@ -3384,10 +3384,10 @@
         <v>23</v>
       </c>
       <c r="AO15" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ15" t="n">
         <v>13</v>
@@ -3426,7 +3426,7 @@
         <v>21</v>
       </c>
       <c r="BC15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD15" t="n">
         <v>12</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -3473,13 +3473,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G16" t="n">
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K17" t="n">
         <v>950</v>
@@ -3691,16 +3691,16 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G18" t="n">
         <v>3.05</v>
       </c>
       <c r="H18" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I18" t="n">
         <v>2.84</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K18" t="n">
         <v>3.4</v>
@@ -3885,16 +3885,16 @@
         <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O18" t="n">
         <v>1.44</v>
       </c>
       <c r="P18" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R18" t="n">
         <v>1.26</v>
@@ -3936,7 +3936,7 @@
         <v>14.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AF18" t="n">
         <v>22</v>
@@ -3954,7 +3954,7 @@
         <v>60</v>
       </c>
       <c r="AK18" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AL18" t="n">
         <v>70</v>
@@ -3978,7 +3978,7 @@
         <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT18" t="n">
         <v>9</v>
@@ -3990,7 +3990,7 @@
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.6</v>
+        <v>29</v>
       </c>
       <c r="AX18" t="n">
         <v>16.5</v>
@@ -4002,29 +4002,29 @@
         <v>17.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="BC18" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG18" t="n">
         <v>7.4</v>
       </c>
-      <c r="BF18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G19" t="n">
         <v>2.12</v>
@@ -4067,25 +4067,25 @@
         <v>3.75</v>
       </c>
       <c r="J19" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
         <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O19" t="n">
         <v>1.21</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q19" t="n">
         <v>1.62</v>
@@ -4097,10 +4097,10 @@
         <v>2.44</v>
       </c>
       <c r="T19" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U19" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V19" t="n">
         <v>1.36</v>
@@ -4112,7 +4112,7 @@
         <v>23</v>
       </c>
       <c r="Y19" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z19" t="n">
         <v>30</v>
@@ -4124,7 +4124,7 @@
         <v>14</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
         <v>15.5</v>
@@ -4166,7 +4166,7 @@
         <v>20</v>
       </c>
       <c r="AQ19" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR19" t="n">
         <v>25</v>
@@ -4175,7 +4175,7 @@
         <v>50</v>
       </c>
       <c r="AT19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU19" t="n">
         <v>8.4</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -4249,25 +4249,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G20" t="n">
         <v>2.62</v>
       </c>
       <c r="H20" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I20" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K20" t="n">
         <v>3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="M20" t="n">
         <v>1.16</v>
@@ -4294,10 +4294,10 @@
         <v>2.42</v>
       </c>
       <c r="U20" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V20" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W20" t="n">
         <v>1.61</v>
@@ -4315,7 +4315,7 @@
         <v>110</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC20" t="n">
         <v>7.8</v>
@@ -4327,7 +4327,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG20" t="n">
         <v>14.5</v>
@@ -4339,10 +4339,10 @@
         <v>140</v>
       </c>
       <c r="AJ20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK20" t="n">
         <v>46</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>48</v>
       </c>
       <c r="AL20" t="n">
         <v>110</v>
@@ -4351,7 +4351,7 @@
         <v>380</v>
       </c>
       <c r="AN20" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO20" t="n">
         <v>150</v>
@@ -4366,7 +4366,7 @@
         <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT20" t="n">
         <v>5.8</v>
@@ -4378,7 +4378,7 @@
         <v>15</v>
       </c>
       <c r="AW20" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="AX20" t="n">
         <v>12</v>
@@ -4387,32 +4387,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC20" t="n">
         <v>36</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G21" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="H21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I21" t="n">
         <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4467,7 +4467,7 @@
         <v>1.12</v>
       </c>
       <c r="N21" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O21" t="n">
         <v>1.54</v>
@@ -4476,7 +4476,7 @@
         <v>1.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="R21" t="n">
         <v>1.19</v>
@@ -4494,7 +4494,7 @@
         <v>1.28</v>
       </c>
       <c r="W21" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="X21" t="n">
         <v>10.5</v>
@@ -4509,10 +4509,10 @@
         <v>150</v>
       </c>
       <c r="AB21" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD21" t="n">
         <v>20</v>
@@ -4539,13 +4539,13 @@
         <v>32</v>
       </c>
       <c r="AL21" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM21" t="n">
         <v>260</v>
       </c>
       <c r="AN21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO21" t="n">
         <v>150</v>
@@ -4560,10 +4560,10 @@
         <v>6.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AU21" t="n">
         <v>6.8</v>
@@ -4572,7 +4572,7 @@
         <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX21" t="n">
         <v>9.800000000000001</v>
@@ -4596,17 +4596,17 @@
         <v>7.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BF21" t="n">
         <v>20</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -4652,10 +4652,10 @@
         <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
         <v>1.1</v>
@@ -4664,13 +4664,13 @@
         <v>3.05</v>
       </c>
       <c r="O22" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P22" t="n">
         <v>1.71</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R22" t="n">
         <v>1.26</v>
@@ -4682,7 +4682,7 @@
         <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V22" t="n">
         <v>1.29</v>
@@ -4715,7 +4715,7 @@
         <v>70</v>
       </c>
       <c r="AF22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
@@ -4727,7 +4727,7 @@
         <v>80</v>
       </c>
       <c r="AJ22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK22" t="n">
         <v>27</v>
@@ -4739,10 +4739,10 @@
         <v>170</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO22" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP22" t="n">
         <v>9.800000000000001</v>
@@ -4751,13 +4751,13 @@
         <v>11</v>
       </c>
       <c r="AR22" t="n">
-        <v>8.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
         <v>7</v>
@@ -4781,26 +4781,26 @@
         <v>55</v>
       </c>
       <c r="BB22" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC22" t="n">
         <v>21</v>
       </c>
       <c r="BD22" t="n">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="BE22" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BF22" t="n">
         <v>18</v>
       </c>
       <c r="BG22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -4834,13 +4834,13 @@
         <v>2.4</v>
       </c>
       <c r="G23" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
         <v>2.88</v>
@@ -4861,7 +4861,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="Q23" t="n">
         <v>2.92</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.42</v>
+        <v>1.87</v>
       </c>
       <c r="G24" t="n">
-        <v>2.54</v>
+        <v>1.95</v>
       </c>
       <c r="H24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J24" t="n">
         <v>3.55</v>
       </c>
-      <c r="I24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3</v>
-      </c>
       <c r="K24" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="P24" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.56</v>
+        <v>2.08</v>
       </c>
       <c r="R24" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="U24" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="W24" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="X24" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="Y24" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="Z24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK24" t="n">
         <v>26</v>
       </c>
-      <c r="AA24" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG24" t="n">
+      <c r="AL24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF24" t="n">
         <v>13</v>
       </c>
-      <c r="AH24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>29</v>
-      </c>
       <c r="BG24" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Juticalpa</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>1.97</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>550</v>
       </c>
       <c r="J25" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="K25" t="n">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>3.35</v>
+        <v>1.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="P25" t="n">
-        <v>1.82</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.04</v>
+        <v>1.19</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>3.75</v>
+        <v>1.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="U25" t="n">
-        <v>1.96</v>
+        <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Genesis Huracan</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juticalpa</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>1.98</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="I26" t="n">
-        <v>550</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>1.31</v>
+        <v>2.76</v>
       </c>
       <c r="O26" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="P26" t="n">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.19</v>
+        <v>2.46</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S26" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="T26" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,184 +5593,184 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.89</v>
+        <v>2.42</v>
       </c>
       <c r="G27" t="n">
-        <v>1.98</v>
+        <v>2.54</v>
       </c>
       <c r="H27" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="I27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S27" t="n">
         <v>5.1</v>
       </c>
-      <c r="J27" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S27" t="n">
-        <v>5</v>
-      </c>
       <c r="T27" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="V27" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="W27" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="X27" t="n">
         <v>10.5</v>
       </c>
       <c r="Y27" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV27" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z27" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR27" t="n">
+      <c r="AW27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB27" t="n">
         <v>30</v>
       </c>
-      <c r="AS27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BC27" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="BD27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE27" t="n">
         <v>7.8</v>
       </c>
-      <c r="BE27" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BF27" t="n">
-        <v>16.5</v>
+        <v>29</v>
       </c>
       <c r="BG27" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -5801,16 +5801,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="G28" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H28" t="n">
         <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J28" t="n">
         <v>4.3</v>
@@ -5834,7 +5834,7 @@
         <v>2.06</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R28" t="n">
         <v>1.41</v>
@@ -5843,16 +5843,16 @@
         <v>3.25</v>
       </c>
       <c r="T28" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U28" t="n">
         <v>1.96</v>
       </c>
       <c r="V28" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W28" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="X28" t="n">
         <v>16</v>
@@ -5867,10 +5867,10 @@
         <v>280</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD28" t="n">
         <v>27</v>
@@ -5882,16 +5882,16 @@
         <v>9</v>
       </c>
       <c r="AG28" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AH28" t="n">
         <v>24</v>
       </c>
       <c r="AI28" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ28" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK28" t="n">
         <v>16.5</v>
@@ -5903,34 +5903,34 @@
         <v>180</v>
       </c>
       <c r="AN28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO28" t="n">
         <v>130</v>
       </c>
       <c r="AP28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR28" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AS28" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV28" t="n">
         <v>24</v>
       </c>
       <c r="AW28" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AX28" t="n">
         <v>8.4</v>
@@ -5951,7 +5951,7 @@
         <v>15</v>
       </c>
       <c r="BD28" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE28" t="n">
         <v>80</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>3.15</v>
       </c>
       <c r="G29" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H29" t="n">
         <v>2.5</v>
@@ -6022,7 +6022,7 @@
         <v>3.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P29" t="n">
         <v>1.73</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G30" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="H30" t="n">
         <v>3.6</v>
       </c>
       <c r="I30" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J30" t="n">
         <v>2.84</v>
@@ -6207,43 +6207,43 @@
         <v>3.3</v>
       </c>
       <c r="L30" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M30" t="n">
         <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="O30" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P30" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U30" t="n">
         <v>1.73</v>
       </c>
       <c r="V30" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="X30" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
         <v>1000</v>
@@ -6303,56 +6303,56 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR30" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AS30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT30" t="n">
         <v>5.8</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>5.7</v>
       </c>
       <c r="AU30" t="n">
         <v>5.6</v>
       </c>
       <c r="AV30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX30" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>4.3</v>
       </c>
       <c r="AY30" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BA30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB30" t="n">
         <v>5.8</v>
       </c>
-      <c r="BB30" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BC30" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF30" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BG30" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -6407,13 +6407,13 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O31" t="n">
         <v>1.14</v>
       </c>
       <c r="P31" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q31" t="n">
         <v>1.14</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
         <v>3.75</v>
       </c>
       <c r="L32" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M32" t="n">
         <v>1.08</v>
@@ -6634,37 +6634,37 @@
         <v>15</v>
       </c>
       <c r="Y32" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z32" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AB32" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE32" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AF32" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG32" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI32" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ32" t="n">
         <v>130</v>
@@ -6679,25 +6679,25 @@
         <v>140</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO32" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AP32" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ32" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AR32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS32" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AT32" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU32" t="n">
         <v>7</v>
@@ -6709,38 +6709,38 @@
         <v>18.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY32" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AZ32" t="n">
         <v>17</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BB32" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BC32" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BD32" t="n">
-        <v>50</v>
+        <v>7.4</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BF32" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BG32" t="n">
         <v>13.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -6771,13 +6771,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="G33" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="H33" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
         <v>3.1</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
         <v>4.3</v>
       </c>
       <c r="K34" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
         <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V35" t="n">
         <v>1.94</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -7380,13 +7380,13 @@
         <v>4.2</v>
       </c>
       <c r="O36" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P36" t="n">
         <v>2.08</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="R36" t="n">
         <v>1.43</v>
@@ -7395,7 +7395,7 @@
         <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U36" t="n">
         <v>2.32</v>
@@ -7422,13 +7422,13 @@
         <v>12</v>
       </c>
       <c r="AC36" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD36" t="n">
         <v>18</v>
       </c>
       <c r="AE36" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF36" t="n">
         <v>17</v>
@@ -7437,10 +7437,10 @@
         <v>12</v>
       </c>
       <c r="AH36" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ36" t="n">
         <v>34</v>
@@ -7461,7 +7461,7 @@
         <v>44</v>
       </c>
       <c r="AP36" t="n">
-        <v>4.6</v>
+        <v>14</v>
       </c>
       <c r="AQ36" t="n">
         <v>13</v>
@@ -7470,22 +7470,22 @@
         <v>21</v>
       </c>
       <c r="AS36" t="n">
-        <v>5.8</v>
+        <v>50</v>
       </c>
       <c r="AT36" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU36" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV36" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX36" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY36" t="n">
         <v>9.199999999999999</v>
@@ -7494,29 +7494,29 @@
         <v>13.5</v>
       </c>
       <c r="BA36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC36" t="n">
         <v>5.6</v>
       </c>
-      <c r="BB36" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>5</v>
-      </c>
       <c r="BD36" t="n">
-        <v>5.3</v>
+        <v>24</v>
       </c>
       <c r="BE36" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF36" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG36" t="n">
-        <v>5.5</v>
+        <v>30</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7580,7 @@
         <v>1.24</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R37" t="n">
         <v>1.18</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-01 14:28:30</t>
+          <t>2026-04-01 16:45:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G2" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H2" t="n">
         <v>2.64</v>
@@ -772,7 +772,7 @@
         <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.22</v>
@@ -781,7 +781,7 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.12</v>
@@ -793,16 +793,16 @@
         <v>1.38</v>
       </c>
       <c r="R2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="T2" t="n">
         <v>1.4</v>
       </c>
       <c r="U2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="V2" t="n">
         <v>1.6</v>
@@ -811,28 +811,28 @@
         <v>1.64</v>
       </c>
       <c r="X2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Y2" t="n">
         <v>25</v>
       </c>
       <c r="Z2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA2" t="n">
         <v>42</v>
       </c>
       <c r="AB2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD2" t="n">
         <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF2" t="n">
         <v>26</v>
@@ -841,10 +841,10 @@
         <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AI2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ2" t="n">
         <v>40</v>
@@ -859,7 +859,7 @@
         <v>38</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO2" t="n">
         <v>10.5</v>
@@ -874,16 +874,16 @@
         <v>23</v>
       </c>
       <c r="AS2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU2" t="n">
         <v>11</v>
       </c>
       <c r="AV2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW2" t="n">
         <v>20</v>
@@ -895,13 +895,13 @@
         <v>12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
         <v>22</v>
       </c>
       <c r="BB2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC2" t="n">
         <v>19.5</v>
@@ -910,7 +910,7 @@
         <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BF2" t="n">
         <v>8.6</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G3" t="n">
         <v>3.4</v>
       </c>
       <c r="H3" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I3" t="n">
         <v>2.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -984,7 +984,7 @@
         <v>2.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
         <v>1.46</v>
@@ -996,16 +996,16 @@
         <v>1.67</v>
       </c>
       <c r="U3" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W3" t="n">
         <v>1.41</v>
       </c>
       <c r="X3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
         <v>12</v>
@@ -1014,13 +1014,13 @@
         <v>15.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB3" t="n">
         <v>16</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
         <v>11</v>
@@ -1053,13 +1053,13 @@
         <v>75</v>
       </c>
       <c r="AN3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP3" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>11</v>
@@ -1071,7 +1071,7 @@
         <v>26</v>
       </c>
       <c r="AT3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU3" t="n">
         <v>7.6</v>
@@ -1092,29 +1092,29 @@
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BB3" t="n">
-        <v>14.5</v>
+        <v>48</v>
       </c>
       <c r="BC3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD3" t="n">
         <v>36</v>
       </c>
       <c r="BE3" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="BF3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG3" t="n">
         <v>13</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="H4" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="J4" t="n">
         <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,16 +1169,16 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="O4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
         <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
@@ -1193,10 +1193,10 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="W4" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="G5" t="n">
         <v>6.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="I5" t="n">
         <v>1.79</v>
@@ -1369,13 +1369,13 @@
         <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q5" t="n">
         <v>1.66</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
         <v>2.62</v>
@@ -1393,7 +1393,7 @@
         <v>1.18</v>
       </c>
       <c r="X5" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
@@ -1408,7 +1408,7 @@
         <v>950</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="n">
         <v>970</v>
@@ -1417,7 +1417,7 @@
         <v>970</v>
       </c>
       <c r="AF5" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AG5" t="n">
         <v>950</v>
@@ -1426,83 +1426,83 @@
         <v>18</v>
       </c>
       <c r="AI5" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>85</v>
+        <v>700</v>
       </c>
       <c r="AL5" t="n">
-        <v>65</v>
+        <v>700</v>
       </c>
       <c r="AM5" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="AO5" t="n">
         <v>970</v>
       </c>
       <c r="AP5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS5" t="n">
         <v>4.8</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AT5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV5" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV5" t="n">
+      <c r="AW5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG5" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="G6" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="H6" t="n">
         <v>4.1</v>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1557,7 +1557,7 @@
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O6" t="n">
         <v>1.43</v>
@@ -1587,7 +1587,7 @@
         <v>1.94</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
         <v>1000</v>
@@ -1602,7 +1602,7 @@
         <v>8.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1614,10 +1614,10 @@
         <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1635,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1647,10 +1647,10 @@
         <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
         <v>5.7</v>
@@ -1659,10 +1659,10 @@
         <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX6" t="n">
         <v>8.6</v>
@@ -1671,32 +1671,32 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF6" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF6" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BG6" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="G7" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="I7" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
         <v>3.9</v>
@@ -1748,37 +1748,37 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="T7" t="n">
         <v>1.61</v>
       </c>
       <c r="U7" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="V7" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W7" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.3</v>
+        <v>6.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.55</v>
+        <v>8.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.45</v>
+        <v>8.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.3</v>
+        <v>6.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="BB7" t="n">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.1</v>
+        <v>2.36</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -1927,16 +1927,16 @@
         <v>3.05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J8" t="n">
         <v>2.82</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.39</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC9" t="n">
         <v>14</v>
@@ -2205,7 +2205,7 @@
         <v>70</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK9" t="n">
         <v>13.5</v>
@@ -2223,16 +2223,16 @@
         <v>65</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.2</v>
+        <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.32</v>
+        <v>4.2</v>
       </c>
       <c r="AT9" t="n">
         <v>11.5</v>
@@ -2244,7 +2244,7 @@
         <v>23</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.26</v>
+        <v>12.5</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
@@ -2253,32 +2253,32 @@
         <v>6.2</v>
       </c>
       <c r="AZ9" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="BF9" t="n">
         <v>4.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.26</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>2.24</v>
+        <v>1.02</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
@@ -2348,7 +2348,7 @@
         <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G11" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="H11" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="I11" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J11" t="n">
         <v>4.1</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2551,10 +2551,10 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2614,59 +2614,59 @@
         <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -2703,13 +2703,13 @@
         <v>1.8</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
         <v>4.8</v>
@@ -2742,10 +2742,10 @@
         <v>1.63</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W12" t="n">
         <v>2.24</v>
@@ -2802,65 +2802,65 @@
         <v>970</v>
       </c>
       <c r="AO12" t="n">
-        <v>55</v>
+        <v>300</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AR12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BD12" t="n">
         <v>1.23</v>
       </c>
-      <c r="AS12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BE12" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BF12" t="n">
         <v>1.26</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -3285,13 +3285,13 @@
         <v>2.04</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I15" t="n">
         <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
         <v>3.4</v>
@@ -3303,7 +3303,7 @@
         <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.41</v>
@@ -3321,7 +3321,7 @@
         <v>4.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U15" t="n">
         <v>1.92</v>
@@ -3330,10 +3330,10 @@
         <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="X15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="n">
         <v>14.5</v>
@@ -3345,7 +3345,7 @@
         <v>120</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC15" t="n">
         <v>7.6</v>
@@ -3360,7 +3360,7 @@
         <v>11.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
         <v>21</v>
@@ -3378,7 +3378,7 @@
         <v>48</v>
       </c>
       <c r="AM15" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AN15" t="n">
         <v>23</v>
@@ -3393,7 +3393,7 @@
         <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.5</v>
+        <v>29</v>
       </c>
       <c r="AS15" t="n">
         <v>13</v>
@@ -3405,7 +3405,7 @@
         <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW15" t="n">
         <v>12</v>
@@ -3417,7 +3417,7 @@
         <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA15" t="n">
         <v>12.5</v>
@@ -3426,23 +3426,23 @@
         <v>21</v>
       </c>
       <c r="BC15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BE15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BG15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.09</v>
+        <v>1.78</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>1.09</v>
+        <v>2.12</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3509,7 +3509,7 @@
         <v>1.3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S16" t="n">
         <v>1.3</v>
@@ -3521,10 +3521,10 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="H17" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.02</v>
+        <v>2.84</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3694,10 +3694,10 @@
         <v>1.27</v>
       </c>
       <c r="O17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Q17" t="n">
         <v>1.33</v>
@@ -3715,64 +3715,64 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP17" t="n">
         <v>1.03</v>
@@ -3823,14 +3823,14 @@
         <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="G18" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="I18" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K18" t="n">
         <v>3.25</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.5</v>
@@ -3885,19 +3885,19 @@
         <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P18" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S18" t="n">
         <v>4.4</v>
@@ -3906,125 +3906,125 @@
         <v>1.94</v>
       </c>
       <c r="U18" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="W18" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="X18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AA18" t="n">
         <v>55</v>
       </c>
       <c r="AB18" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AF18" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ18" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AK18" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL18" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AM18" t="n">
         <v>160</v>
       </c>
       <c r="AN18" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AO18" t="n">
         <v>42</v>
       </c>
       <c r="AP18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.8</v>
+        <v>44</v>
       </c>
       <c r="AT18" t="n">
         <v>9</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY18" t="n">
         <v>11</v>
       </c>
-      <c r="AW18" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BB18" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BC18" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG18" t="n">
         <v>32</v>
       </c>
-      <c r="BD18" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>34</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -4058,19 +4058,19 @@
         <v>2.06</v>
       </c>
       <c r="G19" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H19" t="n">
         <v>3.6</v>
       </c>
       <c r="I19" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
         <v>1.3</v>
@@ -4094,25 +4094,25 @@
         <v>1.57</v>
       </c>
       <c r="S19" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T19" t="n">
         <v>1.59</v>
       </c>
       <c r="U19" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X19" t="n">
         <v>23</v>
       </c>
       <c r="Y19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z19" t="n">
         <v>30</v>
@@ -4124,7 +4124,7 @@
         <v>14</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD19" t="n">
         <v>15.5</v>
@@ -4139,7 +4139,7 @@
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI19" t="n">
         <v>40</v>
@@ -4163,7 +4163,7 @@
         <v>27</v>
       </c>
       <c r="AP19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>17</v>
@@ -4172,10 +4172,10 @@
         <v>25</v>
       </c>
       <c r="AS19" t="n">
-        <v>50</v>
+        <v>10.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU19" t="n">
         <v>8.4</v>
@@ -4208,7 +4208,7 @@
         <v>24</v>
       </c>
       <c r="BE19" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="BF19" t="n">
         <v>9.199999999999999</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -4273,25 +4273,25 @@
         <v>1.16</v>
       </c>
       <c r="N20" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="O20" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="P20" t="n">
         <v>1.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
         <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
         <v>1.58</v>
@@ -4303,7 +4303,7 @@
         <v>1.61</v>
       </c>
       <c r="X20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y20" t="n">
         <v>9</v>
@@ -4324,7 +4324,7 @@
         <v>19</v>
       </c>
       <c r="AE20" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AF20" t="n">
         <v>14.5</v>
@@ -4336,7 +4336,7 @@
         <v>34</v>
       </c>
       <c r="AI20" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AJ20" t="n">
         <v>44</v>
@@ -4348,13 +4348,13 @@
         <v>110</v>
       </c>
       <c r="AM20" t="n">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="AN20" t="n">
         <v>60</v>
       </c>
       <c r="AO20" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AP20" t="n">
         <v>6</v>
@@ -4366,13 +4366,13 @@
         <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="AT20" t="n">
         <v>5.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV20" t="n">
         <v>15</v>
@@ -4387,32 +4387,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="BA20" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="BB20" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BC20" t="n">
         <v>36</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.4</v>
+        <v>95</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="BG20" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -4446,167 +4446,167 @@
         <v>2.02</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H21" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="I21" t="n">
         <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="O21" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="P21" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="R21" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U21" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="V21" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
         <v>1.9</v>
       </c>
       <c r="X21" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="Y21" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG21" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE21" t="n">
+      <c r="AH21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI21" t="n">
         <v>90</v>
       </c>
-      <c r="AF21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>110</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AK21" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AL21" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM21" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AO21" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AP21" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AQ21" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT21" t="n">
         <v>6.6</v>
       </c>
-      <c r="AS21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AU21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD21" t="n">
         <v>6.8</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF21" t="n">
         <v>16</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BG21" t="n">
         <v>7.4</v>
       </c>
-      <c r="AX21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G22" t="n">
         <v>2.12</v>
@@ -4658,22 +4658,22 @@
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P22" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S22" t="n">
         <v>4.4</v>
@@ -4682,16 +4682,16 @@
         <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V22" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W22" t="n">
         <v>1.89</v>
       </c>
       <c r="X22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y22" t="n">
         <v>970</v>
@@ -4700,7 +4700,7 @@
         <v>32</v>
       </c>
       <c r="AA22" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AB22" t="n">
         <v>7.8</v>
@@ -4709,13 +4709,13 @@
         <v>7.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE22" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
@@ -4724,7 +4724,7 @@
         <v>23</v>
       </c>
       <c r="AI22" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AJ22" t="n">
         <v>27</v>
@@ -4733,19 +4733,19 @@
         <v>27</v>
       </c>
       <c r="AL22" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM22" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AN22" t="n">
         <v>22</v>
       </c>
       <c r="AO22" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
         <v>11</v>
@@ -4757,13 +4757,13 @@
         <v>11.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU22" t="n">
         <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW22" t="n">
         <v>50</v>
@@ -4775,13 +4775,13 @@
         <v>9.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA22" t="n">
         <v>55</v>
       </c>
       <c r="BB22" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC22" t="n">
         <v>21</v>
@@ -4790,7 +4790,7 @@
         <v>38</v>
       </c>
       <c r="BE22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF22" t="n">
         <v>18</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -4834,16 +4834,16 @@
         <v>2.4</v>
       </c>
       <c r="G23" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H23" t="n">
         <v>3.55</v>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J23" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K23" t="n">
         <v>3.25</v>
@@ -4864,7 +4864,7 @@
         <v>1.46</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -5025,19 +5025,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G24" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
         <v>3.9</v>
@@ -5049,7 +5049,7 @@
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O24" t="n">
         <v>1.37</v>
@@ -5061,10 +5061,10 @@
         <v>2.08</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T24" t="n">
         <v>1.96</v>
@@ -5073,16 +5073,16 @@
         <v>1.96</v>
       </c>
       <c r="V24" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W24" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X24" t="n">
         <v>16</v>
       </c>
       <c r="Y24" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z24" t="n">
         <v>44</v>
@@ -5091,7 +5091,7 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC24" t="n">
         <v>9.4</v>
@@ -5106,7 +5106,7 @@
         <v>11.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH24" t="n">
         <v>25</v>
@@ -5133,19 +5133,19 @@
         <v>100</v>
       </c>
       <c r="AP24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>13.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS24" t="n">
         <v>38</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU24" t="n">
         <v>7.4</v>
@@ -5154,10 +5154,10 @@
         <v>16.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX24" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY24" t="n">
         <v>9.199999999999999</v>
@@ -5175,7 +5175,7 @@
         <v>18.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE24" t="n">
         <v>44</v>
@@ -5184,11 +5184,11 @@
         <v>13</v>
       </c>
       <c r="BG24" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="G25" t="n">
         <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="I25" t="n">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="K25" t="n">
         <v>950</v>
@@ -5267,10 +5267,10 @@
         <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G26" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H26" t="n">
         <v>4.6</v>
@@ -5425,22 +5425,22 @@
         <v>5.1</v>
       </c>
       <c r="J26" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N26" t="n">
         <v>2.76</v>
       </c>
       <c r="O26" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P26" t="n">
         <v>1.59</v>
@@ -5452,7 +5452,7 @@
         <v>1.21</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T26" t="n">
         <v>2.2</v>
@@ -5461,7 +5461,7 @@
         <v>1.74</v>
       </c>
       <c r="V26" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W26" t="n">
         <v>2.02</v>
@@ -5482,13 +5482,13 @@
         <v>6.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD26" t="n">
         <v>22</v>
       </c>
       <c r="AE26" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AF26" t="n">
         <v>11</v>
@@ -5503,7 +5503,7 @@
         <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK26" t="n">
         <v>27</v>
@@ -5521,25 +5521,25 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>30</v>
+        <v>14.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT26" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW26" t="n">
         <v>8.4</v>
@@ -5551,10 +5551,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB26" t="n">
         <v>19.5</v>
@@ -5566,17 +5566,17 @@
         <v>8</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF26" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BG26" t="n">
         <v>8.6</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5670,7 @@
         <v>26</v>
       </c>
       <c r="AA27" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AB27" t="n">
         <v>8</v>
@@ -5682,7 +5682,7 @@
         <v>17</v>
       </c>
       <c r="AE27" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AF27" t="n">
         <v>15</v>
@@ -5694,28 +5694,28 @@
         <v>24</v>
       </c>
       <c r="AI27" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AJ27" t="n">
         <v>40</v>
       </c>
       <c r="AK27" t="n">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="AL27" t="n">
-        <v>65</v>
+        <v>460</v>
       </c>
       <c r="AM27" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN27" t="n">
         <v>38</v>
       </c>
       <c r="AO27" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AP27" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ27" t="n">
         <v>8.800000000000001</v>
@@ -5754,7 +5754,7 @@
         <v>30</v>
       </c>
       <c r="BC27" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="BD27" t="n">
         <v>7.2</v>
@@ -5766,11 +5766,11 @@
         <v>29</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.4</v>
+        <v>60</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G28" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I28" t="n">
         <v>7.4</v>
@@ -5819,19 +5819,19 @@
         <v>4.5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M28" t="n">
         <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
         <v>1.3</v>
       </c>
       <c r="P28" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q28" t="n">
         <v>1.88</v>
@@ -5852,7 +5852,7 @@
         <v>1.15</v>
       </c>
       <c r="W28" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="X28" t="n">
         <v>16</v>
@@ -5867,10 +5867,10 @@
         <v>280</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD28" t="n">
         <v>27</v>
@@ -5882,7 +5882,7 @@
         <v>9</v>
       </c>
       <c r="AG28" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AH28" t="n">
         <v>24</v>
@@ -5891,7 +5891,7 @@
         <v>110</v>
       </c>
       <c r="AJ28" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK28" t="n">
         <v>16.5</v>
@@ -5915,7 +5915,7 @@
         <v>21</v>
       </c>
       <c r="AR28" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AS28" t="n">
         <v>48</v>
@@ -5924,28 +5924,28 @@
         <v>7.4</v>
       </c>
       <c r="AU28" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV28" t="n">
         <v>24</v>
       </c>
       <c r="AW28" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AX28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY28" t="n">
         <v>9</v>
       </c>
       <c r="AZ28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA28" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="BB28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC28" t="n">
         <v>15</v>
@@ -5954,17 +5954,17 @@
         <v>32</v>
       </c>
       <c r="BE28" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BF28" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG28" t="n">
         <v>42</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G29" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H29" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="I29" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="J29" t="n">
         <v>3.35</v>
@@ -6025,7 +6025,7 @@
         <v>1.41</v>
       </c>
       <c r="P29" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q29" t="n">
         <v>2.2</v>
@@ -6040,13 +6040,13 @@
         <v>1.91</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V29" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W29" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X29" t="n">
         <v>14</v>
@@ -6076,16 +6076,16 @@
         <v>26</v>
       </c>
       <c r="AG29" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH29" t="n">
         <v>24</v>
       </c>
       <c r="AI29" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ29" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK29" t="n">
         <v>50</v>
@@ -6094,7 +6094,7 @@
         <v>70</v>
       </c>
       <c r="AM29" t="n">
-        <v>160</v>
+        <v>450</v>
       </c>
       <c r="AN29" t="n">
         <v>60</v>
@@ -6124,7 +6124,7 @@
         <v>10.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="AX29" t="n">
         <v>18.5</v>
@@ -6139,26 +6139,26 @@
         <v>32</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.8</v>
+        <v>38</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="BG29" t="n">
         <v>21</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
         <v>3.6</v>
       </c>
       <c r="I30" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J30" t="n">
         <v>2.84</v>
@@ -6237,7 +6237,7 @@
         <v>1.73</v>
       </c>
       <c r="V30" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W30" t="n">
         <v>1.6</v>
@@ -6333,7 +6333,7 @@
         <v>6.4</v>
       </c>
       <c r="BB30" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC30" t="n">
         <v>5.8</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -6383,19 +6383,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="G31" t="n">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="H31" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="I31" t="n">
         <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="K31" t="n">
         <v>950</v>
@@ -6407,13 +6407,13 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="O31" t="n">
         <v>1.14</v>
       </c>
       <c r="P31" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Q31" t="n">
         <v>1.14</v>
@@ -6422,7 +6422,7 @@
         <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T31" t="n">
         <v>1.11</v>
@@ -6431,10 +6431,10 @@
         <v>1.11</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -6491,62 +6491,62 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF31" t="n">
         <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
         <v>4.9</v>
       </c>
       <c r="H32" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="I32" t="n">
         <v>2</v>
@@ -6595,7 +6595,7 @@
         <v>3.75</v>
       </c>
       <c r="L32" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="M32" t="n">
         <v>1.08</v>
@@ -6628,7 +6628,7 @@
         <v>2</v>
       </c>
       <c r="W32" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X32" t="n">
         <v>15</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
         <v>4.3</v>
       </c>
       <c r="K34" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
         <v>4.6</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I35" t="n">
         <v>2.06</v>
@@ -7177,7 +7177,7 @@
         <v>3.65</v>
       </c>
       <c r="L35" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M35" t="n">
         <v>1.09</v>
@@ -7186,7 +7186,7 @@
         <v>3.1</v>
       </c>
       <c r="O35" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P35" t="n">
         <v>1.72</v>
@@ -7213,37 +7213,37 @@
         <v>1.28</v>
       </c>
       <c r="X35" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC35" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Z35" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AD35" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF35" t="n">
         <v>40</v>
       </c>
       <c r="AG35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH35" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI35" t="n">
         <v>60</v>
@@ -7252,7 +7252,7 @@
         <v>130</v>
       </c>
       <c r="AK35" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL35" t="n">
         <v>95</v>
@@ -7264,7 +7264,7 @@
         <v>110</v>
       </c>
       <c r="AO35" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP35" t="n">
         <v>10</v>
@@ -7291,7 +7291,7 @@
         <v>21</v>
       </c>
       <c r="AX35" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AY35" t="n">
         <v>15.5</v>
@@ -7300,29 +7300,29 @@
         <v>19</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BB35" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BC35" t="n">
-        <v>4.3</v>
+        <v>55</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF35" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BG35" t="n">
         <v>17</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
         <v>2.24</v>
       </c>
       <c r="H36" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I36" t="n">
         <v>4.1</v>
@@ -7368,7 +7368,7 @@
         <v>3.4</v>
       </c>
       <c r="K36" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -7392,7 +7392,7 @@
         <v>1.43</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T36" t="n">
         <v>1.68</v>
@@ -7404,7 +7404,7 @@
         <v>1.32</v>
       </c>
       <c r="W36" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X36" t="n">
         <v>16.5</v>
@@ -7497,7 +7497,7 @@
         <v>6.4</v>
       </c>
       <c r="BB36" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BC36" t="n">
         <v>5.6</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:59</t>
+          <t>2026-04-01 19:03:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -766,7 +766,7 @@
         <v>2.64</v>
       </c>
       <c r="I2" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="J2" t="n">
         <v>4.3</v>
@@ -784,19 +784,19 @@
         <v>8.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P2" t="n">
         <v>3.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S2" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="T2" t="n">
         <v>1.4</v>
@@ -805,19 +805,19 @@
         <v>3.35</v>
       </c>
       <c r="V2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W2" t="n">
         <v>1.64</v>
       </c>
       <c r="X2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Y2" t="n">
         <v>25</v>
       </c>
       <c r="Z2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA2" t="n">
         <v>42</v>
@@ -856,10 +856,10 @@
         <v>24</v>
       </c>
       <c r="AM2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AO2" t="n">
         <v>10.5</v>
@@ -910,7 +910,7 @@
         <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BF2" t="n">
         <v>8.6</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -951,28 +951,28 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G3" t="n">
         <v>3.4</v>
       </c>
       <c r="H3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
         <v>4.6</v>
@@ -981,10 +981,10 @@
         <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R3" t="n">
         <v>1.46</v>
@@ -993,19 +993,19 @@
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="W3" t="n">
         <v>1.41</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
         <v>12</v>
@@ -1029,7 +1029,7 @@
         <v>22</v>
       </c>
       <c r="AF3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AG3" t="n">
         <v>14</v>
@@ -1047,16 +1047,16 @@
         <v>36</v>
       </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AP3" t="n">
         <v>16.5</v>
@@ -1068,13 +1068,13 @@
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
         <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY3" t="n">
         <v>12.5</v>
@@ -1092,7 +1092,7 @@
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BB3" t="n">
         <v>48</v>
@@ -1101,20 +1101,20 @@
         <v>30</v>
       </c>
       <c r="BD3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE3" t="n">
         <v>46</v>
       </c>
       <c r="BF3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>2.98</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="I4" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
         <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
         <v>1.25</v>
@@ -1178,137 +1178,137 @@
         <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.27</v>
+        <v>1.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="V4" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="W4" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.08</v>
+        <v>14.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.09</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.09</v>
+        <v>13.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.09</v>
+        <v>11.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.09</v>
+        <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.06</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.09</v>
+        <v>9.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.09</v>
+        <v>19.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.09</v>
+        <v>19.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.09</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.07</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.09</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.09</v>
+        <v>7.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.09</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.09</v>
+        <v>7.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.08</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.09</v>
+        <v>7.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.09</v>
+        <v>13.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G5" t="n">
         <v>6.4</v>
@@ -1354,34 +1354,34 @@
         <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
         <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="R5" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U5" t="n">
         <v>2.1</v>
@@ -1393,28 +1393,28 @@
         <v>1.18</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="Z5" t="n">
         <v>10.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
         <v>950</v>
       </c>
       <c r="AC5" t="n">
-        <v>42</v>
+        <v>17.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AE5" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
         <v>500</v>
@@ -1438,71 +1438,71 @@
         <v>700</v>
       </c>
       <c r="AM5" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
         <v>700</v>
       </c>
       <c r="AO5" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AS5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV5" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AW5" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.2</v>
+        <v>8.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -1533,31 +1533,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G6" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O6" t="n">
         <v>1.43</v>
@@ -1566,13 +1566,13 @@
         <v>1.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T6" t="n">
         <v>2</v>
@@ -1599,7 +1599,7 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AC6" t="n">
         <v>9.199999999999999</v>
@@ -1611,19 +1611,19 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG6" t="n">
         <v>21</v>
       </c>
       <c r="AH6" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1635,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1647,10 +1647,10 @@
         <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AT6" t="n">
         <v>5.7</v>
@@ -1662,7 +1662,7 @@
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AX6" t="n">
         <v>8.6</v>
@@ -1671,10 +1671,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BB6" t="n">
         <v>10.5</v>
@@ -1683,20 +1683,20 @@
         <v>11.5</v>
       </c>
       <c r="BD6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF6" t="n">
         <v>5.7</v>
       </c>
-      <c r="BE6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG6" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -1727,61 +1727,61 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.76</v>
+        <v>2.42</v>
       </c>
       <c r="G7" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="H7" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="I7" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N7" t="n">
         <v>3.9</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.44</v>
+        <v>2.78</v>
       </c>
       <c r="T7" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U7" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y7" t="n">
         <v>1000</v>
@@ -1793,10 +1793,10 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC7" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1811,13 +1811,13 @@
         <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AK7" t="n">
         <v>1000</v>
@@ -1832,10 +1832,10 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="AQ7" t="n">
         <v>6.4</v>
@@ -1844,53 +1844,53 @@
         <v>8.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV7" t="n">
         <v>6.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY7" t="n">
         <v>5.3</v>
       </c>
-      <c r="AY7" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.76</v>
+        <v>3.95</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.6</v>
+        <v>2.92</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="BF7" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
         <v>1.49</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y8" t="n">
         <v>1000</v>
@@ -1984,25 +1984,25 @@
         <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
         <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH8" t="n">
         <v>1000</v>
@@ -2011,10 +2011,10 @@
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.06</v>
+        <v>5.1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.12</v>
+        <v>5.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.12</v>
+        <v>1.77</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.12</v>
+        <v>1.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.12</v>
+        <v>5.1</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.12</v>
+        <v>1.7</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.12</v>
+        <v>1.79</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.12</v>
+        <v>1.72</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.12</v>
+        <v>1.68</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.12</v>
+        <v>1.76</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.12</v>
+        <v>1.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.12</v>
+        <v>1.79</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.12</v>
+        <v>1.78</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.12</v>
+        <v>1.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.12</v>
+        <v>1.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.12</v>
+        <v>1.76</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.12</v>
+        <v>1.79</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -2121,13 +2121,13 @@
         <v>1.51</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I9" t="n">
         <v>7.6</v>
       </c>
       <c r="J9" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="K9" t="n">
         <v>6</v>
@@ -2205,7 +2205,7 @@
         <v>70</v>
       </c>
       <c r="AJ9" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AK9" t="n">
         <v>13.5</v>
@@ -2253,10 +2253,10 @@
         <v>6.2</v>
       </c>
       <c r="AZ9" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BB9" t="n">
         <v>7.6</v>
@@ -2265,7 +2265,7 @@
         <v>7.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BE9" t="n">
         <v>12.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="G11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="H11" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="I11" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K11" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2527,10 +2527,10 @@
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P11" t="n">
         <v>2.12</v>
@@ -2539,7 +2539,7 @@
         <v>1.54</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
         <v>2.36</v>
@@ -2554,7 +2554,7 @@
         <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2569,7 +2569,7 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC11" t="n">
         <v>1000</v>
@@ -2581,10 +2581,10 @@
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH11" t="n">
         <v>1000</v>
@@ -2593,10 +2593,10 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2605,68 +2605,68 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.02</v>
+        <v>1.62</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
         <v>950</v>
       </c>
       <c r="Z12" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
@@ -2766,13 +2766,13 @@
         <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
         <v>950</v>
       </c>
       <c r="AE12" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
         <v>970</v>
@@ -2793,7 +2793,7 @@
         <v>970</v>
       </c>
       <c r="AL12" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>300</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.28</v>
+        <v>6.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.28</v>
+        <v>6.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.28</v>
+        <v>6.4</v>
       </c>
       <c r="AZ12" t="n">
         <v>1.28</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BC12" t="n">
         <v>1.28</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.26</v>
+        <v>2.22</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -3282,10 +3282,10 @@
         <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
         <v>5</v>
@@ -3303,13 +3303,13 @@
         <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
         <v>1.41</v>
       </c>
       <c r="P15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q15" t="n">
         <v>2.26</v>
@@ -3318,19 +3318,19 @@
         <v>1.27</v>
       </c>
       <c r="S15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T15" t="n">
         <v>1.96</v>
       </c>
       <c r="U15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V15" t="n">
         <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X15" t="n">
         <v>11</v>
@@ -3345,7 +3345,7 @@
         <v>120</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC15" t="n">
         <v>7.6</v>
@@ -3366,7 +3366,7 @@
         <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>85</v>
+        <v>370</v>
       </c>
       <c r="AJ15" t="n">
         <v>24</v>
@@ -3378,10 +3378,10 @@
         <v>48</v>
       </c>
       <c r="AM15" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AO15" t="n">
         <v>95</v>
@@ -3393,10 +3393,10 @@
         <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT15" t="n">
         <v>7</v>
@@ -3405,22 +3405,22 @@
         <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
       </c>
       <c r="AY15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
         <v>17.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB15" t="n">
         <v>21</v>
@@ -3429,20 +3429,20 @@
         <v>20</v>
       </c>
       <c r="BD15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG15" t="n">
         <v>13</v>
       </c>
-      <c r="BF15" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>15</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>1.78</v>
       </c>
       <c r="G16" t="n">
-        <v>8.800000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="H16" t="n">
         <v>2.12</v>
@@ -3488,7 +3488,7 @@
         <v>2.8</v>
       </c>
       <c r="K16" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3509,7 +3509,7 @@
         <v>1.3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S16" t="n">
         <v>1.3</v>
@@ -3542,7 +3542,7 @@
         <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD16" t="n">
         <v>1000</v>
@@ -3557,13 +3557,13 @@
         <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK16" t="n">
         <v>1000</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.27</v>
+        <v>5.8</v>
       </c>
       <c r="AU16" t="n">
         <v>4.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="BF16" t="n">
         <v>5.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
         <v>8.6</v>
       </c>
       <c r="H17" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="J17" t="n">
         <v>2.84</v>
@@ -3691,13 +3691,13 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="O17" t="n">
         <v>1.01</v>
       </c>
       <c r="P17" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
         <v>1.33</v>
@@ -3718,10 +3718,10 @@
         <v>1.3</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="X17" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Y17" t="n">
         <v>500</v>
@@ -3730,10 +3730,10 @@
         <v>500</v>
       </c>
       <c r="AA17" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
         <v>500</v>
@@ -3757,7 +3757,7 @@
         <v>500</v>
       </c>
       <c r="AJ17" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK17" t="n">
         <v>500</v>
@@ -3766,7 +3766,7 @@
         <v>500</v>
       </c>
       <c r="AM17" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
         <v>500</v>
@@ -3775,62 +3775,62 @@
         <v>500</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>1.45</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -3861,82 +3861,82 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G18" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="H18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N18" t="n">
         <v>2.98</v>
       </c>
-      <c r="I18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.15</v>
-      </c>
       <c r="O18" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="P18" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="R18" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T18" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V18" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X18" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y18" t="n">
         <v>10.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AF18" t="n">
         <v>16.5</v>
@@ -3948,83 +3948,83 @@
         <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ18" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO18" t="n">
         <v>55</v>
       </c>
-      <c r="AM18" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>42</v>
-      </c>
       <c r="AP18" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AT18" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AV18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW18" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="BB18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC18" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="BE18" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BG18" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J19" t="n">
         <v>3.95</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.3</v>
@@ -4079,37 +4079,37 @@
         <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.21</v>
       </c>
       <c r="P19" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R19" t="n">
         <v>1.57</v>
       </c>
       <c r="S19" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="T19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U19" t="n">
         <v>2.52</v>
       </c>
       <c r="V19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W19" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="n">
         <v>19.5</v>
@@ -4133,7 +4133,7 @@
         <v>38</v>
       </c>
       <c r="AF19" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG19" t="n">
         <v>11</v>
@@ -4145,10 +4145,10 @@
         <v>40</v>
       </c>
       <c r="AJ19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL19" t="n">
         <v>29</v>
@@ -4157,7 +4157,7 @@
         <v>65</v>
       </c>
       <c r="AN19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO19" t="n">
         <v>27</v>
@@ -4166,13 +4166,13 @@
         <v>19.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR19" t="n">
         <v>25</v>
       </c>
       <c r="AS19" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT19" t="n">
         <v>12</v>
@@ -4181,13 +4181,13 @@
         <v>8.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW19" t="n">
         <v>30</v>
       </c>
       <c r="AX19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY19" t="n">
         <v>10</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>2.46</v>
       </c>
       <c r="G20" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="H20" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J20" t="n">
         <v>2.88</v>
@@ -4276,10 +4276,10 @@
         <v>2.16</v>
       </c>
       <c r="O20" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="P20" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Q20" t="n">
         <v>3.3</v>
@@ -4288,28 +4288,28 @@
         <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V20" t="n">
         <v>1.33</v>
       </c>
       <c r="W20" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="X20" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA20" t="n">
         <v>110</v>
@@ -4318,16 +4318,16 @@
         <v>6.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD20" t="n">
         <v>19</v>
       </c>
       <c r="AE20" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AF20" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG20" t="n">
         <v>14.5</v>
@@ -4336,7 +4336,7 @@
         <v>34</v>
       </c>
       <c r="AI20" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ20" t="n">
         <v>44</v>
@@ -4345,7 +4345,7 @@
         <v>46</v>
       </c>
       <c r="AL20" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM20" t="n">
         <v>500</v>
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AR20" t="n">
         <v>20</v>
@@ -4375,7 +4375,7 @@
         <v>6.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AW20" t="n">
         <v>60</v>
@@ -4384,10 +4384,10 @@
         <v>12</v>
       </c>
       <c r="AY20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ20" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BA20" t="n">
         <v>42</v>
@@ -4402,17 +4402,17 @@
         <v>38</v>
       </c>
       <c r="BE20" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="BF20" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="BG20" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -4446,10 +4446,10 @@
         <v>2.02</v>
       </c>
       <c r="G21" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
         <v>4.5</v>
@@ -4458,7 +4458,7 @@
         <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4473,7 +4473,7 @@
         <v>1.48</v>
       </c>
       <c r="P21" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q21" t="n">
         <v>2.48</v>
@@ -4494,7 +4494,7 @@
         <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X21" t="n">
         <v>18</v>
@@ -4503,7 +4503,7 @@
         <v>12</v>
       </c>
       <c r="Z21" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AA21" t="n">
         <v>500</v>
@@ -4536,10 +4536,10 @@
         <v>500</v>
       </c>
       <c r="AK21" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AL21" t="n">
-        <v>50</v>
+        <v>460</v>
       </c>
       <c r="AM21" t="n">
         <v>500</v>
@@ -4554,13 +4554,13 @@
         <v>9.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR21" t="n">
         <v>21</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT21" t="n">
         <v>6.6</v>
@@ -4569,7 +4569,7 @@
         <v>6.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>5.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW21" t="n">
         <v>7</v>
@@ -4584,29 +4584,29 @@
         <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="BB21" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BD21" t="n">
-        <v>6.8</v>
+        <v>42</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BF21" t="n">
         <v>16</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -4643,13 +4643,13 @@
         <v>2.12</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I22" t="n">
         <v>4.4</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K22" t="n">
         <v>3.6</v>
@@ -4670,7 +4670,7 @@
         <v>1.72</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R22" t="n">
         <v>1.27</v>
@@ -4679,7 +4679,7 @@
         <v>4.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
         <v>1.92</v>
@@ -4694,7 +4694,7 @@
         <v>12</v>
       </c>
       <c r="Y22" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Z22" t="n">
         <v>32</v>
@@ -4718,31 +4718,31 @@
         <v>12</v>
       </c>
       <c r="AG22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI22" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AJ22" t="n">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="AK22" t="n">
         <v>27</v>
       </c>
       <c r="AL22" t="n">
-        <v>48</v>
+        <v>290</v>
       </c>
       <c r="AM22" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
         <v>22</v>
       </c>
       <c r="AO22" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="AP22" t="n">
         <v>10</v>
@@ -4754,7 +4754,7 @@
         <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="AT22" t="n">
         <v>6.8</v>
@@ -4781,7 +4781,7 @@
         <v>55</v>
       </c>
       <c r="BB22" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BC22" t="n">
         <v>21</v>
@@ -4790,17 +4790,17 @@
         <v>38</v>
       </c>
       <c r="BE22" t="n">
-        <v>11.5</v>
+        <v>29</v>
       </c>
       <c r="BF22" t="n">
         <v>18</v>
       </c>
       <c r="BG22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -4834,16 +4834,16 @@
         <v>2.4</v>
       </c>
       <c r="G23" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="H23" t="n">
         <v>3.55</v>
       </c>
       <c r="I23" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="K23" t="n">
         <v>3.25</v>
@@ -4864,7 +4864,7 @@
         <v>1.46</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="G24" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H24" t="n">
         <v>4.6</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K24" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5049,61 +5049,61 @@
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P24" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="Q24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W24" t="n">
         <v>2.08</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.06</v>
-      </c>
       <c r="X24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z24" t="n">
         <v>44</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB24" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD24" t="n">
         <v>22</v>
       </c>
       <c r="AE24" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AF24" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG24" t="n">
         <v>11.5</v>
@@ -5124,10 +5124,10 @@
         <v>48</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AN24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO24" t="n">
         <v>100</v>
@@ -5136,31 +5136,31 @@
         <v>11.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS24" t="n">
         <v>38</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW24" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX24" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
         <v>18</v>
@@ -5169,16 +5169,16 @@
         <v>34</v>
       </c>
       <c r="BB24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC24" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD24" t="n">
         <v>25</v>
       </c>
       <c r="BE24" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BF24" t="n">
         <v>13</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -5222,19 +5222,19 @@
         <v>1.39</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="H25" t="n">
         <v>3.5</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="J25" t="n">
         <v>3.45</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5270,7 +5270,7 @@
         <v>1.12</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5327,62 +5327,62 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
         <v>3.5</v>
       </c>
       <c r="K26" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5452,7 +5452,7 @@
         <v>1.21</v>
       </c>
       <c r="S26" t="n">
-        <v>4.9</v>
+        <v>2.46</v>
       </c>
       <c r="T26" t="n">
         <v>2.2</v>
@@ -5467,116 +5467,116 @@
         <v>2.02</v>
       </c>
       <c r="X26" t="n">
-        <v>10.5</v>
+        <v>950</v>
       </c>
       <c r="Y26" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>11</v>
+        <v>500</v>
       </c>
       <c r="AG26" t="n">
-        <v>11.5</v>
+        <v>500</v>
       </c>
       <c r="AH26" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AR26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>14.5</v>
       </c>
-      <c r="AS26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>22</v>
-      </c>
       <c r="BA26" t="n">
-        <v>8.6</v>
+        <v>2.34</v>
       </c>
       <c r="BB26" t="n">
-        <v>19.5</v>
+        <v>2.24</v>
       </c>
       <c r="BC26" t="n">
-        <v>21</v>
+        <v>2.28</v>
       </c>
       <c r="BD26" t="n">
-        <v>8</v>
+        <v>2.32</v>
       </c>
       <c r="BE26" t="n">
-        <v>9</v>
+        <v>2.36</v>
       </c>
       <c r="BF26" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.6</v>
+        <v>2.34</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -5607,19 +5607,19 @@
         </is>
       </c>
       <c r="F27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G27" t="n">
         <v>2.42</v>
       </c>
-      <c r="G27" t="n">
-        <v>2.54</v>
-      </c>
       <c r="H27" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I27" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J27" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K27" t="n">
         <v>3.2</v>
@@ -5631,19 +5631,19 @@
         <v>1.12</v>
       </c>
       <c r="N27" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O27" t="n">
         <v>1.53</v>
       </c>
       <c r="P27" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="R27" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S27" t="n">
         <v>5.1</v>
@@ -5658,10 +5658,10 @@
         <v>1.35</v>
       </c>
       <c r="W27" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="X27" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y27" t="n">
         <v>11</v>
@@ -5670,7 +5670,7 @@
         <v>26</v>
       </c>
       <c r="AA27" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB27" t="n">
         <v>8</v>
@@ -5682,13 +5682,13 @@
         <v>17</v>
       </c>
       <c r="AE27" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="AF27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH27" t="n">
         <v>24</v>
@@ -5697,10 +5697,10 @@
         <v>500</v>
       </c>
       <c r="AJ27" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK27" t="n">
-        <v>140</v>
+        <v>34</v>
       </c>
       <c r="AL27" t="n">
         <v>460</v>
@@ -5709,13 +5709,13 @@
         <v>500</v>
       </c>
       <c r="AN27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO27" t="n">
         <v>500</v>
       </c>
       <c r="AP27" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ27" t="n">
         <v>8.800000000000001</v>
@@ -5724,7 +5724,7 @@
         <v>20</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.4</v>
+        <v>65</v>
       </c>
       <c r="AT27" t="n">
         <v>6.6</v>
@@ -5736,7 +5736,7 @@
         <v>13.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>7.2</v>
+        <v>48</v>
       </c>
       <c r="AX27" t="n">
         <v>12</v>
@@ -5748,19 +5748,19 @@
         <v>19</v>
       </c>
       <c r="BA27" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BB27" t="n">
         <v>30</v>
       </c>
       <c r="BC27" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF27" t="n">
         <v>29</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -5801,97 +5801,97 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="G28" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="H28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M28" t="n">
         <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O28" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P28" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="R28" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
         <v>3.25</v>
       </c>
       <c r="T28" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U28" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V28" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W28" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="X28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y28" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA28" t="n">
-        <v>280</v>
+        <v>190</v>
       </c>
       <c r="AB28" t="n">
         <v>8</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE28" t="n">
         <v>110</v>
       </c>
       <c r="AF28" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG28" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI28" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ28" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AK28" t="n">
         <v>16.5</v>
@@ -5903,22 +5903,22 @@
         <v>180</v>
       </c>
       <c r="AN28" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO28" t="n">
         <v>130</v>
       </c>
       <c r="AP28" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR28" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AS28" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AT28" t="n">
         <v>7.4</v>
@@ -5927,16 +5927,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW28" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AX28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY28" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ28" t="n">
         <v>21</v>
@@ -5945,10 +5945,10 @@
         <v>38</v>
       </c>
       <c r="BB28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC28" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD28" t="n">
         <v>32</v>
@@ -5957,14 +5957,14 @@
         <v>70</v>
       </c>
       <c r="BF28" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BG28" t="n">
         <v>42</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -5998,13 +5998,13 @@
         <v>3.1</v>
       </c>
       <c r="G29" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H29" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="I29" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J29" t="n">
         <v>3.35</v>
@@ -6022,10 +6022,10 @@
         <v>3.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P29" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q29" t="n">
         <v>2.2</v>
@@ -6040,43 +6040,43 @@
         <v>1.91</v>
       </c>
       <c r="U29" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V29" t="n">
         <v>1.61</v>
       </c>
       <c r="W29" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="X29" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Y29" t="n">
         <v>10.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AB29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AC29" t="n">
         <v>7.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF29" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG29" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH29" t="n">
         <v>24</v>
@@ -6088,19 +6088,19 @@
         <v>60</v>
       </c>
       <c r="AK29" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL29" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM29" t="n">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="AN29" t="n">
         <v>60</v>
       </c>
       <c r="AO29" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AP29" t="n">
         <v>10</v>
@@ -6136,29 +6136,29 @@
         <v>17</v>
       </c>
       <c r="BA29" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BC29" t="n">
         <v>18</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BE29" t="n">
         <v>38</v>
       </c>
       <c r="BF29" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BG29" t="n">
         <v>21</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -6198,10 +6198,10 @@
         <v>3.6</v>
       </c>
       <c r="I30" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="K30" t="n">
         <v>3.3</v>
@@ -6237,10 +6237,10 @@
         <v>1.73</v>
       </c>
       <c r="V30" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6297,62 +6297,62 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>6.6</v>
+        <v>1.13</v>
       </c>
       <c r="AQ30" t="n">
-        <v>8.199999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AR30" t="n">
-        <v>5.4</v>
+        <v>1.13</v>
       </c>
       <c r="AS30" t="n">
-        <v>6.4</v>
+        <v>1.13</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU30" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="AV30" t="n">
-        <v>5</v>
+        <v>1.13</v>
       </c>
       <c r="AW30" t="n">
-        <v>6.2</v>
+        <v>1.13</v>
       </c>
       <c r="AX30" t="n">
-        <v>4.6</v>
+        <v>1.13</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.4</v>
+        <v>1.13</v>
       </c>
       <c r="AZ30" t="n">
-        <v>5.4</v>
+        <v>1.13</v>
       </c>
       <c r="BA30" t="n">
-        <v>6.4</v>
+        <v>1.13</v>
       </c>
       <c r="BB30" t="n">
-        <v>6.4</v>
+        <v>1.13</v>
       </c>
       <c r="BC30" t="n">
-        <v>5.8</v>
+        <v>1.13</v>
       </c>
       <c r="BD30" t="n">
-        <v>6.2</v>
+        <v>1.13</v>
       </c>
       <c r="BE30" t="n">
-        <v>6.6</v>
+        <v>1.13</v>
       </c>
       <c r="BF30" t="n">
-        <v>5.8</v>
+        <v>1.13</v>
       </c>
       <c r="BG30" t="n">
-        <v>6.4</v>
+        <v>1.13</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -6386,16 +6386,16 @@
         <v>1.27</v>
       </c>
       <c r="G31" t="n">
-        <v>2.1</v>
+        <v>990</v>
       </c>
       <c r="H31" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="I31" t="n">
         <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="K31" t="n">
         <v>950</v>
@@ -6407,7 +6407,7 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O31" t="n">
         <v>1.14</v>
@@ -6416,13 +6416,13 @@
         <v>1.31</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="R31" t="n">
         <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="T31" t="n">
         <v>1.11</v>
@@ -6434,7 +6434,7 @@
         <v>1.08</v>
       </c>
       <c r="W31" t="n">
-        <v>1.91</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -6485,68 +6485,68 @@
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G32" t="n">
         <v>4.9</v>
@@ -6592,10 +6592,10 @@
         <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L32" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M32" t="n">
         <v>1.08</v>
@@ -6622,7 +6622,7 @@
         <v>1.92</v>
       </c>
       <c r="U32" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V32" t="n">
         <v>2</v>
@@ -6688,7 +6688,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ32" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR32" t="n">
         <v>10</v>
@@ -6703,7 +6703,7 @@
         <v>7</v>
       </c>
       <c r="AV32" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW32" t="n">
         <v>18.5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="G33" t="n">
         <v>2.94</v>
@@ -6783,7 +6783,7 @@
         <v>3.1</v>
       </c>
       <c r="J33" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
         <v>3.05</v>
@@ -6801,7 +6801,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q33" t="n">
         <v>3</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
         <v>7</v>
       </c>
       <c r="I34" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J34" t="n">
         <v>4.3</v>
@@ -6998,7 +6998,7 @@
         <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -7165,10 +7165,10 @@
         <v>4.6</v>
       </c>
       <c r="H35" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="I35" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J35" t="n">
         <v>3.45</v>
@@ -7207,10 +7207,10 @@
         <v>1.91</v>
       </c>
       <c r="V35" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W35" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X35" t="n">
         <v>14</v>
@@ -7222,7 +7222,7 @@
         <v>13</v>
       </c>
       <c r="AA35" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB35" t="n">
         <v>15.5</v>
@@ -7276,7 +7276,7 @@
         <v>10</v>
       </c>
       <c r="AS35" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AT35" t="n">
         <v>11.5</v>
@@ -7291,7 +7291,7 @@
         <v>21</v>
       </c>
       <c r="AX35" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AY35" t="n">
         <v>15.5</v>
@@ -7300,10 +7300,10 @@
         <v>19</v>
       </c>
       <c r="BA35" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BC35" t="n">
         <v>55</v>
@@ -7315,14 +7315,14 @@
         <v>5.2</v>
       </c>
       <c r="BF35" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BG35" t="n">
         <v>17</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
         <v>2.32</v>
       </c>
       <c r="V36" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W36" t="n">
         <v>1.81</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
         <v>1000</v>
       </c>
       <c r="J37" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K37" t="n">
         <v>950</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-01 19:03:26</t>
+          <t>2026-04-01 21:20:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G2" t="n">
         <v>2.56</v>
       </c>
       <c r="H2" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I2" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J2" t="n">
         <v>4.3</v>
@@ -784,13 +784,13 @@
         <v>8.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R2" t="n">
         <v>2.02</v>
@@ -802,10 +802,10 @@
         <v>1.4</v>
       </c>
       <c r="U2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W2" t="n">
         <v>1.64</v>
@@ -814,7 +814,7 @@
         <v>42</v>
       </c>
       <c r="Y2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z2" t="n">
         <v>26</v>
@@ -823,13 +823,13 @@
         <v>42</v>
       </c>
       <c r="AB2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC2" t="n">
         <v>12</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE2" t="n">
         <v>22</v>
@@ -850,7 +850,7 @@
         <v>40</v>
       </c>
       <c r="AK2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL2" t="n">
         <v>24</v>
@@ -862,7 +862,7 @@
         <v>9.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP2" t="n">
         <v>34</v>
@@ -874,10 +874,10 @@
         <v>23</v>
       </c>
       <c r="AS2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AT2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU2" t="n">
         <v>11</v>
@@ -901,7 +901,7 @@
         <v>22</v>
       </c>
       <c r="BB2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC2" t="n">
         <v>19.5</v>
@@ -910,17 +910,17 @@
         <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G3" t="n">
         <v>3.4</v>
       </c>
       <c r="H3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="J3" t="n">
         <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.36</v>
@@ -975,31 +975,31 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
         <v>2.22</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U3" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V3" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="W3" t="n">
         <v>1.41</v>
@@ -1008,7 +1008,7 @@
         <v>18.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
         <v>15.5</v>
@@ -1041,10 +1041,10 @@
         <v>32</v>
       </c>
       <c r="AJ3" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AK3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL3" t="n">
         <v>40</v>
@@ -1056,16 +1056,16 @@
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ3" t="n">
         <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS3" t="n">
         <v>27</v>
@@ -1089,10 +1089,10 @@
         <v>12.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB3" t="n">
         <v>48</v>
@@ -1104,17 +1104,17 @@
         <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BF3" t="n">
-        <v>26</v>
+        <v>11.5</v>
       </c>
       <c r="BG3" t="n">
         <v>14</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="G4" t="n">
         <v>3.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I4" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
@@ -1163,7 +1163,7 @@
         <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1178,25 +1178,25 @@
         <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R4" t="n">
         <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V4" t="n">
         <v>1.64</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X4" t="n">
         <v>18.5</v>
@@ -1211,7 +1211,7 @@
         <v>34</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC4" t="n">
         <v>9</v>
@@ -1229,7 +1229,7 @@
         <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI4" t="n">
         <v>36</v>
@@ -1250,7 +1250,7 @@
         <v>29</v>
       </c>
       <c r="AO4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP4" t="n">
         <v>14.5</v>
@@ -1283,7 +1283,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
         <v>16</v>
@@ -1295,20 +1295,20 @@
         <v>18</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="G5" t="n">
         <v>6.4</v>
@@ -1351,10 +1351,10 @@
         <v>1.79</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.3</v>
@@ -1372,7 +1372,7 @@
         <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R5" t="n">
         <v>1.44</v>
@@ -1414,7 +1414,7 @@
         <v>36</v>
       </c>
       <c r="AE5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
         <v>500</v>
@@ -1423,7 +1423,7 @@
         <v>950</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
         <v>500</v>
@@ -1447,62 +1447,62 @@
         <v>29</v>
       </c>
       <c r="AP5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX5" t="n">
         <v>5.6</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AY5" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="BA5" t="n">
         <v>6.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.88</v>
       </c>
       <c r="G6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H6" t="n">
         <v>4.5</v>
@@ -1548,7 +1548,7 @@
         <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.43</v>
@@ -1584,7 +1584,7 @@
         <v>1.23</v>
       </c>
       <c r="W6" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="X6" t="n">
         <v>22</v>
@@ -1602,7 +1602,7 @@
         <v>14</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1611,19 +1611,19 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AG6" t="n">
         <v>21</v>
       </c>
       <c r="AH6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1647,10 +1647,10 @@
         <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="AT6" t="n">
         <v>5.7</v>
@@ -1662,7 +1662,7 @@
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX6" t="n">
         <v>8.6</v>
@@ -1674,7 +1674,7 @@
         <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="BB6" t="n">
         <v>10.5</v>
@@ -1683,20 +1683,20 @@
         <v>11.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -1727,73 +1727,73 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="G7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J7" t="n">
         <v>2.9</v>
       </c>
-      <c r="H7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>3.45</v>
       </c>
-      <c r="K7" t="n">
-        <v>3.85</v>
-      </c>
       <c r="L7" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
         <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="T7" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="U7" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
         <v>500</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>26</v>
       </c>
       <c r="AC7" t="n">
         <v>14</v>
@@ -1808,13 +1808,13 @@
         <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH7" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
         <v>440</v>
@@ -1832,65 +1832,65 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>6.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AV7" t="n">
         <v>6.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="AZ7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA7" t="n">
         <v>5.2</v>
       </c>
-      <c r="BA7" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BB7" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J8" t="n">
         <v>3.05</v>
       </c>
-      <c r="H8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.82</v>
-      </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.06</v>
+        <v>1.42</v>
       </c>
       <c r="P8" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>2.96</v>
+        <v>4.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="X8" t="n">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA8" t="n">
-        <v>900</v>
+        <v>290</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>95</v>
+        <v>7.6</v>
       </c>
       <c r="AD8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>290</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>390</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>210</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>370</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO8" t="n">
         <v>500</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP8" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.77</v>
+        <v>9</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.7</v>
+        <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.79</v>
+        <v>7.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.72</v>
+        <v>7.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.68</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.76</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.79</v>
+        <v>7.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.78</v>
+        <v>7.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.76</v>
+        <v>7.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.79</v>
+        <v>7.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G9" t="n">
         <v>1.51</v>
@@ -2124,13 +2124,13 @@
         <v>6.2</v>
       </c>
       <c r="I9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J9" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2148,13 +2148,13 @@
         <v>2.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R9" t="n">
         <v>1.8</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T9" t="n">
         <v>1.65</v>
@@ -2163,13 +2163,13 @@
         <v>2.32</v>
       </c>
       <c r="V9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W9" t="n">
         <v>2.96</v>
       </c>
       <c r="X9" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -2184,7 +2184,7 @@
         <v>500</v>
       </c>
       <c r="AC9" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="AD9" t="n">
         <v>29</v>
@@ -2217,19 +2217,19 @@
         <v>80</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AO9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ9" t="n">
         <v>14.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS9" t="n">
         <v>4.2</v>
@@ -2244,31 +2244,31 @@
         <v>23</v>
       </c>
       <c r="AW9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AY9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AZ9" t="n">
         <v>11.5</v>
       </c>
       <c r="BA9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE9" t="n">
         <v>12</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>12.5</v>
       </c>
       <c r="BF9" t="n">
         <v>4.2</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -2533,16 +2533,16 @@
         <v>1.18</v>
       </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -2554,7 +2554,7 @@
         <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -2697,28 +2697,28 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="I12" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
         <v>2.62</v>
@@ -2727,16 +2727,16 @@
         <v>1.18</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q12" t="n">
         <v>1.45</v>
       </c>
       <c r="R12" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T12" t="n">
         <v>1.63</v>
@@ -2745,10 +2745,10 @@
         <v>2.32</v>
       </c>
       <c r="V12" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -2757,7 +2757,7 @@
         <v>950</v>
       </c>
       <c r="Z12" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
@@ -2766,7 +2766,7 @@
         <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD12" t="n">
         <v>950</v>
@@ -2793,7 +2793,7 @@
         <v>970</v>
       </c>
       <c r="AL12" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
@@ -2802,31 +2802,31 @@
         <v>970</v>
       </c>
       <c r="AO12" t="n">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AT12" t="n">
         <v>6.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AX12" t="n">
         <v>6.4</v>
@@ -2835,22 +2835,22 @@
         <v>6.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="BF12" t="n">
         <v>2.22</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G15" t="n">
         <v>2.02</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I15" t="n">
         <v>5</v>
@@ -3297,7 +3297,7 @@
         <v>3.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M15" t="n">
         <v>1.1</v>
@@ -3312,7 +3312,7 @@
         <v>1.72</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R15" t="n">
         <v>1.27</v>
@@ -3324,7 +3324,7 @@
         <v>1.96</v>
       </c>
       <c r="U15" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V15" t="n">
         <v>1.25</v>
@@ -3336,7 +3336,7 @@
         <v>11</v>
       </c>
       <c r="Y15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z15" t="n">
         <v>34</v>
@@ -3357,7 +3357,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG15" t="n">
         <v>11</v>
@@ -3366,10 +3366,10 @@
         <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>370</v>
+        <v>90</v>
       </c>
       <c r="AJ15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK15" t="n">
         <v>24</v>
@@ -3381,68 +3381,68 @@
         <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP15" t="n">
         <v>9.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR15" t="n">
         <v>30</v>
       </c>
       <c r="AS15" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AT15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU15" t="n">
         <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC15" t="n">
         <v>20</v>
       </c>
       <c r="BD15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BE15" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG15" t="n">
         <v>14.5</v>
       </c>
-      <c r="BF15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>13</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>1.78</v>
       </c>
       <c r="G16" t="n">
-        <v>3.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H16" t="n">
         <v>2.12</v>
@@ -3488,7 +3488,7 @@
         <v>2.8</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3563,7 +3563,7 @@
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
         <v>1000</v>
@@ -3581,13 +3581,13 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.48</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AS16" t="n">
         <v>1.51</v>
@@ -3599,34 +3599,34 @@
         <v>4.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AW16" t="n">
         <v>1.51</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AY16" t="n">
         <v>1.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="BD16" t="n">
         <v>1.51</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="BF16" t="n">
         <v>5.2</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="G17" t="n">
-        <v>8.6</v>
+        <v>2.8</v>
       </c>
       <c r="H17" t="n">
-        <v>2.38</v>
+        <v>2.84</v>
       </c>
       <c r="I17" t="n">
         <v>12.5</v>
@@ -3691,7 +3691,7 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
         <v>1.01</v>
@@ -3700,25 +3700,25 @@
         <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
         <v>1.3</v>
       </c>
       <c r="W17" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="X17" t="n">
         <v>970</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -3876,10 +3876,10 @@
         <v>3.05</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L18" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="M18" t="n">
         <v>1.11</v>
@@ -3891,7 +3891,7 @@
         <v>1.47</v>
       </c>
       <c r="P18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q18" t="n">
         <v>2.46</v>
@@ -3903,7 +3903,7 @@
         <v>4.7</v>
       </c>
       <c r="T18" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U18" t="n">
         <v>1.95</v>
@@ -3966,7 +3966,7 @@
         <v>38</v>
       </c>
       <c r="AO18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP18" t="n">
         <v>8.199999999999999</v>
@@ -3975,7 +3975,7 @@
         <v>9.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS18" t="n">
         <v>50</v>
@@ -4002,19 +4002,19 @@
         <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="BB18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC18" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="BD18" t="n">
         <v>50</v>
       </c>
       <c r="BE18" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BF18" t="n">
         <v>32</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G19" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H19" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I19" t="n">
         <v>3.8</v>
@@ -4073,7 +4073,7 @@
         <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
         <v>1.04</v>
@@ -4085,19 +4085,19 @@
         <v>1.21</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R19" t="n">
         <v>1.57</v>
       </c>
       <c r="S19" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U19" t="n">
         <v>2.52</v>
@@ -4106,13 +4106,13 @@
         <v>1.36</v>
       </c>
       <c r="W19" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X19" t="n">
         <v>21</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z19" t="n">
         <v>30</v>
@@ -4121,13 +4121,13 @@
         <v>65</v>
       </c>
       <c r="AB19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE19" t="n">
         <v>38</v>
@@ -4139,7 +4139,7 @@
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AI19" t="n">
         <v>40</v>
@@ -4166,16 +4166,16 @@
         <v>19.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR19" t="n">
         <v>25</v>
       </c>
       <c r="AS19" t="n">
-        <v>13.5</v>
+        <v>50</v>
       </c>
       <c r="AT19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU19" t="n">
         <v>8.4</v>
@@ -4193,7 +4193,7 @@
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA19" t="n">
         <v>32</v>
@@ -4202,7 +4202,7 @@
         <v>22</v>
       </c>
       <c r="BC19" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD19" t="n">
         <v>24</v>
@@ -4211,14 +4211,14 @@
         <v>30</v>
       </c>
       <c r="BF19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>2.56</v>
       </c>
       <c r="H20" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I20" t="n">
         <v>3.95</v>
@@ -4273,7 +4273,7 @@
         <v>1.16</v>
       </c>
       <c r="N20" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
         <v>1.77</v>
@@ -4282,7 +4282,7 @@
         <v>1.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R20" t="n">
         <v>1.13</v>
@@ -4318,7 +4318,7 @@
         <v>6.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD20" t="n">
         <v>19</v>
@@ -4351,7 +4351,7 @@
         <v>500</v>
       </c>
       <c r="AN20" t="n">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="AO20" t="n">
         <v>500</v>
@@ -4405,14 +4405,14 @@
         <v>110</v>
       </c>
       <c r="BF20" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="BG20" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
         <v>3.7</v>
@@ -4470,7 +4470,7 @@
         <v>2.92</v>
       </c>
       <c r="O21" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P21" t="n">
         <v>1.61</v>
@@ -4482,7 +4482,7 @@
         <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T21" t="n">
         <v>2.08</v>
@@ -4494,7 +4494,7 @@
         <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="X21" t="n">
         <v>18</v>
@@ -4518,7 +4518,7 @@
         <v>18.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AF21" t="n">
         <v>11</v>
@@ -4530,7 +4530,7 @@
         <v>32</v>
       </c>
       <c r="AI21" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AJ21" t="n">
         <v>500</v>
@@ -4554,7 +4554,7 @@
         <v>9.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR21" t="n">
         <v>21</v>
@@ -4578,10 +4578,10 @@
         <v>9</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4593,20 +4593,20 @@
         <v>13</v>
       </c>
       <c r="BD21" t="n">
-        <v>42</v>
+        <v>6.6</v>
       </c>
       <c r="BE21" t="n">
         <v>28</v>
       </c>
       <c r="BF21" t="n">
-        <v>16</v>
+        <v>5.9</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G22" t="n">
         <v>2.12</v>
       </c>
       <c r="H22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I22" t="n">
         <v>4.4</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K22" t="n">
         <v>3.6</v>
@@ -4679,16 +4679,16 @@
         <v>4.4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U22" t="n">
         <v>1.92</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W22" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X22" t="n">
         <v>12</v>
@@ -4712,7 +4712,7 @@
         <v>18</v>
       </c>
       <c r="AE22" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF22" t="n">
         <v>12</v>
@@ -4727,7 +4727,7 @@
         <v>170</v>
       </c>
       <c r="AJ22" t="n">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="AK22" t="n">
         <v>27</v>
@@ -4781,7 +4781,7 @@
         <v>55</v>
       </c>
       <c r="BB22" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="BC22" t="n">
         <v>21</v>
@@ -4796,11 +4796,11 @@
         <v>18</v>
       </c>
       <c r="BG22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G23" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="H23" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="J23" t="n">
         <v>2.96</v>
       </c>
       <c r="K23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>1.46</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="G24" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="H24" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J24" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5073,61 +5073,61 @@
         <v>1.99</v>
       </c>
       <c r="V24" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W24" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="X24" t="n">
         <v>15.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z24" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA24" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>150</v>
+        <v>320</v>
       </c>
       <c r="AF24" t="n">
         <v>12.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
         <v>90</v>
       </c>
       <c r="AJ24" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AK24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL24" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM24" t="n">
-        <v>390</v>
+        <v>580</v>
       </c>
       <c r="AN24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO24" t="n">
         <v>100</v>
@@ -5136,7 +5136,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR24" t="n">
         <v>21</v>
@@ -5145,13 +5145,13 @@
         <v>38</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU24" t="n">
         <v>7.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW24" t="n">
         <v>30</v>
@@ -5184,11 +5184,11 @@
         <v>13</v>
       </c>
       <c r="BG24" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -5222,13 +5222,13 @@
         <v>1.39</v>
       </c>
       <c r="G25" t="n">
-        <v>4.1</v>
+        <v>2.28</v>
       </c>
       <c r="H25" t="n">
         <v>3.5</v>
       </c>
       <c r="I25" t="n">
-        <v>420</v>
+        <v>110</v>
       </c>
       <c r="J25" t="n">
         <v>3.45</v>
@@ -5270,7 +5270,7 @@
         <v>1.12</v>
       </c>
       <c r="W25" t="n">
-        <v>1.32</v>
+        <v>1.78</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5288,7 +5288,7 @@
         <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD25" t="n">
         <v>1000</v>
@@ -5339,7 +5339,7 @@
         <v>1.17</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AU25" t="n">
         <v>1.14</v>
@@ -5354,7 +5354,7 @@
         <v>1.17</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AZ25" t="n">
         <v>1.17</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -5419,16 +5419,16 @@
         <v>1.97</v>
       </c>
       <c r="H26" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I26" t="n">
         <v>5.1</v>
       </c>
       <c r="J26" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5440,7 +5440,7 @@
         <v>2.76</v>
       </c>
       <c r="O26" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P26" t="n">
         <v>1.59</v>
@@ -5449,16 +5449,16 @@
         <v>2.46</v>
       </c>
       <c r="R26" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S26" t="n">
-        <v>2.46</v>
+        <v>4.7</v>
       </c>
       <c r="T26" t="n">
         <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="V26" t="n">
         <v>1.24</v>
@@ -5467,7 +5467,7 @@
         <v>2.02</v>
       </c>
       <c r="X26" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Y26" t="n">
         <v>1000</v>
@@ -5479,10 +5479,10 @@
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD26" t="n">
         <v>1000</v>
@@ -5491,7 +5491,7 @@
         <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
         <v>500</v>
@@ -5524,13 +5524,13 @@
         <v>6.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AT26" t="n">
         <v>5.1</v>
@@ -5539,44 +5539,44 @@
         <v>6.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.26</v>
+        <v>3.95</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="AX26" t="n">
         <v>5.1</v>
       </c>
       <c r="AY26" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="BB26" t="n">
-        <v>2.24</v>
+        <v>3.85</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.28</v>
+        <v>2.9</v>
       </c>
       <c r="BD26" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.36</v>
+        <v>3.3</v>
       </c>
       <c r="BF26" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BG26" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -5607,19 +5607,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="G27" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H27" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I27" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J27" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K27" t="n">
         <v>3.2</v>
@@ -5640,7 +5640,7 @@
         <v>1.57</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R27" t="n">
         <v>1.2</v>
@@ -5652,13 +5652,13 @@
         <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V27" t="n">
         <v>1.35</v>
       </c>
       <c r="W27" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="X27" t="n">
         <v>9.199999999999999</v>
@@ -5673,10 +5673,10 @@
         <v>900</v>
       </c>
       <c r="AB27" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD27" t="n">
         <v>17</v>
@@ -5700,7 +5700,7 @@
         <v>38</v>
       </c>
       <c r="AK27" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AL27" t="n">
         <v>460</v>
@@ -5712,19 +5712,19 @@
         <v>36</v>
       </c>
       <c r="AO27" t="n">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AP27" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR27" t="n">
         <v>20</v>
       </c>
       <c r="AS27" t="n">
-        <v>65</v>
+        <v>9.6</v>
       </c>
       <c r="AT27" t="n">
         <v>6.6</v>
@@ -5736,7 +5736,7 @@
         <v>13.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>48</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX27" t="n">
         <v>12</v>
@@ -5748,29 +5748,29 @@
         <v>19</v>
       </c>
       <c r="BA27" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>30</v>
+        <v>8.4</v>
       </c>
       <c r="BC27" t="n">
-        <v>28</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE27" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF27" t="n">
-        <v>29</v>
+        <v>8.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>60</v>
+        <v>9.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="G28" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I28" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L28" t="n">
         <v>1.36</v>
@@ -5834,25 +5834,25 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R28" t="n">
         <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T28" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U28" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V28" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W28" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="X28" t="n">
         <v>15</v>
@@ -5861,25 +5861,25 @@
         <v>22</v>
       </c>
       <c r="Z28" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA28" t="n">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AB28" t="n">
         <v>8</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE28" t="n">
         <v>110</v>
       </c>
       <c r="AF28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG28" t="n">
         <v>9.800000000000001</v>
@@ -5888,10 +5888,10 @@
         <v>23</v>
       </c>
       <c r="AI28" t="n">
-        <v>95</v>
+        <v>230</v>
       </c>
       <c r="AJ28" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK28" t="n">
         <v>16.5</v>
@@ -5903,34 +5903,34 @@
         <v>180</v>
       </c>
       <c r="AN28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO28" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AP28" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR28" t="n">
         <v>48</v>
       </c>
       <c r="AS28" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU28" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW28" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AX28" t="n">
         <v>8.4</v>
@@ -5939,13 +5939,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA28" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BB28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC28" t="n">
         <v>15.5</v>
@@ -5957,14 +5957,14 @@
         <v>70</v>
       </c>
       <c r="BF28" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG28" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G29" t="n">
         <v>3.25</v>
@@ -6004,7 +6004,7 @@
         <v>2.52</v>
       </c>
       <c r="I29" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J29" t="n">
         <v>3.35</v>
@@ -6013,7 +6013,7 @@
         <v>3.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
         <v>1.09</v>
@@ -6022,7 +6022,7 @@
         <v>3.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P29" t="n">
         <v>1.73</v>
@@ -6031,10 +6031,10 @@
         <v>2.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S29" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T29" t="n">
         <v>1.91</v>
@@ -6043,7 +6043,7 @@
         <v>1.98</v>
       </c>
       <c r="V29" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W29" t="n">
         <v>1.44</v>
@@ -6079,7 +6079,7 @@
         <v>16</v>
       </c>
       <c r="AH29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI29" t="n">
         <v>55</v>
@@ -6097,7 +6097,7 @@
         <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AO29" t="n">
         <v>32</v>
@@ -6139,26 +6139,26 @@
         <v>42</v>
       </c>
       <c r="BB29" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC29" t="n">
         <v>18</v>
       </c>
       <c r="BD29" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE29" t="n">
         <v>38</v>
       </c>
       <c r="BF29" t="n">
-        <v>32</v>
+        <v>7.4</v>
       </c>
       <c r="BG29" t="n">
         <v>21</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -6189,28 +6189,28 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G30" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H30" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I30" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J30" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="K30" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="L30" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="M30" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N30" t="n">
         <v>2.46</v>
@@ -6219,10 +6219,10 @@
         <v>1.53</v>
       </c>
       <c r="P30" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
@@ -6231,16 +6231,16 @@
         <v>5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U30" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V30" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W30" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6255,10 +6255,10 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD30" t="n">
         <v>1000</v>
@@ -6297,62 +6297,62 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.13</v>
+        <v>2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.13</v>
+        <v>7</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.13</v>
+        <v>1.93</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.13</v>
+        <v>2</v>
       </c>
       <c r="AT30" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AU30" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.13</v>
+        <v>2.04</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.13</v>
+        <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.13</v>
+        <v>8</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.13</v>
+        <v>1.91</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.13</v>
+        <v>2</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.13</v>
+        <v>6.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.13</v>
+        <v>1.94</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.13</v>
+        <v>2</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.13</v>
+        <v>2</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.13</v>
+        <v>2</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.13</v>
+        <v>2</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -6386,19 +6386,19 @@
         <v>1.27</v>
       </c>
       <c r="G31" t="n">
-        <v>990</v>
+        <v>3.55</v>
       </c>
       <c r="H31" t="n">
         <v>4.1</v>
       </c>
       <c r="I31" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="J31" t="n">
         <v>3.6</v>
       </c>
       <c r="K31" t="n">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -6434,7 +6434,7 @@
         <v>1.08</v>
       </c>
       <c r="W31" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
         <v>3.8</v>
       </c>
       <c r="L32" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="M32" t="n">
         <v>1.08</v>
@@ -6670,10 +6670,10 @@
         <v>130</v>
       </c>
       <c r="AK32" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL32" t="n">
         <v>75</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>85</v>
       </c>
       <c r="AM32" t="n">
         <v>140</v>
@@ -6682,7 +6682,7 @@
         <v>85</v>
       </c>
       <c r="AO32" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AP32" t="n">
         <v>9.800000000000001</v>
@@ -6697,10 +6697,10 @@
         <v>19</v>
       </c>
       <c r="AT32" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV32" t="n">
         <v>9.199999999999999</v>
@@ -6712,13 +6712,13 @@
         <v>6.8</v>
       </c>
       <c r="AY32" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ32" t="n">
         <v>17</v>
       </c>
       <c r="BA32" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB32" t="n">
         <v>7.8</v>
@@ -6733,14 +6733,14 @@
         <v>7.8</v>
       </c>
       <c r="BF32" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG32" t="n">
         <v>13.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -6771,16 +6771,16 @@
         </is>
       </c>
       <c r="F33" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H33" t="n">
         <v>2.92</v>
       </c>
-      <c r="G33" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="H33" t="n">
-        <v>3</v>
-      </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J33" t="n">
         <v>3</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="G34" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H34" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I34" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J34" t="n">
         <v>4.3</v>
       </c>
       <c r="K34" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -6998,7 +6998,7 @@
         <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -7159,13 +7159,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G35" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H35" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I35" t="n">
         <v>2.04</v>
@@ -7183,16 +7183,16 @@
         <v>1.09</v>
       </c>
       <c r="N35" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O35" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P35" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R35" t="n">
         <v>1.27</v>
@@ -7216,34 +7216,34 @@
         <v>14</v>
       </c>
       <c r="Y35" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA35" t="n">
         <v>28</v>
       </c>
       <c r="AB35" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC35" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD35" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE35" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AF35" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AG35" t="n">
         <v>21</v>
       </c>
       <c r="AH35" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI35" t="n">
         <v>60</v>
@@ -7252,7 +7252,7 @@
         <v>130</v>
       </c>
       <c r="AK35" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
         <v>95</v>
@@ -7267,10 +7267,10 @@
         <v>22</v>
       </c>
       <c r="AP35" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR35" t="n">
         <v>10</v>
@@ -7285,13 +7285,13 @@
         <v>7.2</v>
       </c>
       <c r="AV35" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW35" t="n">
         <v>21</v>
       </c>
       <c r="AX35" t="n">
-        <v>4.9</v>
+        <v>28</v>
       </c>
       <c r="AY35" t="n">
         <v>15.5</v>
@@ -7300,29 +7300,29 @@
         <v>19</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BC35" t="n">
-        <v>55</v>
+        <v>5.8</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF35" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BG35" t="n">
         <v>17</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -7353,19 +7353,19 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G36" t="n">
         <v>2.24</v>
       </c>
       <c r="H36" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I36" t="n">
         <v>4.1</v>
       </c>
       <c r="J36" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K36" t="n">
         <v>3.55</v>
@@ -7374,7 +7374,7 @@
         <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N36" t="n">
         <v>4.2</v>
@@ -7386,7 +7386,7 @@
         <v>2.08</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R36" t="n">
         <v>1.43</v>
@@ -7398,40 +7398,40 @@
         <v>1.68</v>
       </c>
       <c r="U36" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V36" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W36" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X36" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z36" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA36" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AB36" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE36" t="n">
         <v>48</v>
       </c>
       <c r="AF36" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG36" t="n">
         <v>12</v>
@@ -7440,49 +7440,49 @@
         <v>15.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL36" t="n">
         <v>34</v>
       </c>
-      <c r="AK36" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>32</v>
-      </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN36" t="n">
         <v>17</v>
       </c>
       <c r="AO36" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AP36" t="n">
-        <v>14</v>
+        <v>5.7</v>
       </c>
       <c r="AQ36" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="AS36" t="n">
-        <v>50</v>
+        <v>7.2</v>
       </c>
       <c r="AT36" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU36" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV36" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX36" t="n">
         <v>13.5</v>
@@ -7491,32 +7491,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ36" t="n">
-        <v>13.5</v>
+        <v>5.7</v>
       </c>
       <c r="BA36" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB36" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC36" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD36" t="n">
         <v>24</v>
       </c>
       <c r="BE36" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF36" t="n">
         <v>13</v>
       </c>
       <c r="BG36" t="n">
-        <v>30</v>
+        <v>6.6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-01 21:20:38</t>
+          <t>2026-04-01 23:36:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G2" t="n">
         <v>2.54</v>
       </c>
-      <c r="G2" t="n">
-        <v>2.56</v>
-      </c>
       <c r="H2" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I2" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
         <v>4.4</v>
@@ -787,31 +787,31 @@
         <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="R2" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="S2" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="U2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W2" t="n">
         <v>1.64</v>
       </c>
       <c r="X2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y2" t="n">
         <v>24</v>
@@ -820,7 +820,7 @@
         <v>26</v>
       </c>
       <c r="AA2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB2" t="n">
         <v>24</v>
@@ -838,10 +838,10 @@
         <v>26</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI2" t="n">
         <v>24</v>
@@ -856,25 +856,25 @@
         <v>24</v>
       </c>
       <c r="AM2" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AO2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AP2" t="n">
         <v>34</v>
       </c>
       <c r="AQ2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR2" t="n">
         <v>23</v>
       </c>
       <c r="AS2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT2" t="n">
         <v>21</v>
@@ -910,17 +910,17 @@
         <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -960,13 +960,13 @@
         <v>2.3</v>
       </c>
       <c r="I3" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J3" t="n">
         <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>1.36</v>
@@ -975,49 +975,49 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U3" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X3" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
         <v>30</v>
       </c>
       <c r="AB3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC3" t="n">
         <v>8.199999999999999</v>
@@ -1035,34 +1035,34 @@
         <v>14</v>
       </c>
       <c r="AH3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI3" t="n">
         <v>32</v>
       </c>
       <c r="AJ3" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="n">
         <v>34</v>
       </c>
       <c r="AL3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM3" t="n">
         <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR3" t="n">
         <v>14.5</v>
@@ -1071,10 +1071,10 @@
         <v>27</v>
       </c>
       <c r="AT3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
         <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
         <v>14</v>
@@ -1101,20 +1101,20 @@
         <v>30</v>
       </c>
       <c r="BD3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BF3" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BG3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -1145,76 +1145,76 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="I4" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="R4" t="n">
         <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U4" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="W4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X4" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y4" t="n">
         <v>12.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4" t="n">
         <v>12</v>
@@ -1235,10 +1235,10 @@
         <v>36</v>
       </c>
       <c r="AJ4" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL4" t="n">
         <v>44</v>
@@ -1247,10 +1247,10 @@
         <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO4" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AP4" t="n">
         <v>14.5</v>
@@ -1262,10 +1262,10 @@
         <v>13.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AT4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU4" t="n">
         <v>7.2</v>
@@ -1277,7 +1277,7 @@
         <v>19.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
         <v>11.5</v>
@@ -1286,29 +1286,29 @@
         <v>13</v>
       </c>
       <c r="BA4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="BG4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -1339,70 +1339,70 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="G5" t="n">
         <v>6.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="I5" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
         <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
         <v>1.75</v>
       </c>
       <c r="U5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V5" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="W5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X5" t="n">
         <v>500</v>
       </c>
       <c r="Y5" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>29</v>
       </c>
       <c r="AB5" t="n">
         <v>950</v>
@@ -1411,10 +1411,10 @@
         <v>17.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
         <v>500</v>
@@ -1423,7 +1423,7 @@
         <v>950</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AI5" t="n">
         <v>500</v>
@@ -1447,62 +1447,62 @@
         <v>29</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV5" t="n">
         <v>5.8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>5</v>
       </c>
       <c r="AW5" t="n">
         <v>7.6</v>
       </c>
       <c r="AX5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC5" t="n">
         <v>5.6</v>
       </c>
-      <c r="AY5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BD5" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="BG5" t="n">
         <v>7.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -1533,67 +1533,67 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="G6" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P6" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
         <v>4.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="U6" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1608,25 +1608,25 @@
         <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AF6" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="AG6" t="n">
         <v>21</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1641,28 +1641,28 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
         <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AU6" t="n">
         <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AX6" t="n">
         <v>8.6</v>
@@ -1674,7 +1674,7 @@
         <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BB6" t="n">
         <v>10.5</v>
@@ -1683,20 +1683,20 @@
         <v>11.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.4</v>
+        <v>3.95</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -1727,58 +1727,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G7" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S7" t="n">
         <v>3.2</v>
       </c>
-      <c r="J7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.88</v>
-      </c>
       <c r="T7" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="U7" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1793,7 +1793,7 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
         <v>14</v>
@@ -1808,13 +1808,13 @@
         <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AI7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
         <v>440</v>
@@ -1835,19 +1835,19 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>6.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU7" t="n">
         <v>4.9</v>
@@ -1856,41 +1856,41 @@
         <v>6.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AZ7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC7" t="n">
         <v>4.7</v>
       </c>
-      <c r="BA7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BD7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BF7" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -1921,43 +1921,43 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="G8" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="I8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N8" t="n">
         <v>3.05</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3</v>
       </c>
       <c r="O8" t="n">
         <v>1.42</v>
       </c>
       <c r="P8" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
         <v>4.2</v>
@@ -1969,10 +1969,10 @@
         <v>1.94</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X8" t="n">
         <v>11.5</v>
@@ -2002,10 +2002,10 @@
         <v>75</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="AH8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AI8" t="n">
         <v>390</v>
@@ -2014,16 +2014,16 @@
         <v>210</v>
       </c>
       <c r="AK8" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="AL8" t="n">
-        <v>370</v>
+        <v>270</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AO8" t="n">
         <v>500</v>
@@ -2038,7 +2038,7 @@
         <v>9</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT8" t="n">
         <v>8</v>
@@ -2050,7 +2050,7 @@
         <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.4</v>
+        <v>17.5</v>
       </c>
       <c r="AX8" t="n">
         <v>7.8</v>
@@ -2062,29 +2062,29 @@
         <v>13</v>
       </c>
       <c r="BA8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF8" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BG8" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -2115,94 +2115,94 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="G9" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="H9" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="I9" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J9" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="K9" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="S9" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U9" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="V9" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W9" t="n">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="X9" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB9" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AC9" t="n">
-        <v>46</v>
+        <v>12.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG9" t="n">
         <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI9" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
         <v>36</v>
@@ -2214,71 +2214,71 @@
         <v>25</v>
       </c>
       <c r="AM9" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AV9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW9" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="AY9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BB9" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -2309,58 +2309,58 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="H10" t="n">
-        <v>1.02</v>
+        <v>1.93</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1.09</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>5.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
         <v>1.14</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3</v>
+        <v>2.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="S10" t="n">
-        <v>1.13</v>
+        <v>1.94</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>2.62</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2369,19 +2369,19 @@
         <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
@@ -2414,65 +2414,65 @@
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -2503,58 +2503,58 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="H11" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M11" t="n">
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="P11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U11" t="n">
         <v>2.08</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.11</v>
       </c>
       <c r="V11" t="n">
         <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>2.16</v>
+        <v>2.92</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2584,7 +2584,7 @@
         <v>500</v>
       </c>
       <c r="AG11" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AH11" t="n">
         <v>1000</v>
@@ -2593,10 +2593,10 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AK11" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2605,13 +2605,13 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.3</v>
+        <v>8.4</v>
       </c>
       <c r="AQ11" t="n">
         <v>4.2</v>
@@ -2623,10 +2623,10 @@
         <v>4.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.28</v>
+        <v>9.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.31</v>
+        <v>7</v>
       </c>
       <c r="AV11" t="n">
         <v>4.2</v>
@@ -2635,38 +2635,38 @@
         <v>4.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.3</v>
+        <v>3.35</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.29</v>
+        <v>2.7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.35</v>
+        <v>2.02</v>
       </c>
       <c r="BA11" t="n">
         <v>4.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.32</v>
+        <v>2.82</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.32</v>
+        <v>2.24</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.33</v>
+        <v>2.16</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.35</v>
+        <v>3.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.62</v>
+        <v>4</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="G12" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>2.62</v>
+        <v>5.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="S12" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="T12" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U12" t="n">
         <v>2.32</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="W12" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="X12" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="Y12" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="Z12" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AC12" t="n">
-        <v>500</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>950</v>
+        <v>20</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF12" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AO12" t="n">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.31</v>
+        <v>20</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.33</v>
+        <v>20</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.34</v>
+        <v>10</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.35</v>
+        <v>12</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.31</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.34</v>
+        <v>17</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.35</v>
+        <v>11</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.32</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.35</v>
+        <v>10.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.34</v>
+        <v>15.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.33</v>
+        <v>14</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.34</v>
+        <v>16</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.35</v>
+        <v>11.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.22</v>
+        <v>6.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.55</v>
+        <v>10.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.02</v>
+        <v>1.77</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.02</v>
+        <v>2.12</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="J13" t="n">
-        <v>1.09</v>
+        <v>2.44</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2927,7 +2927,7 @@
         <v>1.16</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
         <v>1.15</v>
@@ -2939,10 +2939,10 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="G15" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J15" t="n">
         <v>3.35</v>
@@ -3297,7 +3297,7 @@
         <v>3.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="M15" t="n">
         <v>1.1</v>
@@ -3309,52 +3309,52 @@
         <v>1.41</v>
       </c>
       <c r="P15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="U15" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V15" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W15" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="X15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y15" t="n">
         <v>15</v>
       </c>
       <c r="Z15" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AA15" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AE15" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF15" t="n">
         <v>11</v>
@@ -3366,13 +3366,13 @@
         <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="AJ15" t="n">
         <v>22</v>
       </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
         <v>48</v>
@@ -3381,25 +3381,25 @@
         <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO15" t="n">
         <v>110</v>
       </c>
       <c r="AP15" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS15" t="n">
-        <v>28</v>
+        <v>14.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU15" t="n">
         <v>7</v>
@@ -3408,41 +3408,41 @@
         <v>18</v>
       </c>
       <c r="AW15" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA15" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="BB15" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC15" t="n">
         <v>20</v>
       </c>
       <c r="BD15" t="n">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="BE15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -3473,46 +3473,46 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>8.800000000000001</v>
+        <v>2.54</v>
       </c>
       <c r="H16" t="n">
-        <v>2.12</v>
+        <v>2.96</v>
       </c>
       <c r="I16" t="n">
-        <v>12.5</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>1.36</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P16" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.3</v>
+        <v>1.98</v>
       </c>
       <c r="R16" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>3.45</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -3521,10 +3521,10 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W16" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3581,16 +3581,16 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="AT16" t="n">
         <v>5.8</v>
@@ -3599,34 +3599,34 @@
         <v>4.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="BF16" t="n">
         <v>5.2</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
         <v>2.8</v>
@@ -3700,13 +3700,13 @@
         <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -3861,37 +3861,37 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="G18" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="H18" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K18" t="n">
         <v>3.15</v>
       </c>
       <c r="L18" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="M18" t="n">
         <v>1.11</v>
       </c>
       <c r="N18" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P18" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q18" t="n">
         <v>2.46</v>
@@ -3900,46 +3900,46 @@
         <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T18" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U18" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="X18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC18" t="n">
         <v>6.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE18" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF18" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG18" t="n">
         <v>13</v>
@@ -3948,64 +3948,64 @@
         <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ18" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AK18" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL18" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM18" t="n">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="AN18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO18" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR18" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU18" t="n">
         <v>6</v>
       </c>
       <c r="AV18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY18" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA18" t="n">
         <v>55</v>
       </c>
       <c r="BB18" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BC18" t="n">
         <v>32</v>
@@ -4014,17 +4014,17 @@
         <v>50</v>
       </c>
       <c r="BE18" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BF18" t="n">
         <v>32</v>
       </c>
       <c r="BG18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -4058,70 +4058,70 @@
         <v>2.08</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H19" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J19" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
         <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
         <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O19" t="n">
         <v>1.21</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R19" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S19" t="n">
         <v>2.6</v>
       </c>
       <c r="T19" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="U19" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="V19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X19" t="n">
         <v>21</v>
       </c>
       <c r="Y19" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA19" t="n">
         <v>65</v>
       </c>
       <c r="AB19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC19" t="n">
         <v>9.4</v>
@@ -4130,7 +4130,7 @@
         <v>15</v>
       </c>
       <c r="AE19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF19" t="n">
         <v>15.5</v>
@@ -4139,25 +4139,25 @@
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI19" t="n">
         <v>40</v>
       </c>
       <c r="AJ19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK19" t="n">
         <v>19</v>
       </c>
       <c r="AL19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AM19" t="n">
         <v>65</v>
       </c>
       <c r="AN19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO19" t="n">
         <v>27</v>
@@ -4166,19 +4166,19 @@
         <v>19.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS19" t="n">
         <v>50</v>
       </c>
       <c r="AT19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV19" t="n">
         <v>14</v>
@@ -4187,38 +4187,38 @@
         <v>30</v>
       </c>
       <c r="AX19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY19" t="n">
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC19" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE19" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BF19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG19" t="n">
         <v>24</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -4249,170 +4249,170 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.46</v>
+        <v>2.82</v>
       </c>
       <c r="G20" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="H20" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="I20" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="J20" t="n">
         <v>2.88</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L20" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="M20" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="N20" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="O20" t="n">
         <v>1.77</v>
       </c>
       <c r="P20" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
         <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="T20" t="n">
         <v>2.52</v>
       </c>
       <c r="U20" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V20" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="X20" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE20" t="n">
         <v>170</v>
       </c>
       <c r="AF20" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AG20" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI20" t="n">
         <v>540</v>
       </c>
       <c r="AJ20" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AK20" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AL20" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="AM20" t="n">
         <v>500</v>
       </c>
       <c r="AN20" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AO20" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AP20" t="n">
         <v>6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AR20" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU20" t="n">
         <v>6.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AX20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY20" t="n">
         <v>12</v>
       </c>
       <c r="AZ20" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BA20" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB20" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="BC20" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BD20" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BE20" t="n">
         <v>110</v>
       </c>
       <c r="BF20" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BG20" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -4443,61 +4443,61 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I21" t="n">
         <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O21" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="P21" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R21" t="n">
         <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="T21" t="n">
         <v>2.08</v>
       </c>
       <c r="U21" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="V21" t="n">
         <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X21" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="Y21" t="n">
         <v>12</v>
@@ -4521,7 +4521,7 @@
         <v>160</v>
       </c>
       <c r="AF21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG21" t="n">
         <v>11.5</v>
@@ -4545,22 +4545,22 @@
         <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AO21" t="n">
         <v>500</v>
       </c>
       <c r="AP21" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR21" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT21" t="n">
         <v>6.6</v>
@@ -4569,10 +4569,10 @@
         <v>6.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
         <v>9</v>
@@ -4581,7 +4581,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4593,20 +4593,20 @@
         <v>13</v>
       </c>
       <c r="BD21" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE21" t="n">
         <v>28</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -4643,25 +4643,25 @@
         <v>2.12</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I22" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
         <v>1.43</v>
@@ -4670,13 +4670,13 @@
         <v>1.72</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R22" t="n">
         <v>1.27</v>
       </c>
       <c r="S22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T22" t="n">
         <v>1.99</v>
@@ -4685,37 +4685,37 @@
         <v>1.92</v>
       </c>
       <c r="V22" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W22" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y22" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Z22" t="n">
         <v>32</v>
       </c>
       <c r="AA22" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AB22" t="n">
         <v>7.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD22" t="n">
         <v>18</v>
       </c>
       <c r="AE22" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG22" t="n">
         <v>10.5</v>
@@ -4724,83 +4724,83 @@
         <v>22</v>
       </c>
       <c r="AI22" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL22" t="n">
-        <v>290</v>
+        <v>48</v>
       </c>
       <c r="AM22" t="n">
-        <v>580</v>
+        <v>150</v>
       </c>
       <c r="AN22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO22" t="n">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="AP22" t="n">
         <v>10</v>
       </c>
       <c r="AQ22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS22" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW22" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>50</v>
       </c>
       <c r="AX22" t="n">
         <v>10.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ22" t="n">
         <v>18.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>55</v>
+        <v>14.5</v>
       </c>
       <c r="BB22" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC22" t="n">
         <v>22</v>
       </c>
-      <c r="BC22" t="n">
-        <v>21</v>
-      </c>
       <c r="BD22" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="BE22" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="BF22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G23" t="n">
         <v>2.5</v>
       </c>
       <c r="H23" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I23" t="n">
         <v>3.85</v>
@@ -4846,7 +4846,7 @@
         <v>2.96</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>1.46</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G24" t="n">
         <v>1.95</v>
@@ -5034,52 +5034,52 @@
         <v>4.4</v>
       </c>
       <c r="I24" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K24" t="n">
         <v>3.95</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P24" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="R24" t="n">
         <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="T24" t="n">
         <v>1.89</v>
       </c>
       <c r="U24" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W24" t="n">
         <v>2.04</v>
       </c>
       <c r="X24" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y24" t="n">
         <v>17</v>
@@ -5115,7 +5115,7 @@
         <v>90</v>
       </c>
       <c r="AJ24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK24" t="n">
         <v>24</v>
@@ -5130,7 +5130,7 @@
         <v>16</v>
       </c>
       <c r="AO24" t="n">
-        <v>100</v>
+        <v>270</v>
       </c>
       <c r="AP24" t="n">
         <v>11.5</v>
@@ -5145,7 +5145,7 @@
         <v>38</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU24" t="n">
         <v>7.8</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="G25" t="n">
-        <v>2.28</v>
+        <v>1.74</v>
       </c>
       <c r="H25" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I25" t="n">
         <v>110</v>
@@ -5237,28 +5237,28 @@
         <v>11.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>1.1</v>
+        <v>2.36</v>
       </c>
       <c r="O25" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>1.2</v>
+        <v>2.32</v>
       </c>
       <c r="T25" t="n">
         <v>1.11</v>
@@ -5270,7 +5270,7 @@
         <v>1.12</v>
       </c>
       <c r="W25" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5321,58 +5321,58 @@
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT25" t="n">
         <v>1.16</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AU25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY25" t="n">
         <v>1.17</v>
       </c>
-      <c r="AR25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AZ25" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BF25" t="n">
         <v>2.18</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -5413,170 +5413,170 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G26" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="H26" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I26" t="n">
         <v>5.1</v>
       </c>
       <c r="J26" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
         <v>3.75</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M26" t="n">
         <v>1.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="O26" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P26" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="T26" t="n">
         <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="V26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W26" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X26" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC26" t="n">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG26" t="n">
-        <v>500</v>
+        <v>11.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS26" t="n">
         <v>9</v>
       </c>
-      <c r="AR26" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AT26" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV26" t="n">
-        <v>3.95</v>
+        <v>16.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX26" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AY26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD26" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AZ26" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BE26" t="n">
-        <v>3.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF26" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>2.18</v>
+        <v>9</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -5607,31 +5607,31 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G27" t="n">
         <v>2.44</v>
       </c>
       <c r="H27" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I27" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J27" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K27" t="n">
         <v>3.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M27" t="n">
         <v>1.12</v>
       </c>
       <c r="N27" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="O27" t="n">
         <v>1.53</v>
@@ -5640,13 +5640,13 @@
         <v>1.57</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="R27" t="n">
         <v>1.2</v>
       </c>
       <c r="S27" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T27" t="n">
         <v>2.06</v>
@@ -5655,7 +5655,7 @@
         <v>1.78</v>
       </c>
       <c r="V27" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W27" t="n">
         <v>1.69</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -5801,16 +5801,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G28" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H28" t="n">
+        <v>7</v>
+      </c>
+      <c r="I28" t="n">
         <v>7.2</v>
-      </c>
-      <c r="I28" t="n">
-        <v>7.4</v>
       </c>
       <c r="J28" t="n">
         <v>4.3</v>
@@ -5819,40 +5819,40 @@
         <v>4.5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M28" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
         <v>1.31</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R28" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
         <v>3.35</v>
       </c>
       <c r="T28" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
         <v>1.94</v>
       </c>
       <c r="V28" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W28" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="X28" t="n">
         <v>15</v>
@@ -5873,7 +5873,7 @@
         <v>9.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AE28" t="n">
         <v>110</v>
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="AG28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH28" t="n">
         <v>23</v>
       </c>
       <c r="AI28" t="n">
-        <v>230</v>
+        <v>100</v>
       </c>
       <c r="AJ28" t="n">
         <v>14.5</v>
@@ -5897,16 +5897,16 @@
         <v>16.5</v>
       </c>
       <c r="AL28" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM28" t="n">
         <v>180</v>
       </c>
       <c r="AN28" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO28" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AP28" t="n">
         <v>14.5</v>
@@ -5921,7 +5921,7 @@
         <v>65</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU28" t="n">
         <v>8.800000000000001</v>
@@ -5942,29 +5942,29 @@
         <v>22</v>
       </c>
       <c r="BA28" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="BB28" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC28" t="n">
         <v>15.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE28" t="n">
         <v>70</v>
       </c>
       <c r="BF28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -6001,43 +6001,43 @@
         <v>3.25</v>
       </c>
       <c r="H29" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I29" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J29" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K29" t="n">
         <v>3.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M29" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O29" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P29" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R29" t="n">
         <v>1.27</v>
       </c>
       <c r="S29" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T29" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U29" t="n">
         <v>1.98</v>
@@ -6049,37 +6049,37 @@
         <v>1.44</v>
       </c>
       <c r="X29" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB29" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z29" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>11</v>
-      </c>
       <c r="AC29" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD29" t="n">
         <v>12</v>
       </c>
       <c r="AE29" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF29" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AG29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI29" t="n">
         <v>55</v>
@@ -6088,77 +6088,77 @@
         <v>60</v>
       </c>
       <c r="AK29" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AL29" t="n">
         <v>60</v>
       </c>
       <c r="AM29" t="n">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="AN29" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB29" t="n">
         <v>50</v>
       </c>
-      <c r="AO29" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BC29" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="BD29" t="n">
-        <v>7.4</v>
+        <v>50</v>
       </c>
       <c r="BE29" t="n">
         <v>38</v>
       </c>
       <c r="BF29" t="n">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="BG29" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -6192,55 +6192,55 @@
         <v>2.34</v>
       </c>
       <c r="G30" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="H30" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I30" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="K30" t="n">
         <v>3.1</v>
       </c>
       <c r="L30" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M30" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N30" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="O30" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="P30" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U30" t="n">
         <v>1.74</v>
       </c>
       <c r="V30" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W30" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6297,16 +6297,16 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ30" t="n">
         <v>7</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AS30" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AT30" t="n">
         <v>5</v>
@@ -6318,7 +6318,7 @@
         <v>2.04</v>
       </c>
       <c r="AW30" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AX30" t="n">
         <v>8.800000000000001</v>
@@ -6327,32 +6327,32 @@
         <v>8</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="BA30" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="BB30" t="n">
         <v>6.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="BD30" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="BE30" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="BF30" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="BG30" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="G31" t="n">
-        <v>3.55</v>
+        <v>1.56</v>
       </c>
       <c r="H31" t="n">
         <v>4.1</v>
@@ -6398,31 +6398,31 @@
         <v>3.6</v>
       </c>
       <c r="K31" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N31" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="O31" t="n">
         <v>1.14</v>
       </c>
       <c r="P31" t="n">
-        <v>1.31</v>
+        <v>1.66</v>
       </c>
       <c r="Q31" t="n">
         <v>1.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.18</v>
+        <v>1.63</v>
       </c>
       <c r="S31" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="T31" t="n">
         <v>1.11</v>
@@ -6434,7 +6434,7 @@
         <v>1.08</v>
       </c>
       <c r="W31" t="n">
-        <v>1.39</v>
+        <v>2.1</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -6485,7 +6485,7 @@
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -6580,28 +6580,28 @@
         <v>4.5</v>
       </c>
       <c r="G32" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H32" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J32" t="n">
         <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L32" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M32" t="n">
         <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="O32" t="n">
         <v>1.37</v>
@@ -6610,25 +6610,25 @@
         <v>1.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="R32" t="n">
         <v>1.31</v>
       </c>
       <c r="S32" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T32" t="n">
         <v>1.92</v>
       </c>
       <c r="U32" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V32" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X32" t="n">
         <v>15</v>
@@ -6655,7 +6655,7 @@
         <v>23</v>
       </c>
       <c r="AF32" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG32" t="n">
         <v>19.5</v>
@@ -6667,7 +6667,7 @@
         <v>42</v>
       </c>
       <c r="AJ32" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK32" t="n">
         <v>70</v>
@@ -6679,7 +6679,7 @@
         <v>140</v>
       </c>
       <c r="AN32" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
         <v>16.5</v>
@@ -6709,7 +6709,7 @@
         <v>18.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY32" t="n">
         <v>16.5</v>
@@ -6721,26 +6721,26 @@
         <v>7</v>
       </c>
       <c r="BB32" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF32" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>7.6</v>
       </c>
       <c r="BG32" t="n">
         <v>13.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -6771,16 +6771,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
         <v>3.05</v>
       </c>
       <c r="H33" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I33" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
         <v>3</v>
@@ -6804,7 +6804,7 @@
         <v>1.46</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G34" t="n">
         <v>1.57</v>
       </c>
       <c r="H34" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I34" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J34" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K34" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -6995,10 +6995,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -7159,46 +7159,46 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G35" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H35" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J35" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K35" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L35" t="n">
         <v>1.49</v>
       </c>
       <c r="M35" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N35" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O35" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P35" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R35" t="n">
         <v>1.27</v>
       </c>
       <c r="S35" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T35" t="n">
         <v>2</v>
@@ -7207,122 +7207,122 @@
         <v>1.91</v>
       </c>
       <c r="V35" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W35" t="n">
         <v>1.27</v>
       </c>
       <c r="X35" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB35" t="n">
         <v>14</v>
       </c>
-      <c r="Y35" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>16</v>
-      </c>
       <c r="AC35" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD35" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE35" t="n">
         <v>24</v>
       </c>
       <c r="AF35" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG35" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH35" t="n">
         <v>22</v>
       </c>
       <c r="AI35" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AJ35" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL35" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN35" t="n">
         <v>95</v>
       </c>
-      <c r="AM35" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>110</v>
-      </c>
       <c r="AO35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP35" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR35" t="n">
         <v>10</v>
       </c>
       <c r="AS35" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AT35" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU35" t="n">
         <v>7.2</v>
       </c>
       <c r="AV35" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW35" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX35" t="n">
         <v>28</v>
       </c>
       <c r="AY35" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AZ35" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.7</v>
+        <v>36</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="BC35" t="n">
-        <v>5.8</v>
+        <v>55</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.8</v>
+        <v>65</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.9</v>
+        <v>12.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="BG35" t="n">
         <v>17</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G36" t="n">
         <v>2.24</v>
@@ -7362,46 +7362,46 @@
         <v>3.8</v>
       </c>
       <c r="I36" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K36" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M36" t="n">
         <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O36" t="n">
         <v>1.28</v>
       </c>
       <c r="P36" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R36" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S36" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T36" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U36" t="n">
         <v>2.34</v>
       </c>
       <c r="V36" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W36" t="n">
         <v>1.8</v>
@@ -7428,13 +7428,13 @@
         <v>19</v>
       </c>
       <c r="AE36" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF36" t="n">
         <v>15.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH36" t="n">
         <v>15.5</v>
@@ -7443,34 +7443,34 @@
         <v>60</v>
       </c>
       <c r="AJ36" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK36" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL36" t="n">
         <v>34</v>
       </c>
       <c r="AM36" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN36" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AO36" t="n">
         <v>48</v>
       </c>
       <c r="AP36" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AQ36" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS36" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT36" t="n">
         <v>9.800000000000001</v>
@@ -7482,7 +7482,7 @@
         <v>14.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX36" t="n">
         <v>13.5</v>
@@ -7491,32 +7491,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ36" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BA36" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BB36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC36" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC36" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BD36" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BE36" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF36" t="n">
         <v>13</v>
       </c>
       <c r="BG36" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G37" t="n">
         <v>1000</v>
@@ -7565,28 +7565,28 @@
         <v>950</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M37" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N37" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="O37" t="n">
         <v>1.39</v>
       </c>
       <c r="P37" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="Q37" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S37" t="n">
         <v>1.39</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1.38</v>
       </c>
       <c r="T37" t="n">
         <v>1.11</v>
@@ -7598,7 +7598,7 @@
         <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-01 23:36:16</t>
+          <t>2026-04-02 01:54:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="H2" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K2" t="n">
         <v>4.4</v>
@@ -787,46 +787,46 @@
         <v>1.12</v>
       </c>
       <c r="P2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U2" t="n">
         <v>3.35</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3.3</v>
-      </c>
       <c r="V2" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W2" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="X2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="Y2" t="n">
         <v>24</v>
       </c>
       <c r="Z2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
         <v>40</v>
       </c>
       <c r="AB2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
         <v>13.5</v>
@@ -838,46 +838,46 @@
         <v>26</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI2" t="n">
         <v>24</v>
       </c>
       <c r="AJ2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL2" t="n">
         <v>24</v>
       </c>
       <c r="AM2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AQ2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR2" t="n">
         <v>23</v>
       </c>
       <c r="AS2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU2" t="n">
         <v>11</v>
@@ -889,38 +889,38 @@
         <v>20</v>
       </c>
       <c r="AX2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
         <v>34</v>
       </c>
       <c r="BC2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE2" t="n">
         <v>34</v>
       </c>
       <c r="BF2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG2" t="n">
         <v>9</v>
       </c>
-      <c r="BG2" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -957,79 +957,79 @@
         <v>3.4</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="I3" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S3" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="T3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U3" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V3" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X3" t="n">
         <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
         <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB3" t="n">
         <v>16.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
         <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG3" t="n">
         <v>14</v>
@@ -1038,7 +1038,7 @@
         <v>15.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ3" t="n">
         <v>55</v>
@@ -1047,16 +1047,16 @@
         <v>34</v>
       </c>
       <c r="AL3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN3" t="n">
         <v>26</v>
       </c>
       <c r="AO3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP3" t="n">
         <v>18</v>
@@ -1068,19 +1068,19 @@
         <v>14.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT3" t="n">
         <v>15</v>
       </c>
       <c r="AU3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV3" t="n">
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX3" t="n">
         <v>23</v>
@@ -1092,7 +1092,7 @@
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BB3" t="n">
         <v>48</v>
@@ -1101,20 +1101,20 @@
         <v>30</v>
       </c>
       <c r="BD3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF3" t="n">
         <v>23</v>
       </c>
       <c r="BG3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G4" t="n">
         <v>3.1</v>
       </c>
-      <c r="G4" t="n">
-        <v>3.6</v>
-      </c>
       <c r="H4" t="n">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
         <v>1.37</v>
@@ -1169,103 +1169,103 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="T4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U4" t="n">
         <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="X4" t="n">
         <v>17.5</v>
       </c>
       <c r="Y4" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD4" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA4" t="n">
+      <c r="AE4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK4" t="n">
         <v>32</v>
       </c>
-      <c r="AB4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>38</v>
-      </c>
       <c r="AL4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AO4" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
         <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AS4" t="n">
         <v>14</v>
       </c>
       <c r="AT4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU4" t="n">
         <v>7.2</v>
@@ -1274,13 +1274,13 @@
         <v>9.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AX4" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>13</v>
@@ -1289,7 +1289,7 @@
         <v>16.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BC4" t="n">
         <v>18.5</v>
@@ -1301,14 +1301,14 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF4" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -1339,67 +1339,67 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="G5" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="I5" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="R5" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U5" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="W5" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y5" t="n">
         <v>500</v>
       </c>
-      <c r="Y5" t="n">
-        <v>21</v>
-      </c>
       <c r="Z5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA5" t="n">
         <v>29</v>
@@ -1408,22 +1408,22 @@
         <v>950</v>
       </c>
       <c r="AC5" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AD5" t="n">
         <v>19</v>
       </c>
       <c r="AE5" t="n">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
         <v>500</v>
       </c>
       <c r="AG5" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AH5" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI5" t="n">
         <v>500</v>
@@ -1444,34 +1444,34 @@
         <v>700</v>
       </c>
       <c r="AO5" t="n">
-        <v>29</v>
+        <v>6.8</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AX5" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AY5" t="n">
         <v>10</v>
@@ -1480,29 +1480,29 @@
         <v>7.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H6" t="n">
         <v>4.4</v>
@@ -1554,31 +1554,31 @@
         <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q6" t="n">
         <v>2.24</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="U6" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V6" t="n">
         <v>1.27</v>
@@ -1587,7 +1587,7 @@
         <v>1.9</v>
       </c>
       <c r="X6" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="Y6" t="n">
         <v>24</v>
@@ -1599,16 +1599,16 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC6" t="n">
         <v>14</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
         <v>19</v>
@@ -1626,7 +1626,7 @@
         <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1641,40 +1641,40 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
         <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU6" t="n">
         <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="AX6" t="n">
         <v>8.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AZ6" t="n">
         <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BB6" t="n">
         <v>10.5</v>
@@ -1686,17 +1686,17 @@
         <v>10</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BF6" t="n">
         <v>4.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -1727,58 +1727,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H7" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I7" t="n">
         <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
         <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="U7" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
         <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1811,7 +1811,7 @@
         <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
@@ -1844,7 +1844,7 @@
         <v>8.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
         <v>6.2</v>
@@ -1856,41 +1856,41 @@
         <v>6.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="AY7" t="n">
         <v>6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="BD7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE7" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -1921,55 +1921,55 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G8" t="n">
         <v>2.86</v>
       </c>
       <c r="H8" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P8" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q8" t="n">
         <v>2.28</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="U8" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
         <v>1.54</v>
@@ -1978,7 +1978,7 @@
         <v>11.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
         <v>85</v>
@@ -1993,10 +1993,10 @@
         <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="AE8" t="n">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="AF8" t="n">
         <v>75</v>
@@ -2008,7 +2008,7 @@
         <v>65</v>
       </c>
       <c r="AI8" t="n">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="AJ8" t="n">
         <v>210</v>
@@ -2026,19 +2026,19 @@
         <v>600</v>
       </c>
       <c r="AO8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
         <v>9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AR8" t="n">
         <v>9</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT8" t="n">
         <v>8</v>
@@ -2062,29 +2062,29 @@
         <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BC8" t="n">
         <v>14.5</v>
       </c>
       <c r="BD8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE8" t="n">
         <v>8.4</v>
       </c>
-      <c r="BE8" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BF8" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="G9" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="H9" t="n">
         <v>5.8</v>
@@ -2127,10 +2127,10 @@
         <v>6.6</v>
       </c>
       <c r="J9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.26</v>
@@ -2139,49 +2139,49 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="R9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W9" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="X9" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="Y9" t="n">
         <v>42</v>
       </c>
       <c r="Z9" t="n">
-        <v>420</v>
+        <v>65</v>
       </c>
       <c r="AA9" t="n">
         <v>180</v>
       </c>
       <c r="AB9" t="n">
-        <v>29</v>
+        <v>14.5</v>
       </c>
       <c r="AC9" t="n">
         <v>12.5</v>
@@ -2190,7 +2190,7 @@
         <v>24</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF9" t="n">
         <v>12.5</v>
@@ -2202,37 +2202,37 @@
         <v>18</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ9" t="n">
-        <v>36</v>
+        <v>15.5</v>
       </c>
       <c r="AK9" t="n">
         <v>13.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR9" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="AT9" t="n">
         <v>12.5</v>
@@ -2244,41 +2244,41 @@
         <v>21</v>
       </c>
       <c r="AW9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AX9" t="n">
         <v>11</v>
       </c>
       <c r="AY9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="BB9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD9" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BE9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -2309,64 +2309,64 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="G10" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P10" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="R10" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="S10" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="T10" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="U10" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="V10" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z10" t="n">
         <v>500</v>
@@ -2378,7 +2378,7 @@
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AD10" t="n">
         <v>100</v>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
@@ -2414,65 +2414,65 @@
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.08</v>
+        <v>2.76</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.54</v>
+        <v>3.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.46</v>
+        <v>3.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.06</v>
+        <v>3.15</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.48</v>
+        <v>4</v>
       </c>
       <c r="AX10" t="n">
-        <v>2.08</v>
+        <v>2.88</v>
       </c>
       <c r="AY10" t="n">
-        <v>2.84</v>
+        <v>3.55</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.04</v>
+        <v>3.15</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.08</v>
+        <v>2.9</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.12</v>
+        <v>2.86</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G11" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="H11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
         <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K11" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.31</v>
@@ -2527,31 +2527,31 @@
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P11" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="R11" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="T11" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="U11" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
         <v>2.92</v>
@@ -2569,7 +2569,7 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AC11" t="n">
         <v>1000</v>
@@ -2581,7 +2581,7 @@
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AG11" t="n">
         <v>36</v>
@@ -2599,19 +2599,19 @@
         <v>160</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>4.2</v>
@@ -2620,10 +2620,10 @@
         <v>4.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU11" t="n">
         <v>7</v>
@@ -2635,38 +2635,38 @@
         <v>4.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="AY11" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.02</v>
+        <v>7.8</v>
       </c>
       <c r="BA11" t="n">
         <v>4.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.82</v>
+        <v>6.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.24</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="H12" t="n">
         <v>4.7</v>
@@ -2721,7 +2721,7 @@
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.2</v>
@@ -2733,16 +2733,16 @@
         <v>1.59</v>
       </c>
       <c r="R12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S12" t="n">
         <v>2.46</v>
       </c>
       <c r="T12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U12" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V12" t="n">
         <v>1.23</v>
@@ -2763,7 +2763,7 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
         <v>10.5</v>
@@ -2796,7 +2796,7 @@
         <v>28</v>
       </c>
       <c r="AM12" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
         <v>7.6</v>
@@ -2811,10 +2811,10 @@
         <v>20</v>
       </c>
       <c r="AR12" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT12" t="n">
         <v>10</v>
@@ -2838,7 +2838,7 @@
         <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="BB12" t="n">
         <v>15.5</v>
@@ -2847,7 +2847,7 @@
         <v>14</v>
       </c>
       <c r="BD12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE12" t="n">
         <v>11.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -2891,170 +2891,170 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="H13" t="n">
-        <v>2.12</v>
+        <v>3.45</v>
       </c>
       <c r="I13" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="J13" t="n">
-        <v>2.44</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
         <v>1.16</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="S13" t="n">
-        <v>1.15</v>
+        <v>2.08</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>1.48</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="V13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.14</v>
+        <v>5.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.14</v>
+        <v>5.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.13</v>
+        <v>5.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.14</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.14</v>
+        <v>4.7</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.11</v>
+        <v>4.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.12</v>
+        <v>4.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.14</v>
+        <v>5.7</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.12</v>
+        <v>4.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.11</v>
+        <v>4.3</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.12</v>
+        <v>4.7</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.14</v>
+        <v>5.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.13</v>
+        <v>5.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.13</v>
+        <v>4.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.13</v>
+        <v>5.3</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.14</v>
+        <v>5.9</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.55</v>
+        <v>3.75</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.55</v>
+        <v>5.3</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -3085,25 +3085,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>1.19</v>
       </c>
       <c r="H14" t="n">
-        <v>1.02</v>
+        <v>6.6</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>1.09</v>
+        <v>6.4</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
@@ -3115,28 +3115,28 @@
         <v>1.09</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>3.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="R14" t="n">
-        <v>1.24</v>
+        <v>2.14</v>
       </c>
       <c r="S14" t="n">
-        <v>1.09</v>
+        <v>1.67</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3187,68 +3187,68 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -3279,40 +3279,40 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="G15" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="H15" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="I15" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="L15" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M15" t="n">
         <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P15" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="R15" t="n">
         <v>1.28</v>
@@ -3321,128 +3321,128 @@
         <v>4.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="U15" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="V15" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="X15" t="n">
         <v>11.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AA15" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD15" t="n">
         <v>22</v>
       </c>
       <c r="AE15" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AF15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI15" t="n">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="AJ15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK15" t="n">
         <v>22</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>23</v>
       </c>
       <c r="AL15" t="n">
         <v>48</v>
       </c>
       <c r="AM15" t="n">
-        <v>580</v>
+        <v>150</v>
       </c>
       <c r="AN15" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AO15" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AP15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AR15" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AS15" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="AT15" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW15" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AX15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="BB15" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD15" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BE15" t="n">
-        <v>15.5</v>
+        <v>70</v>
       </c>
       <c r="BF15" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -3473,170 +3473,170 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H16" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="I16" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
         <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>500</v>
+        <v>8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH16" t="n">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.28</v>
+        <v>5.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.27</v>
+        <v>7</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.28</v>
+        <v>16</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.29</v>
+        <v>8</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.27</v>
+        <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.29</v>
+        <v>16</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.27</v>
+        <v>6</v>
       </c>
       <c r="AY16" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.24</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.29</v>
+        <v>8</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.29</v>
+        <v>14.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.29</v>
+        <v>19.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.29</v>
+        <v>7.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.3</v>
+        <v>8.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.2</v>
+        <v>19</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.55</v>
+        <v>7.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -3667,124 +3667,124 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="H17" t="n">
-        <v>2.84</v>
+        <v>3.55</v>
       </c>
       <c r="I17" t="n">
-        <v>12.5</v>
+        <v>4.1</v>
       </c>
       <c r="J17" t="n">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>6.8</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.33</v>
+        <v>2.06</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>1.33</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W17" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="X17" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Y17" t="n">
-        <v>500</v>
+        <v>14.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AA17" t="n">
         <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>500</v>
+        <v>8.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AE17" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AF17" t="n">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AG17" t="n">
-        <v>500</v>
+        <v>11.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AJ17" t="n">
-        <v>900</v>
+        <v>48</v>
       </c>
       <c r="AK17" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL17" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AM17" t="n">
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.38</v>
+        <v>6.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.43</v>
+        <v>6.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.44</v>
+        <v>6.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.46</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT17" t="n">
         <v>5.6</v>
@@ -3793,44 +3793,44 @@
         <v>4.9</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.44</v>
+        <v>5.9</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.46</v>
+        <v>7.8</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.41</v>
+        <v>5.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.38</v>
+        <v>5.1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.43</v>
+        <v>6.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.46</v>
+        <v>7.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.45</v>
+        <v>6.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.44</v>
+        <v>6.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.46</v>
+        <v>7.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.47</v>
+        <v>8.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.55</v>
+        <v>6</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.55</v>
+        <v>7.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -3861,170 +3861,170 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K18" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.56</v>
       </c>
-      <c r="M18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>1.48</v>
       </c>
-      <c r="W18" t="n">
-        <v>1.53</v>
-      </c>
       <c r="X18" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AC18" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AF18" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG18" t="n">
         <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AJ18" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS18" t="n">
         <v>38</v>
       </c>
-      <c r="AL18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>450</v>
-      </c>
-      <c r="AN18" t="n">
+      <c r="AT18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA18" t="n">
         <v>40</v>
       </c>
-      <c r="AO18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>55</v>
-      </c>
       <c r="BB18" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BC18" t="n">
         <v>32</v>
       </c>
       <c r="BD18" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BE18" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="BF18" t="n">
         <v>32</v>
       </c>
       <c r="BG18" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -4061,46 +4061,46 @@
         <v>2.12</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I19" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K19" t="n">
         <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
         <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="O19" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P19" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="S19" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="T19" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="U19" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="V19" t="n">
         <v>1.37</v>
@@ -4109,10 +4109,10 @@
         <v>1.89</v>
       </c>
       <c r="X19" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y19" t="n">
         <v>21</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>19.5</v>
       </c>
       <c r="Z19" t="n">
         <v>29</v>
@@ -4121,19 +4121,19 @@
         <v>65</v>
       </c>
       <c r="AB19" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
         <v>15</v>
       </c>
       <c r="AE19" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG19" t="n">
         <v>11</v>
@@ -4142,31 +4142,31 @@
         <v>14.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ19" t="n">
         <v>26</v>
       </c>
       <c r="AK19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN19" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AP19" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AQ19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR19" t="n">
         <v>27</v>
@@ -4175,10 +4175,10 @@
         <v>50</v>
       </c>
       <c r="AT19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV19" t="n">
         <v>14</v>
@@ -4187,7 +4187,7 @@
         <v>30</v>
       </c>
       <c r="AX19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY19" t="n">
         <v>10</v>
@@ -4196,29 +4196,29 @@
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB19" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD19" t="n">
         <v>24</v>
       </c>
-      <c r="BC19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>25</v>
-      </c>
       <c r="BE19" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BF19" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG19" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -4249,88 +4249,88 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J20" t="n">
         <v>2.9</v>
       </c>
-      <c r="H20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.4</v>
       </c>
       <c r="R20" t="n">
         <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="U20" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V20" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X20" t="n">
         <v>6.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA20" t="n">
         <v>75</v>
       </c>
       <c r="AB20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC20" t="n">
         <v>7</v>
       </c>
-      <c r="AC20" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AD20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE20" t="n">
         <v>170</v>
       </c>
       <c r="AF20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
         <v>32</v>
@@ -4339,61 +4339,61 @@
         <v>540</v>
       </c>
       <c r="AJ20" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AK20" t="n">
         <v>55</v>
       </c>
       <c r="AL20" t="n">
-        <v>230</v>
+        <v>95</v>
       </c>
       <c r="AM20" t="n">
         <v>500</v>
       </c>
       <c r="AN20" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO20" t="n">
         <v>140</v>
       </c>
       <c r="AP20" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ20" t="n">
         <v>7</v>
       </c>
       <c r="AR20" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS20" t="n">
         <v>55</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV20" t="n">
         <v>14.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AX20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BA20" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BB20" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BC20" t="n">
         <v>44</v>
@@ -4405,14 +4405,14 @@
         <v>110</v>
       </c>
       <c r="BF20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BG20" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -4449,46 +4449,46 @@
         <v>2.08</v>
       </c>
       <c r="H21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J21" t="n">
         <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L21" t="n">
         <v>1.55</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N21" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O21" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P21" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S21" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U21" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V21" t="n">
         <v>1.29</v>
@@ -4497,7 +4497,7 @@
         <v>1.92</v>
       </c>
       <c r="X21" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y21" t="n">
         <v>12</v>
@@ -4509,16 +4509,16 @@
         <v>500</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC21" t="n">
         <v>7.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AF21" t="n">
         <v>10.5</v>
@@ -4536,7 +4536,7 @@
         <v>500</v>
       </c>
       <c r="AK21" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="AL21" t="n">
         <v>460</v>
@@ -4548,65 +4548,65 @@
         <v>26</v>
       </c>
       <c r="AO21" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP21" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR21" t="n">
         <v>13</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU21" t="n">
         <v>6.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="AX21" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AY21" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA21" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD21" t="n">
         <v>29</v>
       </c>
-      <c r="BB21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BE21" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>8.4</v>
+        <v>19.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -4640,16 +4640,16 @@
         <v>2.06</v>
       </c>
       <c r="G22" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K22" t="n">
         <v>3.5</v>
@@ -4658,7 +4658,7 @@
         <v>1.5</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N22" t="n">
         <v>3.2</v>
@@ -4673,22 +4673,22 @@
         <v>2.32</v>
       </c>
       <c r="R22" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S22" t="n">
         <v>4.5</v>
       </c>
       <c r="T22" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.92</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.89</v>
       </c>
       <c r="X22" t="n">
         <v>11</v>
@@ -4700,7 +4700,7 @@
         <v>32</v>
       </c>
       <c r="AA22" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB22" t="n">
         <v>7.8</v>
@@ -4718,10 +4718,10 @@
         <v>11.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
         <v>80</v>
@@ -4730,7 +4730,7 @@
         <v>26</v>
       </c>
       <c r="AK22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
         <v>48</v>
@@ -4751,10 +4751,10 @@
         <v>12</v>
       </c>
       <c r="AR22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS22" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AT22" t="n">
         <v>7.2</v>
@@ -4763,10 +4763,10 @@
         <v>7.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW22" t="n">
-        <v>14.5</v>
+        <v>55</v>
       </c>
       <c r="AX22" t="n">
         <v>10.5</v>
@@ -4778,29 +4778,29 @@
         <v>18.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>14.5</v>
+        <v>38</v>
       </c>
       <c r="BB22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC22" t="n">
         <v>22</v>
       </c>
       <c r="BD22" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BE22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BF22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG22" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G23" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H23" t="n">
         <v>3.65</v>
@@ -4843,7 +4843,7 @@
         <v>3.85</v>
       </c>
       <c r="J23" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
         <v>3.1</v>
@@ -4864,7 +4864,7 @@
         <v>1.46</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G24" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I24" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J24" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K24" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L24" t="n">
         <v>1.45</v>
@@ -5052,7 +5052,7 @@
         <v>3.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P24" t="n">
         <v>1.88</v>
@@ -5073,10 +5073,10 @@
         <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W24" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X24" t="n">
         <v>14.5</v>
@@ -5085,7 +5085,7 @@
         <v>17</v>
       </c>
       <c r="Z24" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
@@ -5097,13 +5097,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG24" t="n">
         <v>10.5</v>
@@ -5112,13 +5112,13 @@
         <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AJ24" t="n">
         <v>25</v>
       </c>
       <c r="AK24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL24" t="n">
         <v>46</v>
@@ -5133,10 +5133,10 @@
         <v>270</v>
       </c>
       <c r="AP24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR24" t="n">
         <v>21</v>
@@ -5145,7 +5145,7 @@
         <v>38</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU24" t="n">
         <v>7.8</v>
@@ -5169,7 +5169,7 @@
         <v>34</v>
       </c>
       <c r="BB24" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC24" t="n">
         <v>18</v>
@@ -5181,14 +5181,14 @@
         <v>42</v>
       </c>
       <c r="BF24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG24" t="n">
         <v>34</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -5219,170 +5219,170 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="G25" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="H25" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="I25" t="n">
-        <v>110</v>
+        <v>6.8</v>
       </c>
       <c r="J25" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="K25" t="n">
-        <v>11.5</v>
+        <v>5.2</v>
       </c>
       <c r="L25" t="n">
         <v>1.29</v>
       </c>
       <c r="M25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>2.36</v>
+        <v>4.2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R25" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.5</v>
-      </c>
       <c r="S25" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="T25" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="U25" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V25" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="W25" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC25" t="n">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>500</v>
+        <v>7.2</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.21</v>
+        <v>5.8</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.21</v>
+        <v>6.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.21</v>
+        <v>6.8</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.16</v>
+        <v>4.5</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.18</v>
+        <v>4.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.21</v>
+        <v>5.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.21</v>
+        <v>6.6</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.18</v>
+        <v>4.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.17</v>
+        <v>4.3</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.21</v>
+        <v>5.3</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.21</v>
+        <v>6.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.21</v>
+        <v>5</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.19</v>
+        <v>5</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.21</v>
+        <v>5.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.21</v>
+        <v>6.6</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.18</v>
+        <v>3.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G26" t="n">
         <v>1.95</v>
@@ -5440,7 +5440,7 @@
         <v>2.88</v>
       </c>
       <c r="O26" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="P26" t="n">
         <v>1.62</v>
@@ -5458,7 +5458,7 @@
         <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V26" t="n">
         <v>1.25</v>
@@ -5488,7 +5488,7 @@
         <v>21</v>
       </c>
       <c r="AE26" t="n">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="AF26" t="n">
         <v>11</v>
@@ -5497,7 +5497,7 @@
         <v>11.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI26" t="n">
         <v>450</v>
@@ -5530,13 +5530,13 @@
         <v>14.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT26" t="n">
         <v>5.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV26" t="n">
         <v>16.5</v>
@@ -5548,16 +5548,16 @@
         <v>9</v>
       </c>
       <c r="AY26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
         <v>21</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB26" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC26" t="n">
         <v>21</v>
@@ -5566,17 +5566,17 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BE26" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BF26" t="n">
         <v>17.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G27" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H27" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I27" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J27" t="n">
         <v>3.1</v>
@@ -5625,22 +5625,22 @@
         <v>3.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M27" t="n">
         <v>1.12</v>
       </c>
       <c r="N27" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P27" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="R27" t="n">
         <v>1.2</v>
@@ -5652,16 +5652,16 @@
         <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V27" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W27" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y27" t="n">
         <v>11</v>
@@ -5691,13 +5691,13 @@
         <v>12.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI27" t="n">
         <v>500</v>
       </c>
       <c r="AJ27" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AK27" t="n">
         <v>65</v>
@@ -5709,10 +5709,10 @@
         <v>500</v>
       </c>
       <c r="AN27" t="n">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="AO27" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AP27" t="n">
         <v>7.6</v>
@@ -5724,7 +5724,7 @@
         <v>20</v>
       </c>
       <c r="AS27" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT27" t="n">
         <v>6.6</v>
@@ -5736,7 +5736,7 @@
         <v>13.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX27" t="n">
         <v>12</v>
@@ -5748,29 +5748,29 @@
         <v>19</v>
       </c>
       <c r="BA27" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB27" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC27" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BD27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE27" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG27" t="n">
         <v>10</v>
       </c>
-      <c r="BF27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -5801,64 +5801,64 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="G28" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H28" t="n">
         <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K28" t="n">
         <v>4.5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P28" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="T28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U28" t="n">
         <v>2</v>
       </c>
-      <c r="U28" t="n">
-        <v>1.94</v>
-      </c>
       <c r="V28" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W28" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="X28" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z28" t="n">
         <v>60</v>
@@ -5867,104 +5867,104 @@
         <v>700</v>
       </c>
       <c r="AB28" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD28" t="n">
         <v>26</v>
       </c>
       <c r="AE28" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF28" t="n">
         <v>9</v>
       </c>
       <c r="AG28" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AH28" t="n">
         <v>23</v>
       </c>
       <c r="AI28" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ28" t="n">
         <v>14.5</v>
       </c>
       <c r="AK28" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL28" t="n">
         <v>36</v>
       </c>
       <c r="AM28" t="n">
-        <v>180</v>
+        <v>390</v>
       </c>
       <c r="AN28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO28" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP28" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR28" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS28" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV28" t="n">
         <v>24</v>
       </c>
       <c r="AW28" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX28" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA28" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BB28" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC28" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD28" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE28" t="n">
         <v>70</v>
       </c>
       <c r="BF28" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG28" t="n">
         <v>42</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -5998,16 +5998,16 @@
         <v>3.15</v>
       </c>
       <c r="G29" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H29" t="n">
         <v>2.54</v>
       </c>
       <c r="I29" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="J29" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K29" t="n">
         <v>3.4</v>
@@ -6025,7 +6025,7 @@
         <v>1.43</v>
       </c>
       <c r="P29" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q29" t="n">
         <v>2.3</v>
@@ -6037,16 +6037,16 @@
         <v>4.5</v>
       </c>
       <c r="T29" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U29" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W29" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X29" t="n">
         <v>10.5</v>
@@ -6067,7 +6067,7 @@
         <v>7.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE29" t="n">
         <v>32</v>
@@ -6076,19 +6076,19 @@
         <v>21</v>
       </c>
       <c r="AG29" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ29" t="n">
         <v>60</v>
       </c>
       <c r="AK29" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL29" t="n">
         <v>60</v>
@@ -6103,7 +6103,7 @@
         <v>38</v>
       </c>
       <c r="AP29" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ29" t="n">
         <v>8.4</v>
@@ -6115,7 +6115,7 @@
         <v>34</v>
       </c>
       <c r="AT29" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU29" t="n">
         <v>7</v>
@@ -6133,13 +6133,13 @@
         <v>12.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA29" t="n">
         <v>46</v>
       </c>
       <c r="BB29" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BC29" t="n">
         <v>36</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -6192,28 +6192,28 @@
         <v>2.34</v>
       </c>
       <c r="G30" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H30" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I30" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J30" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="K30" t="n">
         <v>3.1</v>
       </c>
       <c r="L30" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M30" t="n">
         <v>1.14</v>
       </c>
       <c r="N30" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="O30" t="n">
         <v>1.56</v>
@@ -6222,7 +6222,7 @@
         <v>1.48</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
@@ -6240,10 +6240,10 @@
         <v>1.32</v>
       </c>
       <c r="W30" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Y30" t="n">
         <v>1000</v>
@@ -6255,10 +6255,10 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
         <v>1000</v>
@@ -6297,62 +6297,62 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.14</v>
+        <v>6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="AT30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX30" t="n">
         <v>5</v>
       </c>
-      <c r="AU30" t="n">
+      <c r="AY30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA30" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>2.16</v>
       </c>
       <c r="BB30" t="n">
         <v>6.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="BD30" t="n">
-        <v>2.16</v>
+        <v>4.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.16</v>
+        <v>7.4</v>
       </c>
       <c r="BF30" t="n">
-        <v>2.16</v>
+        <v>6.6</v>
       </c>
       <c r="BG30" t="n">
-        <v>2.16</v>
+        <v>2.96</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="G31" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="H31" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="I31" t="n">
-        <v>420</v>
+        <v>8.6</v>
       </c>
       <c r="J31" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="K31" t="n">
-        <v>85</v>
+        <v>6.2</v>
       </c>
       <c r="L31" t="n">
         <v>1.24</v>
@@ -6407,40 +6407,40 @@
         <v>1.02</v>
       </c>
       <c r="N31" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="O31" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P31" t="n">
-        <v>1.66</v>
+        <v>2.56</v>
       </c>
       <c r="Q31" t="n">
         <v>1.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="S31" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="T31" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="U31" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="V31" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="W31" t="n">
-        <v>2.1</v>
+        <v>2.96</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Z31" t="n">
         <v>1000</v>
@@ -6449,104 +6449,104 @@
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE31" t="n">
         <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI31" t="n">
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.06</v>
+        <v>6.4</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.06</v>
+        <v>6.6</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.06</v>
+        <v>7.2</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.06</v>
+        <v>7.8</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.06</v>
+        <v>5</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.06</v>
+        <v>5.1</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.06</v>
+        <v>6.4</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.06</v>
+        <v>7.4</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.06</v>
+        <v>4.8</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.06</v>
+        <v>4.7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.06</v>
+        <v>5.9</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.06</v>
+        <v>7.2</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.06</v>
+        <v>5.1</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.06</v>
+        <v>5.2</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.06</v>
+        <v>6.2</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.06</v>
+        <v>7.4</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.55</v>
+        <v>7.4</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -6580,19 +6580,19 @@
         <v>4.5</v>
       </c>
       <c r="G32" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H32" t="n">
         <v>1.92</v>
       </c>
       <c r="I32" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="J32" t="n">
         <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L32" t="n">
         <v>1.45</v>
@@ -6619,7 +6619,7 @@
         <v>3.9</v>
       </c>
       <c r="T32" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U32" t="n">
         <v>2</v>
@@ -6640,7 +6640,7 @@
         <v>12.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB32" t="n">
         <v>16</v>
@@ -6718,19 +6718,19 @@
         <v>17</v>
       </c>
       <c r="BA32" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB32" t="n">
         <v>8</v>
       </c>
       <c r="BC32" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD32" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE32" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF32" t="n">
         <v>7.8</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -6774,19 +6774,19 @@
         <v>3</v>
       </c>
       <c r="G33" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H33" t="n">
         <v>2.94</v>
       </c>
       <c r="I33" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K33" t="n">
         <v>3</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3.05</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -6804,7 +6804,7 @@
         <v>1.46</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G34" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H34" t="n">
         <v>7</v>
       </c>
       <c r="I34" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J34" t="n">
         <v>4.4</v>
       </c>
       <c r="K34" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -6995,10 +6995,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -7159,25 +7159,25 @@
         </is>
       </c>
       <c r="F35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G35" t="n">
         <v>4.4</v>
       </c>
-      <c r="G35" t="n">
-        <v>4.6</v>
-      </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="I35" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="J35" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K35" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L35" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M35" t="n">
         <v>1.1</v>
@@ -7189,7 +7189,7 @@
         <v>1.43</v>
       </c>
       <c r="P35" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q35" t="n">
         <v>2.3</v>
@@ -7198,37 +7198,37 @@
         <v>1.27</v>
       </c>
       <c r="S35" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U35" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V35" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="W35" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y35" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z35" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB35" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD35" t="n">
         <v>10.5</v>
@@ -7240,7 +7240,7 @@
         <v>32</v>
       </c>
       <c r="AG35" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AH35" t="n">
         <v>22</v>
@@ -7249,25 +7249,25 @@
         <v>48</v>
       </c>
       <c r="AJ35" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK35" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL35" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN35" t="n">
         <v>85</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>95</v>
       </c>
       <c r="AO35" t="n">
         <v>21</v>
       </c>
       <c r="AP35" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ35" t="n">
         <v>7.2</v>
@@ -7279,7 +7279,7 @@
         <v>21</v>
       </c>
       <c r="AT35" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU35" t="n">
         <v>7.2</v>
@@ -7288,22 +7288,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW35" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX35" t="n">
         <v>28</v>
       </c>
       <c r="AY35" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA35" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB35" t="n">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="BC35" t="n">
         <v>55</v>
@@ -7312,17 +7312,17 @@
         <v>65</v>
       </c>
       <c r="BE35" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BF35" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BG35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
         <v>2.2</v>
       </c>
       <c r="G36" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H36" t="n">
         <v>3.8</v>
@@ -7371,7 +7371,7 @@
         <v>3.45</v>
       </c>
       <c r="L36" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M36" t="n">
         <v>1.07</v>
@@ -7383,16 +7383,16 @@
         <v>1.28</v>
       </c>
       <c r="P36" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R36" t="n">
         <v>1.44</v>
       </c>
       <c r="S36" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T36" t="n">
         <v>1.67</v>
@@ -7404,13 +7404,13 @@
         <v>1.33</v>
       </c>
       <c r="W36" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X36" t="n">
         <v>17.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Z36" t="n">
         <v>32</v>
@@ -7440,7 +7440,7 @@
         <v>15.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ36" t="n">
         <v>30</v>
@@ -7452,25 +7452,25 @@
         <v>34</v>
       </c>
       <c r="AM36" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO36" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP36" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="AQ36" t="n">
         <v>14.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS36" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AT36" t="n">
         <v>9.800000000000001</v>
@@ -7482,41 +7482,41 @@
         <v>14.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="AX36" t="n">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="AY36" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ36" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA36" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="BB36" t="n">
         <v>7.2</v>
       </c>
       <c r="BC36" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD36" t="n">
         <v>28</v>
       </c>
       <c r="BE36" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BF36" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BG36" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -7547,31 +7547,31 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.05</v>
+        <v>2.34</v>
       </c>
       <c r="G37" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="H37" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="I37" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J37" t="n">
-        <v>1.1</v>
+        <v>2.56</v>
       </c>
       <c r="K37" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L37" t="n">
         <v>1.46</v>
       </c>
       <c r="M37" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N37" t="n">
-        <v>1.63</v>
+        <v>2.8</v>
       </c>
       <c r="O37" t="n">
         <v>1.39</v>
@@ -7580,25 +7580,25 @@
         <v>1.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R37" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S37" t="n">
-        <v>1.39</v>
+        <v>3.3</v>
       </c>
       <c r="T37" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="U37" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W37" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -7655,62 +7655,62 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>1.54</v>
       </c>
       <c r="G2" t="n">
-        <v>2.64</v>
+        <v>1.56</v>
       </c>
       <c r="H2" t="n">
-        <v>2.56</v>
+        <v>6.4</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6</v>
+        <v>6.8</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>250</v>
+      </c>
+      <c r="BC2" t="n">
         <v>8.6</v>
       </c>
-      <c r="O2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="X2" t="n">
-        <v>46</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC2" t="n">
+      <c r="BD2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE2" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>34</v>
-      </c>
       <c r="BF2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG2" t="n">
         <v>9.6</v>
       </c>
-      <c r="BG2" t="n">
-        <v>9</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="H3" t="n">
-        <v>2.24</v>
+        <v>2.54</v>
       </c>
       <c r="I3" t="n">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
         <v>1.35</v>
@@ -975,7 +975,7 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.24</v>
@@ -984,7 +984,7 @@
         <v>2.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R3" t="n">
         <v>1.52</v>
@@ -993,128 +993,128 @@
         <v>2.84</v>
       </c>
       <c r="T3" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U3" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="V3" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="W3" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="X3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AB3" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC3" t="n">
         <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AF3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AJ3" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AK3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL3" t="n">
         <v>34</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>40</v>
       </c>
       <c r="AM3" t="n">
         <v>65</v>
       </c>
       <c r="AN3" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AO3" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP3" t="n">
         <v>18</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AS3" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AT3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AX3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BB3" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BC3" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD3" t="n">
         <v>30</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>34</v>
       </c>
       <c r="BE3" t="n">
         <v>55</v>
       </c>
       <c r="BF3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BG3" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -1145,76 +1145,76 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="H4" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="I4" t="n">
-        <v>2.76</v>
+        <v>2.54</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.44</v>
       </c>
-      <c r="S4" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.48</v>
-      </c>
       <c r="X4" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
         <v>12.5</v>
@@ -1226,89 +1226,89 @@
         <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AK4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN4" t="n">
         <v>32</v>
       </c>
-      <c r="AL4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>26</v>
-      </c>
       <c r="AO4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP4" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV4" t="n">
         <v>10</v>
       </c>
-      <c r="AR4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AW4" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
         <v>13</v>
       </c>
       <c r="BA4" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="BB4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BC4" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD4" t="n">
         <v>18.5</v>
       </c>
-      <c r="BD4" t="n">
-        <v>24</v>
-      </c>
       <c r="BE4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>16</v>
+        <v>7.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -1342,167 +1342,167 @@
         <v>6.4</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K5" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="T5" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="U5" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="V5" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="W5" t="n">
         <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="n">
-        <v>500</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>29</v>
+        <v>14.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="AC5" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AG5" t="n">
         <v>42</v>
       </c>
       <c r="AH5" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AK5" t="n">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="AL5" t="n">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="AM5" t="n">
-        <v>580</v>
+        <v>180</v>
       </c>
       <c r="AN5" t="n">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AO5" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AP5" t="n">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.2</v>
+        <v>50</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.6</v>
+        <v>44</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -1533,40 +1533,40 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="G6" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P6" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="R6" t="n">
         <v>1.28</v>
@@ -1575,19 +1575,19 @@
         <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="U6" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="V6" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="X6" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="Y6" t="n">
         <v>24</v>
@@ -1602,28 +1602,28 @@
         <v>13</v>
       </c>
       <c r="AC6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>46</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG6" t="n">
         <v>19</v>
       </c>
-      <c r="AG6" t="n">
-        <v>21</v>
-      </c>
       <c r="AH6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AK6" t="n">
         <v>500</v>
@@ -1635,68 +1635,68 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.65</v>
+        <v>11.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY6" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
         <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.7</v>
+        <v>11</v>
       </c>
       <c r="BB6" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BC6" t="n">
         <v>11.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.65</v>
+        <v>11.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.85</v>
+        <v>12.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="G7" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="H7" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="I7" t="n">
         <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S7" t="n">
         <v>3.2</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.35</v>
-      </c>
       <c r="T7" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="U7" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC7" t="n">
         <v>7.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>270</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX7" t="n">
         <v>16</v>
       </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>440</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AY7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="BB7" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.35</v>
+        <v>22</v>
       </c>
       <c r="BD7" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.8</v>
+        <v>20</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
         <v>2.86</v>
@@ -1933,40 +1933,40 @@
         <v>3.25</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
         <v>3.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="O8" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="R8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="U8" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="V8" t="n">
         <v>1.45</v>
@@ -1975,46 +1975,46 @@
         <v>1.54</v>
       </c>
       <c r="X8" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AA8" t="n">
-        <v>290</v>
+        <v>220</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC8" t="n">
         <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE8" t="n">
         <v>140</v>
       </c>
       <c r="AF8" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AG8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH8" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
         <v>370</v>
       </c>
       <c r="AJ8" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="AK8" t="n">
-        <v>210</v>
+        <v>38</v>
       </c>
       <c r="AL8" t="n">
         <v>270</v>
@@ -2023,25 +2023,25 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AO8" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AR8" t="n">
         <v>9</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU8" t="n">
         <v>6.4</v>
@@ -2050,10 +2050,10 @@
         <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AX8" t="n">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="AY8" t="n">
         <v>10.5</v>
@@ -2062,29 +2062,29 @@
         <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="BC8" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -2118,61 +2118,61 @@
         <v>1.52</v>
       </c>
       <c r="G9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I9" t="n">
         <v>6.6</v>
       </c>
       <c r="J9" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K9" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="S9" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="T9" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="U9" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
         <v>1.17</v>
       </c>
       <c r="W9" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="X9" t="n">
         <v>80</v>
       </c>
       <c r="Y9" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Z9" t="n">
         <v>65</v>
@@ -2181,13 +2181,13 @@
         <v>180</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AE9" t="n">
         <v>70</v>
@@ -2205,37 +2205,37 @@
         <v>60</v>
       </c>
       <c r="AJ9" t="n">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="AK9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL9" t="n">
         <v>23</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN9" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AO9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP9" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AR9" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.3</v>
+        <v>19</v>
       </c>
       <c r="AT9" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU9" t="n">
         <v>11</v>
@@ -2247,10 +2247,10 @@
         <v>30</v>
       </c>
       <c r="AX9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AZ9" t="n">
         <v>16</v>
@@ -2262,23 +2262,23 @@
         <v>13.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H10" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="I10" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
@@ -2333,7 +2333,7 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.16</v>
@@ -2345,22 +2345,22 @@
         <v>1.48</v>
       </c>
       <c r="R10" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="S10" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="T10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="U10" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2369,7 +2369,7 @@
         <v>500</v>
       </c>
       <c r="Z10" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
@@ -2417,62 +2417,62 @@
         <v>55</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BF10" t="n">
         <v>3.6</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.8</v>
       </c>
       <c r="BG10" t="n">
         <v>3.9</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="G11" t="n">
         <v>1.5</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J11" t="n">
         <v>4.7</v>
       </c>
       <c r="K11" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.31</v>
@@ -2527,22 +2527,22 @@
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O11" t="n">
         <v>1.19</v>
       </c>
       <c r="P11" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R11" t="n">
         <v>1.61</v>
       </c>
       <c r="S11" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T11" t="n">
         <v>1.77</v>
@@ -2554,7 +2554,7 @@
         <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2599,13 +2599,13 @@
         <v>160</v>
       </c>
       <c r="AL11" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
@@ -2614,13 +2614,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="AR11" t="n">
         <v>4.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT11" t="n">
         <v>5.5</v>
@@ -2629,22 +2629,22 @@
         <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX11" t="n">
         <v>4.7</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.2</v>
+        <v>30</v>
       </c>
       <c r="BB11" t="n">
         <v>6.2</v>
@@ -2653,20 +2653,20 @@
         <v>7</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="BE11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BG11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -2697,121 +2697,121 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="G12" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="H12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K12" t="n">
         <v>4.7</v>
       </c>
-      <c r="I12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M12" t="n">
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U12" t="n">
         <v>2.46</v>
       </c>
-      <c r="Q12" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.34</v>
-      </c>
       <c r="V12" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W12" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="X12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z12" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE12" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AF12" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AG12" t="n">
         <v>10.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AJ12" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AK12" t="n">
         <v>16.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AO12" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AP12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ12" t="n">
         <v>20</v>
       </c>
       <c r="AR12" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="AS12" t="n">
         <v>11.5</v>
@@ -2823,10 +2823,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AX12" t="n">
         <v>10.5</v>
@@ -2835,32 +2835,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BC12" t="n">
         <v>14</v>
       </c>
       <c r="BD12" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF12" t="n">
         <v>6.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G13" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
         <v>4</v>
@@ -2909,40 +2909,40 @@
         <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="O13" t="n">
         <v>1.16</v>
       </c>
       <c r="P13" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R13" t="n">
         <v>1.63</v>
       </c>
       <c r="S13" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="T13" t="n">
         <v>1.48</v>
       </c>
       <c r="U13" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X13" t="n">
         <v>32</v>
@@ -3011,7 +3011,7 @@
         <v>6</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AU13" t="n">
         <v>4.2</v>
@@ -3023,10 +3023,10 @@
         <v>5.7</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AZ13" t="n">
         <v>4.7</v>
@@ -3047,14 +3047,14 @@
         <v>5.9</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.75</v>
+        <v>6.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -3088,10 +3088,10 @@
         <v>1.14</v>
       </c>
       <c r="G14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="I14" t="n">
         <v>25</v>
@@ -3100,43 +3100,43 @@
         <v>6.4</v>
       </c>
       <c r="K14" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="L14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P14" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="R14" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="T14" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="V14" t="n">
         <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3175,7 +3175,7 @@
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK14" t="n">
         <v>1000</v>
@@ -3187,13 +3187,13 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AQ14" t="n">
         <v>4.2</v>
@@ -3205,10 +3205,10 @@
         <v>4.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AV14" t="n">
         <v>4.2</v>
@@ -3217,38 +3217,38 @@
         <v>4.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BA14" t="n">
         <v>4.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BF14" t="n">
         <v>2.14</v>
       </c>
       <c r="BG14" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G15" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H15" t="n">
         <v>5.8</v>
@@ -3291,10 +3291,10 @@
         <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.51</v>
@@ -3306,7 +3306,7 @@
         <v>3.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P15" t="n">
         <v>1.76</v>
@@ -3315,13 +3315,13 @@
         <v>2.24</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U15" t="n">
         <v>1.88</v>
@@ -3330,16 +3330,16 @@
         <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z15" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA15" t="n">
         <v>160</v>
@@ -3348,7 +3348,7 @@
         <v>7.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD15" t="n">
         <v>22</v>
@@ -3357,7 +3357,7 @@
         <v>90</v>
       </c>
       <c r="AF15" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AG15" t="n">
         <v>10.5</v>
@@ -3372,19 +3372,19 @@
         <v>19</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM15" t="n">
         <v>150</v>
       </c>
       <c r="AN15" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP15" t="n">
         <v>10</v>
@@ -3393,22 +3393,22 @@
         <v>15</v>
       </c>
       <c r="AR15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS15" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV15" t="n">
         <v>20</v>
       </c>
       <c r="AW15" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AX15" t="n">
         <v>9</v>
@@ -3417,22 +3417,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA15" t="n">
         <v>80</v>
       </c>
       <c r="BB15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC15" t="n">
         <v>19</v>
       </c>
       <c r="BD15" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="BE15" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BF15" t="n">
         <v>13.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -3473,58 +3473,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G16" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
         <v>3.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T16" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U16" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V16" t="n">
         <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="X16" t="n">
         <v>14</v>
@@ -3536,7 +3536,7 @@
         <v>24</v>
       </c>
       <c r="AA16" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AB16" t="n">
         <v>11.5</v>
@@ -3545,13 +3545,13 @@
         <v>8</v>
       </c>
       <c r="AD16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AF16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG16" t="n">
         <v>12</v>
@@ -3563,10 +3563,10 @@
         <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL16" t="n">
         <v>42</v>
@@ -3578,22 +3578,22 @@
         <v>23</v>
       </c>
       <c r="AO16" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU16" t="n">
         <v>6.6</v>
@@ -3605,7 +3605,7 @@
         <v>16</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="AY16" t="n">
         <v>10</v>
@@ -3614,29 +3614,29 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="BB16" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BC16" t="n">
         <v>19.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.6</v>
+        <v>18.5</v>
       </c>
       <c r="BE16" t="n">
         <v>8.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="G17" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="H17" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="I17" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
         <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
@@ -3706,22 +3706,22 @@
         <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U17" t="n">
         <v>2.02</v>
       </c>
       <c r="V17" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W17" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="X17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y17" t="n">
         <v>14.5</v>
@@ -3733,19 +3733,19 @@
         <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD17" t="n">
         <v>17</v>
       </c>
       <c r="AE17" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AF17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG17" t="n">
         <v>11.5</v>
@@ -3754,7 +3754,7 @@
         <v>19.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ17" t="n">
         <v>48</v>
@@ -3769,68 +3769,68 @@
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO17" t="n">
         <v>600</v>
       </c>
       <c r="AP17" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="AT17" t="n">
         <v>5.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.9</v>
+        <v>13.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.8</v>
+        <v>44</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.4</v>
+        <v>15.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -3867,34 +3867,34 @@
         <v>3.05</v>
       </c>
       <c r="H18" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="I18" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
         <v>3.35</v>
       </c>
       <c r="O18" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
         <v>1.3</v>
@@ -3903,28 +3903,28 @@
         <v>4.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U18" t="n">
         <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W18" t="n">
         <v>1.48</v>
       </c>
       <c r="X18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y18" t="n">
         <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA18" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB18" t="n">
         <v>11</v>
@@ -3933,25 +3933,25 @@
         <v>7.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF18" t="n">
         <v>19.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI18" t="n">
         <v>48</v>
       </c>
       <c r="AJ18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK18" t="n">
         <v>36</v>
@@ -3960,16 +3960,16 @@
         <v>55</v>
       </c>
       <c r="AM18" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN18" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO18" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AP18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ18" t="n">
         <v>9.199999999999999</v>
@@ -3978,19 +3978,19 @@
         <v>15.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT18" t="n">
         <v>10</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV18" t="n">
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX18" t="n">
         <v>17.5</v>
@@ -4002,29 +4002,29 @@
         <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB18" t="n">
         <v>44</v>
       </c>
       <c r="BC18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BD18" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BG18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G19" t="n">
         <v>2.08</v>
       </c>
-      <c r="G19" t="n">
-        <v>2.12</v>
-      </c>
       <c r="H19" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I19" t="n">
         <v>3.65</v>
       </c>
       <c r="J19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
         <v>1.3</v>
@@ -4088,7 +4088,7 @@
         <v>2.62</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R19" t="n">
         <v>1.67</v>
@@ -4100,13 +4100,13 @@
         <v>1.55</v>
       </c>
       <c r="U19" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V19" t="n">
         <v>1.37</v>
       </c>
       <c r="W19" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="X19" t="n">
         <v>26</v>
@@ -4115,7 +4115,7 @@
         <v>21</v>
       </c>
       <c r="Z19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA19" t="n">
         <v>65</v>
@@ -4124,25 +4124,25 @@
         <v>14.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD19" t="n">
         <v>15</v>
       </c>
       <c r="AE19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF19" t="n">
         <v>16</v>
       </c>
       <c r="AG19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH19" t="n">
         <v>14.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AJ19" t="n">
         <v>26</v>
@@ -4160,7 +4160,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AO19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP19" t="n">
         <v>22</v>
@@ -4169,7 +4169,7 @@
         <v>18</v>
       </c>
       <c r="AR19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS19" t="n">
         <v>50</v>
@@ -4178,7 +4178,7 @@
         <v>13</v>
       </c>
       <c r="AU19" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV19" t="n">
         <v>14</v>
@@ -4199,26 +4199,26 @@
         <v>32</v>
       </c>
       <c r="BB19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC19" t="n">
         <v>17</v>
       </c>
       <c r="BD19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF19" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -4252,70 +4252,70 @@
         <v>2.84</v>
       </c>
       <c r="G20" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="H20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="K20" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="L20" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="M20" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N20" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="O20" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="P20" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
         <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="U20" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X20" t="n">
         <v>6.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA20" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC20" t="n">
         <v>7</v>
@@ -4324,43 +4324,43 @@
         <v>16.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="AF20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH20" t="n">
         <v>32</v>
       </c>
       <c r="AI20" t="n">
-        <v>540</v>
+        <v>120</v>
       </c>
       <c r="AJ20" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AK20" t="n">
         <v>55</v>
       </c>
       <c r="AL20" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AM20" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="AN20" t="n">
         <v>75</v>
       </c>
       <c r="AO20" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR20" t="n">
         <v>17.5</v>
@@ -4369,50 +4369,50 @@
         <v>55</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU20" t="n">
         <v>6.4</v>
       </c>
       <c r="AV20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX20" t="n">
         <v>14.5</v>
       </c>
-      <c r="AW20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>15</v>
-      </c>
       <c r="AY20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BA20" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="BB20" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BC20" t="n">
         <v>44</v>
       </c>
       <c r="BD20" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BE20" t="n">
         <v>110</v>
       </c>
       <c r="BF20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG20" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -4443,170 +4443,170 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H21" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="I21" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J21" t="n">
         <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L21" t="n">
         <v>1.55</v>
       </c>
       <c r="M21" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N21" t="n">
         <v>2.94</v>
       </c>
       <c r="O21" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="P21" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="R21" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="U21" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="V21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="X21" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Y21" t="n">
         <v>12</v>
       </c>
       <c r="Z21" t="n">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="AA21" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AF21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>460</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>9</v>
-      </c>
       <c r="AR21" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.6</v>
+        <v>40</v>
       </c>
       <c r="AT21" t="n">
         <v>6.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AX21" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY21" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BA21" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BB21" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="BC21" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="BD21" t="n">
         <v>29</v>
       </c>
       <c r="BE21" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BG21" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G22" t="n">
         <v>2.08</v>
@@ -4646,7 +4646,7 @@
         <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
         <v>3.4</v>
@@ -4655,7 +4655,7 @@
         <v>3.5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M22" t="n">
         <v>1.1</v>
@@ -4664,22 +4664,22 @@
         <v>3.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P22" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S22" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U22" t="n">
         <v>1.94</v>
@@ -4700,7 +4700,7 @@
         <v>32</v>
       </c>
       <c r="AA22" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB22" t="n">
         <v>7.8</v>
@@ -4712,7 +4712,7 @@
         <v>18</v>
       </c>
       <c r="AE22" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF22" t="n">
         <v>11.5</v>
@@ -4727,13 +4727,13 @@
         <v>80</v>
       </c>
       <c r="AJ22" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK22" t="n">
         <v>25</v>
       </c>
       <c r="AL22" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM22" t="n">
         <v>150</v>
@@ -4754,7 +4754,7 @@
         <v>27</v>
       </c>
       <c r="AS22" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AT22" t="n">
         <v>7.2</v>
@@ -4763,7 +4763,7 @@
         <v>7.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW22" t="n">
         <v>55</v>
@@ -4772,13 +4772,13 @@
         <v>10.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA22" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BB22" t="n">
         <v>22</v>
@@ -4790,17 +4790,17 @@
         <v>40</v>
       </c>
       <c r="BE22" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="BF22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="G23" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="H23" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="I23" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="G24" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
         <v>3.7</v>
@@ -5043,91 +5043,91 @@
         <v>3.9</v>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O24" t="n">
         <v>1.37</v>
       </c>
       <c r="P24" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W24" t="n">
         <v>2.1</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.06</v>
-      </c>
       <c r="X24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z24" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB24" t="n">
         <v>8.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD24" t="n">
         <v>18.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>200</v>
       </c>
       <c r="AJ24" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AK24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="n">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AM24" t="n">
         <v>580</v>
       </c>
       <c r="AN24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO24" t="n">
         <v>270</v>
@@ -5136,10 +5136,10 @@
         <v>12</v>
       </c>
       <c r="AQ24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AS24" t="n">
         <v>38</v>
@@ -5151,16 +5151,16 @@
         <v>7.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW24" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AX24" t="n">
         <v>10</v>
       </c>
       <c r="AY24" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ24" t="n">
         <v>18</v>
@@ -5175,10 +5175,10 @@
         <v>18</v>
       </c>
       <c r="BD24" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BE24" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BF24" t="n">
         <v>12.5</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -5219,82 +5219,82 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="G25" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="H25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N25" t="n">
         <v>4.6</v>
       </c>
-      <c r="I25" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N25" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O25" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U25" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q25" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.12</v>
-      </c>
       <c r="V25" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W25" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="X25" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y25" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Z25" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE25" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
         <v>12</v>
@@ -5303,16 +5303,16 @@
         <v>11</v>
       </c>
       <c r="AH25" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL25" t="n">
         <v>32</v>
@@ -5321,68 +5321,68 @@
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="AQ25" t="n">
-        <v>5.8</v>
+        <v>19.5</v>
       </c>
       <c r="AR25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF25" t="n">
         <v>6.4</v>
       </c>
-      <c r="AS25" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BG25" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -5413,19 +5413,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="G26" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="H26" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J26" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K26" t="n">
         <v>3.75</v>
@@ -5437,10 +5437,10 @@
         <v>1.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O26" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="P26" t="n">
         <v>1.62</v>
@@ -5458,19 +5458,19 @@
         <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V26" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W26" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X26" t="n">
         <v>11</v>
       </c>
       <c r="Y26" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z26" t="n">
         <v>38</v>
@@ -5482,7 +5482,7 @@
         <v>7</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD26" t="n">
         <v>21</v>
@@ -5497,19 +5497,19 @@
         <v>11.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AI26" t="n">
-        <v>450</v>
+        <v>240</v>
       </c>
       <c r="AJ26" t="n">
         <v>24</v>
       </c>
       <c r="AK26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL26" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
@@ -5518,43 +5518,43 @@
         <v>22</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ26" t="n">
         <v>10.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="AS26" t="n">
-        <v>9.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW26" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AX26" t="n">
         <v>9</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB26" t="n">
         <v>19.5</v>
@@ -5563,20 +5563,20 @@
         <v>21</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.199999999999999</v>
+        <v>44</v>
       </c>
       <c r="BE26" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="BF26" t="n">
         <v>17.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G27" t="n">
         <v>2.34</v>
       </c>
-      <c r="G27" t="n">
-        <v>2.42</v>
-      </c>
       <c r="H27" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="I27" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J27" t="n">
         <v>3.1</v>
@@ -5631,13 +5631,13 @@
         <v>1.12</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="O27" t="n">
         <v>1.54</v>
       </c>
       <c r="P27" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q27" t="n">
         <v>2.62</v>
@@ -5649,34 +5649,34 @@
         <v>5.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U27" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V27" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W27" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="X27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z27" t="n">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="AA27" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB27" t="n">
         <v>7.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD27" t="n">
         <v>17</v>
@@ -5685,13 +5685,13 @@
         <v>440</v>
       </c>
       <c r="AF27" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="n">
         <v>500</v>
@@ -5718,13 +5718,13 @@
         <v>7.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR27" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT27" t="n">
         <v>6.6</v>
@@ -5736,10 +5736,10 @@
         <v>13.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AX27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY27" t="n">
         <v>10</v>
@@ -5748,29 +5748,29 @@
         <v>19</v>
       </c>
       <c r="BA27" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB27" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BC27" t="n">
-        <v>28</v>
+        <v>7.6</v>
       </c>
       <c r="BD27" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="G28" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I28" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K28" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L28" t="n">
         <v>1.37</v>
@@ -5840,10 +5840,10 @@
         <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T28" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
@@ -5852,22 +5852,22 @@
         <v>1.15</v>
       </c>
       <c r="W28" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="X28" t="n">
         <v>17.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Z28" t="n">
         <v>60</v>
       </c>
       <c r="AA28" t="n">
-        <v>700</v>
+        <v>220</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC28" t="n">
         <v>9.800000000000001</v>
@@ -5876,7 +5876,7 @@
         <v>26</v>
       </c>
       <c r="AE28" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF28" t="n">
         <v>9</v>
@@ -5888,10 +5888,10 @@
         <v>23</v>
       </c>
       <c r="AI28" t="n">
-        <v>95</v>
+        <v>230</v>
       </c>
       <c r="AJ28" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK28" t="n">
         <v>16</v>
@@ -5900,10 +5900,10 @@
         <v>36</v>
       </c>
       <c r="AM28" t="n">
-        <v>390</v>
+        <v>130</v>
       </c>
       <c r="AN28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AO28" t="n">
         <v>120</v>
@@ -5912,37 +5912,37 @@
         <v>15.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR28" t="n">
         <v>50</v>
       </c>
       <c r="AS28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT28" t="n">
         <v>7.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY28" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9</v>
       </c>
       <c r="AZ28" t="n">
         <v>21</v>
       </c>
       <c r="BA28" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="BB28" t="n">
         <v>13</v>
@@ -5957,14 +5957,14 @@
         <v>70</v>
       </c>
       <c r="BF28" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG28" t="n">
         <v>42</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G29" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H29" t="n">
         <v>2.54</v>
@@ -6007,7 +6007,7 @@
         <v>2.56</v>
       </c>
       <c r="J29" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K29" t="n">
         <v>3.4</v>
@@ -6046,13 +6046,13 @@
         <v>1.64</v>
       </c>
       <c r="W29" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X29" t="n">
         <v>10.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z29" t="n">
         <v>15</v>
@@ -6073,7 +6073,7 @@
         <v>32</v>
       </c>
       <c r="AF29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG29" t="n">
         <v>13.5</v>
@@ -6088,7 +6088,7 @@
         <v>60</v>
       </c>
       <c r="AK29" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL29" t="n">
         <v>60</v>
@@ -6103,10 +6103,10 @@
         <v>38</v>
       </c>
       <c r="AP29" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ29" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR29" t="n">
         <v>14</v>
@@ -6133,13 +6133,13 @@
         <v>12.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA29" t="n">
         <v>46</v>
       </c>
       <c r="BB29" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BC29" t="n">
         <v>36</v>
@@ -6151,14 +6151,14 @@
         <v>38</v>
       </c>
       <c r="BF29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BG29" t="n">
         <v>27</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G30" t="n">
         <v>2.52</v>
@@ -6213,13 +6213,13 @@
         <v>1.14</v>
       </c>
       <c r="N30" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O30" t="n">
         <v>1.56</v>
       </c>
       <c r="P30" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q30" t="n">
         <v>2.78</v>
@@ -6255,7 +6255,7 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
         <v>1000</v>
@@ -6300,28 +6300,28 @@
         <v>6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="AR30" t="n">
         <v>6</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AV30" t="n">
         <v>5.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.5</v>
+        <v>2.86</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AY30" t="n">
         <v>4.9</v>
@@ -6330,16 +6330,16 @@
         <v>5.8</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="BB30" t="n">
         <v>6.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.5</v>
+        <v>2.86</v>
       </c>
       <c r="BE30" t="n">
         <v>7.4</v>
@@ -6348,11 +6348,11 @@
         <v>6.6</v>
       </c>
       <c r="BG30" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
         <v>1.24</v>
       </c>
       <c r="M31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N31" t="n">
         <v>5.3</v>
@@ -6413,19 +6413,19 @@
         <v>1.15</v>
       </c>
       <c r="P31" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q31" t="n">
         <v>1.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S31" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="T31" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U31" t="n">
         <v>2.14</v>
@@ -6437,10 +6437,10 @@
         <v>2.96</v>
       </c>
       <c r="X31" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="Y31" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="Z31" t="n">
         <v>1000</v>
@@ -6470,7 +6470,7 @@
         <v>23</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ31" t="n">
         <v>14.5</v>
@@ -6491,19 +6491,19 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ31" t="n">
         <v>6.6</v>
       </c>
       <c r="AR31" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS31" t="n">
         <v>7.8</v>
       </c>
       <c r="AT31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AU31" t="n">
         <v>5.1</v>
@@ -6512,41 +6512,41 @@
         <v>6.4</v>
       </c>
       <c r="AW31" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX31" t="n">
         <v>4.8</v>
       </c>
       <c r="AY31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BA31" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC31" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BD31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE31" t="n">
         <v>7.4</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="BG31" t="n">
         <v>7.4</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G32" t="n">
         <v>4.5</v>
       </c>
-      <c r="G32" t="n">
-        <v>4.9</v>
-      </c>
       <c r="H32" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="I32" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="J32" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K32" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L32" t="n">
         <v>1.45</v>
@@ -6601,13 +6601,13 @@
         <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O32" t="n">
         <v>1.37</v>
       </c>
       <c r="P32" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q32" t="n">
         <v>2.14</v>
@@ -6616,22 +6616,22 @@
         <v>1.31</v>
       </c>
       <c r="S32" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T32" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U32" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V32" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="W32" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X32" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y32" t="n">
         <v>8.6</v>
@@ -6640,13 +6640,13 @@
         <v>12.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AB32" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD32" t="n">
         <v>11</v>
@@ -6655,25 +6655,25 @@
         <v>23</v>
       </c>
       <c r="AF32" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG32" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AH32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI32" t="n">
         <v>42</v>
       </c>
       <c r="AJ32" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL32" t="n">
         <v>70</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>75</v>
       </c>
       <c r="AM32" t="n">
         <v>140</v>
@@ -6682,7 +6682,7 @@
         <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AP32" t="n">
         <v>9.800000000000001</v>
@@ -6691,16 +6691,16 @@
         <v>7.4</v>
       </c>
       <c r="AR32" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT32" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV32" t="n">
         <v>9.199999999999999</v>
@@ -6709,38 +6709,38 @@
         <v>18.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AY32" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AZ32" t="n">
         <v>17</v>
       </c>
       <c r="BA32" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB32" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC32" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BD32" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE32" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF32" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG32" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -6771,19 +6771,19 @@
         </is>
       </c>
       <c r="F33" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H33" t="n">
         <v>3</v>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>3.1</v>
       </c>
-      <c r="H33" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>2.98</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2.92</v>
       </c>
       <c r="K33" t="n">
         <v>3</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G34" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H34" t="n">
         <v>7</v>
       </c>
       <c r="I34" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J34" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K34" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -6995,10 +6995,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -7165,10 +7165,10 @@
         <v>4.4</v>
       </c>
       <c r="H35" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I35" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J35" t="n">
         <v>3.45</v>
@@ -7180,19 +7180,19 @@
         <v>1.5</v>
       </c>
       <c r="M35" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N35" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O35" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P35" t="n">
         <v>1.73</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R35" t="n">
         <v>1.27</v>
@@ -7201,16 +7201,16 @@
         <v>4.4</v>
       </c>
       <c r="T35" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V35" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="W35" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X35" t="n">
         <v>11</v>
@@ -7219,7 +7219,7 @@
         <v>7.8</v>
       </c>
       <c r="Z35" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA35" t="n">
         <v>26</v>
@@ -7231,10 +7231,10 @@
         <v>7.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE35" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF35" t="n">
         <v>32</v>
@@ -7243,19 +7243,19 @@
         <v>18</v>
       </c>
       <c r="AH35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI35" t="n">
         <v>48</v>
       </c>
       <c r="AJ35" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="n">
         <v>65</v>
       </c>
       <c r="AL35" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM35" t="n">
         <v>150</v>
@@ -7267,13 +7267,13 @@
         <v>21</v>
       </c>
       <c r="AP35" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ35" t="n">
         <v>7.2</v>
       </c>
       <c r="AR35" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS35" t="n">
         <v>21</v>
@@ -7288,10 +7288,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW35" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX35" t="n">
-        <v>28</v>
+        <v>19.5</v>
       </c>
       <c r="AY35" t="n">
         <v>15.5</v>
@@ -7300,29 +7300,29 @@
         <v>19</v>
       </c>
       <c r="BA35" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BB35" t="n">
-        <v>85</v>
+        <v>13.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BD35" t="n">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="BE35" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG35" t="n">
         <v>18</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -7353,31 +7353,31 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="G36" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="H36" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="J36" t="n">
         <v>3.3</v>
       </c>
       <c r="K36" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L36" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M36" t="n">
         <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O36" t="n">
         <v>1.28</v>
@@ -7386,7 +7386,7 @@
         <v>2.08</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R36" t="n">
         <v>1.44</v>
@@ -7395,43 +7395,43 @@
         <v>3.15</v>
       </c>
       <c r="T36" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="U36" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V36" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W36" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="X36" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Y36" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AA36" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AB36" t="n">
         <v>11.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AF36" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG36" t="n">
         <v>11</v>
@@ -7440,83 +7440,83 @@
         <v>15.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ36" t="n">
         <v>30</v>
       </c>
       <c r="AK36" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL36" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO36" t="n">
         <v>34</v>
       </c>
-      <c r="AM36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>46</v>
-      </c>
       <c r="AP36" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="AS36" t="n">
-        <v>7.8</v>
+        <v>50</v>
       </c>
       <c r="AT36" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AU36" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV36" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AW36" t="n">
         <v>32</v>
       </c>
       <c r="AX36" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AY36" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BA36" t="n">
         <v>38</v>
       </c>
       <c r="BB36" t="n">
-        <v>7.2</v>
+        <v>27</v>
       </c>
       <c r="BC36" t="n">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="BD36" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG36" t="n">
         <v>28</v>
       </c>
-      <c r="BE36" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
         <v>3.65</v>
       </c>
       <c r="J37" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="K37" t="n">
         <v>4.1</v>
@@ -7589,10 +7589,10 @@
         <v>3.3</v>
       </c>
       <c r="T37" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U37" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V37" t="n">
         <v>1.37</v>
@@ -7664,16 +7664,16 @@
         <v>3.8</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AU37" t="n">
         <v>2.98</v>
       </c>
       <c r="AV37" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AW37" t="n">
         <v>4.1</v>
@@ -7688,13 +7688,13 @@
         <v>3.75</v>
       </c>
       <c r="BA37" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB37" t="n">
         <v>4.2</v>
       </c>
       <c r="BC37" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD37" t="n">
         <v>4.2</v>
@@ -7703,14 +7703,14 @@
         <v>4.4</v>
       </c>
       <c r="BF37" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH31"/>
+  <dimension ref="A1:BH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10:15:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Al-Jndal</t>
+          <t>KAC 1909</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeddah Club</t>
+          <t>VST Volkermarkt</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.46</v>
+        <v>4.6</v>
       </c>
       <c r="H2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="S2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>240</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>260</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>4.9</v>
       </c>
-      <c r="I2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="S2" t="n">
-        <v>18</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>230</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>240</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG2" t="n">
+      <c r="AR2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX2" t="n">
         <v>22</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>580</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>340</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>140</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>140</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>10.5</v>
       </c>
       <c r="AY2" t="n">
         <v>18.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.5</v>
+        <v>42</v>
       </c>
       <c r="BB2" t="n">
+        <v>95</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>80</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>140</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>240</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>140</v>
+      </c>
+      <c r="BG2" t="n">
         <v>34</v>
       </c>
-      <c r="BC2" t="n">
-        <v>60</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>80</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>16</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -942,76 +942,76 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KAC 1909</t>
+          <t>Tampere Utd</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VST Volkermarkt</t>
+          <t>FC Jazz</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9</v>
+        <v>1.02</v>
       </c>
       <c r="H3" t="n">
-        <v>1.93</v>
+        <v>300</v>
       </c>
       <c r="I3" t="n">
-        <v>2.02</v>
+        <v>510</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>55</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>110</v>
       </c>
       <c r="L3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="S3" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="U3" t="n">
-        <v>2.58</v>
+        <v>2.14</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.34</v>
+        <v>50</v>
       </c>
       <c r="X3" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
         <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1020,10 +1020,10 @@
         <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
@@ -1035,7 +1035,7 @@
         <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1053,75 +1053,75 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.8</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BB3" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.35</v>
+        <v>1.55</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:55:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tampere Utd</t>
+          <t>Al Faisaly ( KSA )</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Jazz</t>
+          <t>Al Jubail</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="G4" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="H4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="R4" t="n">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="S4" t="n">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="T4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>1.14</v>
       </c>
       <c r="W4" t="n">
-        <v>3.25</v>
+        <v>2.28</v>
       </c>
       <c r="X4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>18.5</v>
+        <v>6.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="AE4" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>990</v>
       </c>
       <c r="AI4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AL4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>4.2</v>
+        <v>75</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AP4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AR4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AS4" t="n">
-        <v>18.5</v>
+        <v>2.86</v>
       </c>
       <c r="AT4" t="n">
-        <v>13</v>
+        <v>2.86</v>
       </c>
       <c r="AU4" t="n">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="AV4" t="n">
-        <v>25</v>
+        <v>4.9</v>
       </c>
       <c r="AW4" t="n">
-        <v>30</v>
+        <v>4.7</v>
       </c>
       <c r="AX4" t="n">
-        <v>10.5</v>
+        <v>2.86</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>3.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>36</v>
+        <v>4.7</v>
       </c>
       <c r="BB4" t="n">
-        <v>11.5</v>
+        <v>2.86</v>
       </c>
       <c r="BC4" t="n">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.5</v>
+        <v>2.98</v>
       </c>
       <c r="BE4" t="n">
-        <v>32</v>
+        <v>2.86</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>15.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Slovakian 2 Liga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:55:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Al Faisaly ( KSA )</t>
+          <t>Zlate Moravce</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jubail</t>
+          <t>Lokomotiva Zvolen</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="G5" t="n">
-        <v>1.45</v>
+        <v>1.89</v>
       </c>
       <c r="H5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF5" t="n">
         <v>8.4</v>
       </c>
-      <c r="I5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N5" t="n">
-        <v>6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="AG5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>310</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>420</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>150</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD5" t="n">
         <v>90</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>14</v>
-      </c>
       <c r="BE5" t="n">
-        <v>28</v>
+        <v>350</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.5</v>
+        <v>23</v>
       </c>
       <c r="BG5" t="n">
-        <v>15</v>
+        <v>190</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Slovakian 2 Liga</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,184 +1519,184 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Zlate Moravce</t>
+          <t>SAK Klagenfurt</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lokomotiva Zvolen</t>
+          <t>Kottmannsdorf</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="G6" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="H6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N6" t="n">
         <v>4.5</v>
       </c>
-      <c r="I6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N6" t="n">
-        <v>6.2</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.74</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.32</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="U6" t="n">
-        <v>2.62</v>
+        <v>2.24</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="X6" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="Z6" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AF6" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AI6" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
         <v>23</v>
       </c>
       <c r="AK6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR6" t="n">
         <v>28</v>
       </c>
-      <c r="AM6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP6" t="n">
+      <c r="AS6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>23</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG6" t="n">
         <v>22</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>30</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAK Klagenfurt</t>
+          <t>Asco Atsv Wolfsberg</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kottmannsdorf</t>
+          <t>Atus Ferlach</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.9</v>
+        <v>1.15</v>
       </c>
       <c r="G7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H7" t="n">
+        <v>13</v>
+      </c>
+      <c r="I7" t="n">
+        <v>22</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K7" t="n">
+        <v>25</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="U7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>4.2</v>
       </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U7" t="n">
+      <c r="AR7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE7" t="n">
         <v>2.34</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW7" t="n">
+      <c r="BF7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BG7" t="n">
         <v>8.4</v>
       </c>
-      <c r="AX7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Asco Atsv Wolfsberg</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Atus Ferlach</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="G8" t="n">
-        <v>1.18</v>
+        <v>1.76</v>
       </c>
       <c r="H8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X8" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP8" t="n">
         <v>11</v>
       </c>
-      <c r="I8" t="n">
-        <v>25</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="AQ8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT8" t="n">
         <v>6.8</v>
       </c>
-      <c r="K8" t="n">
-        <v>950</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG8" t="n">
+      <c r="AU8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>90</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>80</v>
+      </c>
+      <c r="BB8" t="n">
         <v>16</v>
       </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BC8" t="n">
-        <v>4.9</v>
+        <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.6</v>
+        <v>42</v>
       </c>
       <c r="BE8" t="n">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.36</v>
+        <v>13.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>CSA Steaua Bucuresti</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="G9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T9" t="n">
         <v>1.73</v>
       </c>
-      <c r="H9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="U9" t="n">
         <v>2.16</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.88</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>2.36</v>
+        <v>1.86</v>
       </c>
       <c r="X9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV9" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y9" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>180</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="AW9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN9" t="n">
+      <c r="BF9" t="n">
         <v>13</v>
       </c>
-      <c r="AO9" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ9" t="n">
+      <c r="BG9" t="n">
         <v>17</v>
       </c>
-      <c r="AR9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>80</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>42</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:35:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CSA Steaua Bucuresti</t>
+          <t>Al-Zulfi SC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>Al-Anwar Club</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="G10" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="I10" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
         <v>3.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.35</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.3</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="X10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE10" t="n">
         <v>130</v>
       </c>
       <c r="AF10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>200</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP10" t="n">
         <v>11</v>
       </c>
-      <c r="AH10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP10" t="n">
+      <c r="AQ10" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>12.5</v>
       </c>
       <c r="AR10" t="n">
         <v>11</v>
       </c>
       <c r="AS10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT10" t="n">
         <v>7.8</v>
       </c>
-      <c r="AT10" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AX10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
         <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.4</v>
+        <v>48</v>
       </c>
       <c r="BB10" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="BC10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG10" t="n">
         <v>18.5</v>
       </c>
-      <c r="BD10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>50</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:35:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al-Zulfi SC</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al-Anwar Club</t>
+          <t>Sarmiento de Junin</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.16</v>
+        <v>2.72</v>
       </c>
       <c r="G11" t="n">
-        <v>2.32</v>
+        <v>2.76</v>
       </c>
       <c r="H11" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="I11" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>2.92</v>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>2.36</v>
       </c>
       <c r="O11" t="n">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>1.43</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.08</v>
+        <v>3.15</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="S11" t="n">
-        <v>3.85</v>
+        <v>7.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="X11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG11" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y11" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AH11" t="n">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="AI11" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AJ11" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AK11" t="n">
         <v>48</v>
       </c>
       <c r="AL11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>27</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>95</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC11" t="n">
         <v>44</v>
       </c>
-      <c r="AM11" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BD11" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.800000000000001</v>
+        <v>200</v>
       </c>
       <c r="BF11" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.199999999999999</v>
+        <v>80</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P12" t="n">
         <v>2.76</v>
       </c>
-      <c r="G12" t="n">
+      <c r="Q12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U12" t="n">
         <v>2.78</v>
       </c>
-      <c r="H12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.68</v>
-      </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="X12" t="n">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="Z12" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB12" t="n">
-        <v>7</v>
+        <v>15.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AF12" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AH12" t="n">
-        <v>29</v>
+        <v>14.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="AJ12" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AK12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM12" t="n">
         <v>50</v>
       </c>
-      <c r="AL12" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>270</v>
-      </c>
       <c r="AN12" t="n">
-        <v>70</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO12" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="AR12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AS12" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV12" t="n">
         <v>14.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="AX12" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="BB12" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE12" t="n">
         <v>42</v>
       </c>
-      <c r="BC12" t="n">
-        <v>42</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>60</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>110</v>
-      </c>
       <c r="BF12" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="BG12" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.08</v>
+        <v>3.3</v>
       </c>
       <c r="G13" t="n">
-        <v>2.12</v>
+        <v>3.4</v>
       </c>
       <c r="H13" t="n">
-        <v>3.55</v>
+        <v>2.48</v>
       </c>
       <c r="I13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N13" t="n">
         <v>3.65</v>
       </c>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N13" t="n">
-        <v>6</v>
-      </c>
       <c r="O13" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="P13" t="n">
-        <v>2.64</v>
+        <v>1.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.59</v>
+        <v>2.06</v>
       </c>
       <c r="R13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.66</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.37</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.89</v>
+        <v>1.42</v>
       </c>
       <c r="X13" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Y13" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>29</v>
+        <v>16.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AB13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR13" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD13" t="n">
+      <c r="AS13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>15</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="BA13" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>46</v>
+      </c>
+      <c r="BC13" t="n">
         <v>34</v>
       </c>
-      <c r="AF13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA13" t="n">
+      <c r="BD13" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>90</v>
+      </c>
+      <c r="BF13" t="n">
         <v>32</v>
       </c>
-      <c r="BB13" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BG13" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>1.88</v>
       </c>
       <c r="G14" t="n">
-        <v>3.35</v>
+        <v>1.92</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="I14" t="n">
-        <v>2.54</v>
+        <v>5.3</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="P14" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="V14" t="n">
-        <v>1.64</v>
+        <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>1.42</v>
+        <v>2.08</v>
       </c>
       <c r="X14" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="Z14" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="AA14" t="n">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.5</v>
+        <v>6.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AE14" t="n">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="AF14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>21</v>
       </c>
-      <c r="AG14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>55</v>
-      </c>
       <c r="AK14" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AL14" t="n">
         <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="n">
-        <v>44</v>
+        <v>18.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="AP14" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AQ14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX14" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AR14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX14" t="n">
+      <c r="AY14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>85</v>
+      </c>
+      <c r="BB14" t="n">
         <v>19</v>
       </c>
-      <c r="AY14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>46</v>
-      </c>
       <c r="BC14" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="BD14" t="n">
         <v>46</v>
       </c>
       <c r="BE14" t="n">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="BF14" t="n">
-        <v>36</v>
+        <v>16.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="G15" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="I15" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L15" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M15" t="n">
         <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P15" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="R15" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S15" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="U15" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="V15" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="X15" t="n">
         <v>11</v>
       </c>
       <c r="Y15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z15" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AA15" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AB15" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AF15" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AG15" t="n">
         <v>10.5</v>
       </c>
       <c r="AH15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>25</v>
       </c>
-      <c r="AI15" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="AK15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN15" t="n">
         <v>21</v>
       </c>
-      <c r="AK15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AO15" t="n">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="AP15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AS15" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW15" t="n">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="BB15" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BC15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD15" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BE15" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="BF15" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG15" t="n">
         <v>70</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zaragoza</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="L16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.34</v>
+        <v>2.74</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.36</v>
+        <v>1.88</v>
       </c>
       <c r="G17" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="H17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K17" t="n">
         <v>3.95</v>
       </c>
-      <c r="I17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.1</v>
-      </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P17" t="n">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>2.02</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Juticalpa</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="G18" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="M18" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.02</v>
+        <v>1.64</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="T18" t="n">
-        <v>1.88</v>
+        <v>1.69</v>
       </c>
       <c r="U18" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="V18" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="X18" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="Y18" t="n">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="Z18" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AD18" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH18" t="n">
         <v>20</v>
       </c>
       <c r="AI18" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AK18" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM18" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC18" t="n">
         <v>13.5</v>
       </c>
-      <c r="AO18" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU18" t="n">
+      <c r="BD18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE18" t="n">
         <v>7.8</v>
       </c>
-      <c r="AV18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>55</v>
-      </c>
       <c r="BF18" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>60</v>
+        <v>7.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Genesis Huracan</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Juticalpa</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="G19" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="H19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I19" t="n">
         <v>5</v>
       </c>
-      <c r="I19" t="n">
-        <v>6.2</v>
-      </c>
       <c r="J19" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="M19" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6</v>
+        <v>2.96</v>
       </c>
       <c r="O19" t="n">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="P19" t="n">
-        <v>2.26</v>
+        <v>1.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.64</v>
+        <v>2.46</v>
       </c>
       <c r="R19" t="n">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="S19" t="n">
-        <v>2.58</v>
+        <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>1.69</v>
+        <v>2.14</v>
       </c>
       <c r="U19" t="n">
-        <v>2.14</v>
+        <v>1.79</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="X19" t="n">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="Y19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK19" t="n">
         <v>24</v>
       </c>
-      <c r="Z19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF19" t="n">
+      <c r="AL19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>12</v>
       </c>
-      <c r="AG19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
+      <c r="AR19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV19" t="n">
         <v>18</v>
       </c>
-      <c r="AK19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL19" t="n">
+      <c r="AW19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD19" t="n">
         <v>32</v>
       </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
+      <c r="BE19" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF19" t="n">
         <v>18</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ19" t="n">
+      <c r="BG19" t="n">
         <v>15.5</v>
       </c>
-      <c r="BA19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,184 +4235,184 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="G20" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>2.42</v>
       </c>
       <c r="I20" t="n">
-        <v>4.9</v>
+        <v>2.44</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
         <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="P20" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="U20" t="n">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="W20" t="n">
-        <v>2.04</v>
+        <v>1.4</v>
       </c>
       <c r="X20" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT20" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD20" t="n">
+      <c r="AU20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX20" t="n">
         <v>20</v>
       </c>
-      <c r="AE20" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK20" t="n">
+      <c r="AY20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>55</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>42</v>
+      </c>
+      <c r="BG20" t="n">
         <v>25</v>
       </c>
-      <c r="AL20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.35</v>
+        <v>1.68</v>
       </c>
       <c r="G21" t="n">
-        <v>3.45</v>
+        <v>1.69</v>
       </c>
       <c r="H21" t="n">
-        <v>2.42</v>
+        <v>6.4</v>
       </c>
       <c r="I21" t="n">
-        <v>2.48</v>
+        <v>6.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="O21" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="P21" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="U21" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="V21" t="n">
-        <v>1.68</v>
+        <v>1.17</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4</v>
+        <v>2.44</v>
       </c>
       <c r="X21" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Y21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC21" t="n">
         <v>8.6</v>
       </c>
-      <c r="Z21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="AD21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>80</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD21" t="n">
         <v>34</v>
       </c>
-      <c r="AB21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI21" t="n">
+      <c r="BE21" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG21" t="n">
         <v>48</v>
       </c>
-      <c r="AJ21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>55</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>38</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>44</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>24</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.67</v>
+        <v>2.32</v>
       </c>
       <c r="G22" t="n">
-        <v>1.69</v>
+        <v>2.38</v>
       </c>
       <c r="H22" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="I22" t="n">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="L22" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="M22" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>2.74</v>
       </c>
       <c r="O22" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>1.56</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.04</v>
+        <v>2.68</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="S22" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="U22" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="V22" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>2.46</v>
+        <v>1.73</v>
       </c>
       <c r="X22" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Y22" t="n">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AA22" t="n">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="AB22" t="n">
         <v>7.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>25</v>
+        <v>16.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AF22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>9.4</v>
       </c>
-      <c r="AG22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN22" t="n">
+      <c r="AR22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY22" t="n">
         <v>10.5</v>
       </c>
-      <c r="AO22" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV22" t="n">
+      <c r="AZ22" t="n">
         <v>22</v>
       </c>
-      <c r="AW22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>21</v>
-      </c>
       <c r="BA22" t="n">
-        <v>60</v>
+        <v>15.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="BC22" t="n">
-        <v>17.5</v>
+        <v>28</v>
       </c>
       <c r="BD22" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BE22" t="n">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="BF22" t="n">
-        <v>9.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BG22" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:15:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>CD Olimpia</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Lobos UPNFM</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.32</v>
+        <v>1.4</v>
       </c>
       <c r="G23" t="n">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="H23" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="K23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X23" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF23" t="n">
         <v>3.3</v>
       </c>
-      <c r="L23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="X23" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC23" t="n">
+      <c r="BG23" t="n">
         <v>7.2</v>
       </c>
-      <c r="AD23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>29</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>65</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>46</v>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="G24" t="n">
-        <v>2.48</v>
+        <v>4.6</v>
       </c>
       <c r="H24" t="n">
-        <v>3.7</v>
+        <v>1.99</v>
       </c>
       <c r="I24" t="n">
-        <v>4.2</v>
+        <v>2.04</v>
       </c>
       <c r="J24" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="K24" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="L24" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="M24" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="P24" t="n">
-        <v>1.54</v>
+        <v>1.88</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.68</v>
+        <v>2.1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="T24" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="U24" t="n">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="V24" t="n">
-        <v>1.33</v>
+        <v>1.96</v>
       </c>
       <c r="W24" t="n">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="X24" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF24" t="n">
         <v>34</v>
       </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AP24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU24" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AV24" t="n">
-        <v>5.7</v>
+        <v>9.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.2</v>
+        <v>19.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>5.2</v>
+        <v>26</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.6</v>
+        <v>15.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="BA24" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BB24" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BC24" t="n">
-        <v>5.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE24" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BF24" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20:15:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CD Olimpia</t>
+          <t>Talleres</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lobos UPNFM</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.4</v>
+        <v>2.84</v>
       </c>
       <c r="G25" t="n">
-        <v>1.51</v>
+        <v>2.92</v>
       </c>
       <c r="H25" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="I25" t="n">
-        <v>8.6</v>
+        <v>3.2</v>
       </c>
       <c r="J25" t="n">
-        <v>4.5</v>
+        <v>2.94</v>
       </c>
       <c r="K25" t="n">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.62</v>
+        <v>1.47</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.58</v>
+        <v>3.05</v>
       </c>
       <c r="R25" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4.4</v>
+        <v>1.51</v>
       </c>
       <c r="G26" t="n">
-        <v>4.6</v>
+        <v>1.53</v>
       </c>
       <c r="H26" t="n">
-        <v>1.99</v>
+        <v>7.4</v>
       </c>
       <c r="I26" t="n">
-        <v>2.06</v>
+        <v>7.6</v>
       </c>
       <c r="J26" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="K26" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="L26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.88</v>
+        <v>2.32</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Talleres</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.86</v>
+        <v>3.95</v>
       </c>
       <c r="G27" t="n">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="H27" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J27" t="n">
         <v>3.15</v>
       </c>
-      <c r="I27" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.94</v>
-      </c>
       <c r="K27" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P27" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.05</v>
+        <v>2.34</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.52</v>
+        <v>2.44</v>
       </c>
       <c r="G28" t="n">
-        <v>1.54</v>
+        <v>2.48</v>
       </c>
       <c r="H28" t="n">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="I28" t="n">
-        <v>7.6</v>
+        <v>3.45</v>
       </c>
       <c r="J28" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="K28" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P28" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,33 +5981,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Real Espana</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>CD Marathon</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="G29" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="H29" t="n">
-        <v>2.16</v>
+        <v>2.74</v>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="J29" t="n">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="K29" t="n">
         <v>3.45</v>
@@ -6016,537 +6016,149 @@
         <v>1.5</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N29" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="O29" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P29" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="R29" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="T29" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="U29" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="V29" t="n">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="W29" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="X29" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="Z29" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
         <v>12</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE29" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AG29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH29" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI29" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>10.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR29" t="n">
-        <v>11.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS29" t="n">
-        <v>25</v>
+        <v>5.4</v>
       </c>
       <c r="AT29" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="AW29" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AX29" t="n">
-        <v>27</v>
+        <v>4.8</v>
       </c>
       <c r="AY29" t="n">
-        <v>15.5</v>
+        <v>4.9</v>
       </c>
       <c r="AZ29" t="n">
-        <v>18</v>
+        <v>5.3</v>
       </c>
       <c r="BA29" t="n">
-        <v>40</v>
+        <v>5.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>75</v>
+        <v>6.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>46</v>
+        <v>5.1</v>
       </c>
       <c r="BD29" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BE29" t="n">
-        <v>18</v>
+        <v>5.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>16.5</v>
+        <v>5</v>
       </c>
       <c r="BG29" t="n">
-        <v>19.5</v>
+        <v>5.2</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-02 11:25:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Once Caldas</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Ind Medellin</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="I30" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="X30" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>29</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>27</v>
-      </c>
-      <c r="BH30" t="inlineStr">
-        <is>
-          <t>2026-04-02 11:25:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Honduras Liga Nacional</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Real Espana</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>CD Marathon</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="G31" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="H31" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="I31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J31" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X31" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH31" t="inlineStr">
-        <is>
-          <t>2026-04-02 11:25:25</t>
+          <t>2026-04-02 13:57:04</t>
         </is>
       </c>
     </row>
